--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
@@ -558,8 +558,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>192.894</v>
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-192.894</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.90149e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.578</v>
       </c>
       <c r="F2" t="n">
         <v>0.1041068919463167</v>
@@ -584,7 +593,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 20.156x + -10528.520</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -601,8 +610,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>167.724</v>
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-167.724</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.8692e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.01300000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0.3194170350105707</v>
@@ -627,7 +645,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.110x + -11894.280</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -644,8 +662,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>156.5880000000001</v>
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-156.5880000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.8499e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.279</v>
       </c>
       <c r="F4" t="n">
         <v>0.4592797322174187</v>
@@ -670,7 +697,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.604x + -11916.574</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -687,8 +714,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>146.3920000000001</v>
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-146.3920000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.83647e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.505</v>
       </c>
       <c r="F5" t="n">
         <v>0.4211102207886185</v>
@@ -713,7 +749,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.037x + -11929.575</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -730,8 +766,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>140.352</v>
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-140.352</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.82578e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.648</v>
       </c>
       <c r="F6" t="n">
         <v>0.7438327345209143</v>
@@ -756,7 +801,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.132x + -12825.707</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -773,8 +818,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>137.215</v>
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-137.215</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.81836e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.807</v>
       </c>
       <c r="F7" t="n">
         <v>0.147417332115022</v>
@@ -799,7 +853,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.466x + -11753.455</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -816,8 +870,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>133.602</v>
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-133.602</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.8107e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.911</v>
       </c>
       <c r="F8" t="n">
         <v>0.5572059038139808</v>
@@ -842,7 +905,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.280x + -12489.765</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -859,8 +922,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>131.738</v>
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-131.738</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.80569e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.02</v>
       </c>
       <c r="F9" t="n">
         <v>0.4414859778278686</v>
@@ -885,7 +957,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.426x + -11877.666</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -902,8 +974,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>128.581</v>
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-128.581</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.80002e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.11499999999999</v>
       </c>
       <c r="F10" t="n">
         <v>0.3162438204802794</v>
@@ -928,7 +1009,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.416x + -12204.342</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -945,8 +1026,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>124.093</v>
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-124.093</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.79627e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.221</v>
       </c>
       <c r="F11" t="n">
         <v>0.4522738789671745</v>
@@ -971,7 +1061,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.049x + -12358.873</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -1134,8 +1224,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>152.723</v>
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-152.723</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.93127e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.024</v>
       </c>
       <c r="F2" t="n">
         <v>0.2512352603199477</v>
@@ -1160,7 +1259,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.102x + -10893.998</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -1177,8 +1276,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>131.984</v>
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-131.984</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.92917e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.54600000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0.2541025803483765</v>
@@ -1203,7 +1311,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.632x + -11504.339</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -1220,8 +1328,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>129.28</v>
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-129.28</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.9212e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.687</v>
       </c>
       <c r="F4" t="n">
         <v>0.1400792209286618</v>
@@ -1246,7 +1363,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.953x + -11430.260</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -1263,8 +1380,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>124.1009999999999</v>
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-124.1009999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.91187e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.82899999999999</v>
       </c>
       <c r="F5" t="n">
         <v>0.09920623244385056</v>
@@ -1289,7 +1415,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.858x + -11224.706</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -1306,8 +1432,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>119.293</v>
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-119.293</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.90558e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.934</v>
       </c>
       <c r="F6" t="n">
         <v>0.3692688177840676</v>
@@ -1332,7 +1467,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.133x + -12214.074</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -1349,8 +1484,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>117.867</v>
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-117.867</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.90046e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.021</v>
       </c>
       <c r="F7" t="n">
         <v>0.2876184136939834</v>
@@ -1375,7 +1519,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.627x + -11820.217</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -1392,8 +1536,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>116.985</v>
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-116.985</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.89592e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.09099999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0.3206527290458294</v>
@@ -1418,7 +1571,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.062x + -11887.292</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -1435,8 +1588,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>113.1130000000001</v>
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-113.1130000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.89145e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.19</v>
       </c>
       <c r="F9" t="n">
         <v>0.2387408756064689</v>
@@ -1461,7 +1623,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.648x + -12030.072</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -1478,8 +1640,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>113.2769999999999</v>
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-113.2769999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.88963e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.23</v>
       </c>
       <c r="F10" t="n">
         <v>0.55146302771261</v>
@@ -1504,7 +1675,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.618x + -12366.105</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -1521,8 +1692,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>110.489</v>
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-110.489</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.88777e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.30500000000001</v>
       </c>
       <c r="F11" t="n">
         <v>0.6038148698054053</v>
@@ -1547,7 +1727,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.345x + -12585.917</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -1564,8 +1744,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="n">
-        <v>111.1540000000001</v>
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-111.1540000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.88503e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.361</v>
       </c>
       <c r="F12" t="n">
         <v>0.4339865350767734</v>
@@ -1590,7 +1779,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.522x + -12076.695</t>
         </is>
       </c>
       <c r="Y12" t="n">
@@ -1607,8 +1796,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" t="n">
-        <v>110.27</v>
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-110.27</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.88355e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.414</v>
       </c>
       <c r="F13" t="n">
         <v>0.3476471371410548</v>
@@ -1633,7 +1831,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.482x + -11945.455</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -1650,8 +1848,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="C14" t="n">
-        <v>107.432</v>
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-107.432</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.88254e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.48099999999999</v>
       </c>
       <c r="F14" t="n">
         <v>0.2703678246490247</v>
@@ -1676,7 +1883,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.217x + -12168.587</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -1693,8 +1900,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" t="n">
-        <v>106.785</v>
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-106.785</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.88131e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.52500000000001</v>
       </c>
       <c r="F15" t="n">
         <v>0.3628685771184439</v>
@@ -1719,7 +1935,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.633x + -12247.848</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -1736,8 +1952,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" t="n">
-        <v>106.9449999999999</v>
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-106.9449999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.87906e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.575</v>
       </c>
       <c r="F16" t="n">
         <v>0.3038978515465716</v>
@@ -1762,7 +1987,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.709x + -11721.623</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -1779,8 +2004,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" t="n">
-        <v>112.684</v>
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-112.684</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.87923e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.623</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1805,7 +2039,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.129x + -8707.147</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -1822,8 +2056,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="C18" t="n">
-        <v>102.746</v>
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-102.746</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.87619e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.688</v>
       </c>
       <c r="F18" t="n">
         <v>0.4190339336780965</v>
@@ -1848,7 +2091,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 29.935x + -12491.809</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -1865,8 +2108,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="C19" t="n">
-        <v>103.851</v>
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-103.851</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.87722e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.718</v>
       </c>
       <c r="F19" t="n">
         <v>0.2802140777179493</v>
@@ -1891,7 +2143,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 29.351x + -12118.932</t>
         </is>
       </c>
       <c r="Y19" t="n">
@@ -1908,8 +2160,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="n">
-        <v>103.498</v>
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-103.498</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.87617e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.75700000000001</v>
       </c>
       <c r="F20" t="n">
         <v>0.4864753798457531</v>
@@ -1934,7 +2195,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 30.174x + -12363.801</t>
         </is>
       </c>
       <c r="Y20" t="n">
@@ -1951,8 +2212,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="n">
-        <v>103.721</v>
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-103.721</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.87411e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.804</v>
       </c>
       <c r="F21" t="n">
         <v>0.04589902996738593</v>
@@ -1977,7 +2247,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.263x + -11432.831</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -1994,8 +2264,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="n">
-        <v>98.95100000000002</v>
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-98.95100000000002</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.87422e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.884</v>
       </c>
       <c r="F22" t="n">
         <v>0.4027869637479747</v>
@@ -2020,7 +2299,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 30.629x + -12330.557</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -2183,8 +2462,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>185.812</v>
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-185.812</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.86232e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.75</v>
       </c>
       <c r="F2" t="n">
         <v>0.3600212400616191</v>
@@ -2209,7 +2497,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 20.211x + -10616.009</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -2226,8 +2514,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>135.001</v>
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-135.001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.8313e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.64400000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0.22385227896093</v>
@@ -2252,7 +2549,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.443x + -12113.065</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -2269,8 +2566,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>126.095</v>
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-126.095</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.82244e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.857</v>
       </c>
       <c r="F4" t="n">
         <v>0.1607162132968337</v>
@@ -2295,7 +2601,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.189x + -11731.888</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -2312,8 +2618,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>117.0359999999999</v>
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-117.0359999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.81385e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.01300000000001</v>
       </c>
       <c r="F5" t="n">
         <v>0.4422891215339908</v>
@@ -2338,7 +2653,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.370x + -12691.811</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -2355,8 +2670,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>114.115</v>
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-114.115</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.80933e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.089</v>
       </c>
       <c r="F6" t="n">
         <v>0.6625664374199612</v>
@@ -2381,7 +2705,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.434x + -13581.757</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -2398,8 +2722,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>111.591</v>
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-111.591</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.8037e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.2</v>
       </c>
       <c r="F7" t="n">
         <v>0.5742009206833052</v>
@@ -2424,7 +2757,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.086x + -12742.011</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -2441,8 +2774,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>113.765</v>
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-113.765</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.79929e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.248</v>
       </c>
       <c r="F8" t="n">
         <v>0.2922844361609989</v>
@@ -2467,7 +2809,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.539x + -12321.753</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -2484,8 +2826,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>111.04</v>
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-111.04</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.79486e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.34</v>
       </c>
       <c r="F9" t="n">
         <v>0.2565641828460719</v>
@@ -2510,7 +2861,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.159x + -11994.225</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -2527,8 +2878,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>108.559</v>
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-108.559</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.79076e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.395</v>
       </c>
       <c r="F10" t="n">
         <v>0.5643059452032864</v>
@@ -2553,7 +2913,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.897x + -13193.131</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -2570,8 +2930,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>108.541</v>
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-108.541</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.78869e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.46299999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0.1837260412898271</v>
@@ -2596,7 +2965,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.677x + -11998.704</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -2613,8 +2982,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="n">
-        <v>106.826</v>
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-106.826</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.78439e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.51300000000001</v>
       </c>
       <c r="F12" t="n">
         <v>0.5118563139027209</v>
@@ -2639,7 +3017,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.372x + -12691.912</t>
         </is>
       </c>
       <c r="Y12" t="n">
@@ -2656,8 +3034,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" t="n">
-        <v>104.324</v>
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-104.324</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.78444e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.59099999999999</v>
       </c>
       <c r="F13" t="n">
         <v>0.229574198938836</v>
@@ -2682,7 +3069,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.118x + -11990.528</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -2699,8 +3086,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="C14" t="n">
-        <v>102.521</v>
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-102.521</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.78023e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.634</v>
       </c>
       <c r="F14" t="n">
         <v>0.434347803510383</v>
@@ -2725,7 +3121,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 29.840x + -13156.683</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -2742,8 +3138,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" t="n">
-        <v>102.628</v>
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-102.628</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.77878e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.67400000000001</v>
       </c>
       <c r="F15" t="n">
         <v>0.3581469239357987</v>
@@ -2768,7 +3173,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 29.519x + -12896.858</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -2785,8 +3190,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" t="n">
-        <v>99.24499999999995</v>
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-99.24499999999995</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.77814e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.73399999999999</v>
       </c>
       <c r="F16" t="n">
         <v>0.552221576868164</v>
@@ -2811,7 +3225,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 30.535x + -13256.571</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -2828,8 +3242,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" t="n">
-        <v>100.254</v>
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-100.254</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.77535e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.78400000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0.05290098768978027</v>
@@ -2854,7 +3277,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.088x + -12033.088</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -2871,8 +3294,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="C18" t="n">
-        <v>103.455</v>
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-103.455</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.77327e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.78700000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0.3624428162188722</v>
@@ -2897,7 +3329,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 29.585x + -12606.354</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -2914,8 +3346,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="C19" t="n">
-        <v>101.533</v>
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-101.533</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.77195e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.83799999999999</v>
       </c>
       <c r="F19" t="n">
         <v>0.4034514158358037</v>
@@ -2940,7 +3381,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 29.926x + -12652.627</t>
         </is>
       </c>
       <c r="Y19" t="n">
@@ -2957,8 +3398,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="n">
-        <v>99.31200000000001</v>
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-99.31200000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.77176e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.887</v>
       </c>
       <c r="F20" t="n">
         <v>0.6268528781091085</v>
@@ -2983,7 +3433,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 31.396x + -13197.963</t>
         </is>
       </c>
       <c r="Y20" t="n">
@@ -3000,8 +3450,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="n">
-        <v>99.928</v>
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-99.928</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.77071e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.929</v>
       </c>
       <c r="F21" t="n">
         <v>0.3365109060421372</v>
@@ -3026,7 +3485,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 29.963x + -12456.513</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -3043,8 +3502,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="n">
-        <v>97.21699999999998</v>
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-97.21699999999998</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.76954e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.98399999999999</v>
       </c>
       <c r="F22" t="n">
         <v>0.4727542272050645</v>
@@ -3069,7 +3537,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 31.109x + -12847.917</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -3232,8 +3700,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>380.9300000000001</v>
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-380.9300000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.18192e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.95399999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.2486354225527059</v>
@@ -3258,7 +3735,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 11.399x + -5628.870</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -3275,8 +3752,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>280.449</v>
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-280.449</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.16511e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.804</v>
       </c>
       <c r="F3" t="n">
         <v>0.3106808278072673</v>
@@ -3301,7 +3787,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 15.315x + -6739.300</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -3318,8 +3804,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>238.361</v>
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-238.361</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.11561e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.575</v>
       </c>
       <c r="F4" t="n">
         <v>0.03977054612979009</v>
@@ -3344,7 +3839,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 17.593x + -7506.888</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -3361,8 +3856,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>215.98</v>
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-215.98</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.0739e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.045</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -3387,7 +3891,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 18.122x + -7557.433</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -3404,8 +3908,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>192.5579999999999</v>
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-192.5579999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.04238e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.39100000000001</v>
       </c>
       <c r="F6" t="n">
         <v>0.4033259512610427</v>
@@ -3430,7 +3943,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.410x + -8910.350</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -3447,8 +3960,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>180.6729999999999</v>
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-180.6729999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.0168e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.64</v>
       </c>
       <c r="F7" t="n">
         <v>0.4485339825041705</v>
@@ -3473,7 +3995,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.443x + -9214.317</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -3490,8 +4012,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>171.162</v>
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-171.162</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.99736e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.855</v>
       </c>
       <c r="F8" t="n">
         <v>0.2243178878806035</v>
@@ -3516,7 +4047,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.207x + -9385.325</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -3533,8 +4064,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>162.43</v>
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-162.43</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.98304e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.03400000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0.4282541859250891</v>
@@ -3559,7 +4099,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.412x + -9752.118</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -3576,8 +4116,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>162.006</v>
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-162.006</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.96941e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.175</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -3602,7 +4151,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.041x + -8582.619</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -3619,8 +4168,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>149.661</v>
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-149.661</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.95913e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.34399999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0.1837973103988853</v>
@@ -3645,7 +4203,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.189x + -9770.345</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -3808,8 +4366,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>302.482</v>
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-302.482</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.13678e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.658</v>
       </c>
       <c r="F2" t="n">
         <v>0.2058765328604114</v>
@@ -3834,7 +4401,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 14.019x + -7342.529</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -3851,8 +4418,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>193.322</v>
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-193.322</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.01041e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.495</v>
       </c>
       <c r="F3" t="n">
         <v>0.4803181678963104</v>
@@ -3877,7 +4453,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 20.640x + -10390.833</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -3894,8 +4470,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>162.029</v>
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-162.029</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.9619e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.06100000000001</v>
       </c>
       <c r="F4" t="n">
         <v>0.3843534950201712</v>
@@ -3920,7 +4505,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.539x + -11150.890</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -3937,8 +4522,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>149.549</v>
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-149.549</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.93403e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.325</v>
       </c>
       <c r="F5" t="n">
         <v>0.2083235471319146</v>
@@ -3963,7 +4557,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.221x + -11336.898</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -3980,8 +4574,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>137.68</v>
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-137.68</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.91834e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.526</v>
       </c>
       <c r="F6" t="n">
         <v>0.6785141872503018</v>
@@ -4006,7 +4609,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.442x + -12337.346</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -4023,8 +4626,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>132.2180000000001</v>
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-132.2180000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.90634e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.682</v>
       </c>
       <c r="F7" t="n">
         <v>0.409746399120797</v>
@@ -4049,7 +4661,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.045x + -11976.821</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -4066,8 +4678,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>126.747</v>
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-126.747</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.89732e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.821</v>
       </c>
       <c r="F8" t="n">
         <v>0.3081169508986153</v>
@@ -4092,7 +4713,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.855x + -11729.212</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -4109,8 +4730,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>126.2839999999999</v>
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-126.2839999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.89073e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.89700000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0.3630077700262435</v>
@@ -4135,7 +4765,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.341x + -11836.717</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -4152,8 +4782,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>123.458</v>
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-123.458</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.88377e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.008</v>
       </c>
       <c r="F10" t="n">
         <v>0.0006176672374678497</v>
@@ -4178,7 +4817,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.219x + -11153.355</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -4195,8 +4834,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>119.3849999999999</v>
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-119.3849999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.87984e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.084</v>
       </c>
       <c r="F11" t="n">
         <v>0.1770090710500854</v>
@@ -4221,7 +4869,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.858x + -11838.617</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -4238,8 +4886,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="n">
-        <v>114.622</v>
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-114.622</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.87379e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.184</v>
       </c>
       <c r="F12" t="n">
         <v>0.2567083334348363</v>
@@ -4264,7 +4921,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.629x + -12099.651</t>
         </is>
       </c>
       <c r="Y12" t="n">
@@ -4281,8 +4938,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" t="n">
-        <v>115.45</v>
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-115.45</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.87175e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.221</v>
       </c>
       <c r="F13" t="n">
         <v>0.3974558107605298</v>
@@ -4307,7 +4973,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.811x + -12075.262</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -4324,8 +4990,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="C14" t="n">
-        <v>112.47</v>
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-112.47</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.86733e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.307</v>
       </c>
       <c r="F14" t="n">
         <v>0.387778184348667</v>
@@ -4350,7 +5025,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.666x + -11892.427</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -4367,8 +5042,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" t="n">
-        <v>111.931</v>
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-111.931</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.86526e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.364</v>
       </c>
       <c r="F15" t="n">
         <v>0.07897212754286122</v>
@@ -4393,7 +5077,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.820x + -11390.898</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -4410,8 +5094,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" t="n">
-        <v>109.052</v>
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-109.052</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.8616e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.419</v>
       </c>
       <c r="F16" t="n">
         <v>0.3183689671825659</v>
@@ -4436,7 +5129,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.880x + -12253.841</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -4453,8 +5146,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" t="n">
-        <v>108.99</v>
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-108.99</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.85864e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.467</v>
       </c>
       <c r="F17" t="n">
         <v>0.4281340566556781</v>
@@ -4479,7 +5181,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.907x + -12158.414</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -4496,8 +5198,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="C18" t="n">
-        <v>110.14</v>
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-110.14</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.85582e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.497</v>
       </c>
       <c r="F18" t="n">
         <v>0.2587208054347807</v>
@@ -4522,7 +5233,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.725x + -11970.203</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -4539,8 +5250,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="C19" t="n">
-        <v>104.009</v>
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-104.009</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.85464e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.607</v>
       </c>
       <c r="F19" t="n">
         <v>0.2543339516804881</v>
@@ -4565,7 +5285,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.939x + -11512.475</t>
         </is>
       </c>
       <c r="Y19" t="n">
@@ -4582,8 +5302,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="n">
-        <v>106.473</v>
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-106.473</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.85318e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.62</v>
       </c>
       <c r="F20" t="n">
         <v>0.3387417122810814</v>
@@ -4608,7 +5337,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.444x + -11638.896</t>
         </is>
       </c>
       <c r="Y20" t="n">
@@ -4625,8 +5354,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="n">
-        <v>103.8749999999999</v>
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-103.8749999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.85219e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.67700000000001</v>
       </c>
       <c r="F21" t="n">
         <v>0.2420241148803841</v>
@@ -4651,7 +5389,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.441x + -11981.094</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -4668,8 +5406,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="n">
-        <v>101.895</v>
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-101.895</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.85043e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.724</v>
       </c>
       <c r="F22" t="n">
         <v>0.3958316044425483</v>
@@ -4694,7 +5441,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 30.299x + -12706.022</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -4857,8 +5604,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>415.287</v>
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-415.287</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.33264e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.247</v>
       </c>
       <c r="F2" t="n">
         <v>0.1510618611807043</v>
@@ -4883,7 +5639,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 10.022x + -4753.425</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -4900,8 +5656,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>300.403</v>
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-300.403</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.29263e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.348</v>
       </c>
       <c r="F3" t="n">
         <v>0.2952116980141143</v>
@@ -4926,7 +5691,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 14.004x + -6004.551</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -4943,8 +5708,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>254.292</v>
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-254.292</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.22555e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.224</v>
       </c>
       <c r="F4" t="n">
         <v>0.3234001837650405</v>
@@ -4969,7 +5743,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 16.384x + -6831.824</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -4986,8 +5760,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>223.92</v>
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-223.92</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.17461e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.798</v>
       </c>
       <c r="F5" t="n">
         <v>0.2374391016058989</v>
@@ -5012,7 +5795,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 18.175x + -7452.966</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -5029,8 +5812,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>203.7020000000001</v>
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-203.7020000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.13556e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.173</v>
       </c>
       <c r="F6" t="n">
         <v>0.3140501217841745</v>
@@ -5055,7 +5847,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 20.119x + -8163.711</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -5072,8 +5864,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>189.032</v>
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-189.032</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.10572e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.495</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -5098,7 +5899,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 20.467x + -8138.085</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -5115,8 +5916,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>177.703</v>
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-177.703</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.08217e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.73</v>
       </c>
       <c r="F8" t="n">
         <v>0.1537407469890794</v>
@@ -5141,7 +5951,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.791x + -8556.790</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -5158,8 +5968,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>169.3899999999999</v>
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-169.3899999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.06404e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.94</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5184,7 +6003,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.106x + -8532.472</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -5201,8 +6020,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>163.521</v>
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-163.521</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.04952e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.096</v>
       </c>
       <c r="F10" t="n">
         <v>0.03565944642924405</v>
@@ -5227,7 +6055,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.508x + -8558.562</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -5244,8 +6072,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>158.2640000000001</v>
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-158.2640000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.03864e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.25</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -5270,7 +6107,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.632x + -8073.836</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -5433,8 +6270,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>261.571</v>
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-261.571</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.15126e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.19499999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.4057070833483696</v>
@@ -5459,7 +6305,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 15.482x + -7987.922</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -5476,8 +6322,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>177.236</v>
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-177.236</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.04695e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.729</v>
       </c>
       <c r="F3" t="n">
         <v>0.6238346451875197</v>
@@ -5502,7 +6357,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.303x + -10453.379</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -5519,8 +6374,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>157.1960000000001</v>
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-157.1960000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.00868e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.166</v>
       </c>
       <c r="F4" t="n">
         <v>0.06818604703665022</v>
@@ -5545,7 +6409,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.580x + -10342.095</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -5562,8 +6426,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>145.2930000000001</v>
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-145.2930000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.98863e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.399</v>
       </c>
       <c r="F5" t="n">
         <v>0.1110759864314674</v>
@@ -5588,7 +6461,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.514x + -10665.842</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -5605,8 +6478,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>136.829</v>
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-136.829</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.97582e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.568</v>
       </c>
       <c r="F6" t="n">
         <v>0.241685382853705</v>
@@ -5631,7 +6513,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.679x + -11109.854</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -5648,8 +6530,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>129.434</v>
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-129.434</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.96574e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.73099999999999</v>
       </c>
       <c r="F7" t="n">
         <v>0.4195948978627454</v>
@@ -5674,7 +6565,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.693x + -11470.745</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -5691,8 +6582,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>129.434</v>
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-129.434</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.95844e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.81999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0.05522112977547446</v>
@@ -5717,7 +6617,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.829x + -10899.961</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -5734,8 +6634,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>122.062</v>
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-122.062</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.9517e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.932</v>
       </c>
       <c r="F9" t="n">
         <v>0.6766973606147526</v>
@@ -5760,7 +6669,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.740x + -12184.708</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -5777,8 +6686,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>121.4230000000001</v>
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-121.4230000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.94842e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.015</v>
       </c>
       <c r="F10" t="n">
         <v>0.1889606284772116</v>
@@ -5803,7 +6721,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.126x + -11277.142</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -5820,8 +6738,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>118.37</v>
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-118.37</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.94245e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.111</v>
       </c>
       <c r="F11" t="n">
         <v>0.4119672874672737</v>
@@ -5846,7 +6773,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.212x + -11202.344</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -5863,8 +6790,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="n">
-        <v>117.152</v>
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-117.152</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.93913e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.166</v>
       </c>
       <c r="F12" t="n">
         <v>0.3924705789042351</v>
@@ -5889,7 +6825,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.012x + -11467.553</t>
         </is>
       </c>
       <c r="Y12" t="n">
@@ -5906,8 +6842,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" t="n">
-        <v>114.402</v>
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-114.402</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.93662e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.233</v>
       </c>
       <c r="F13" t="n">
         <v>0.5272546335985324</v>
@@ -5932,7 +6877,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.843x + -11745.343</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -5949,8 +6894,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="C14" t="n">
-        <v>114.677</v>
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-114.677</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.93307e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.288</v>
       </c>
       <c r="F14" t="n">
         <v>0.2596611031854913</v>
@@ -5975,7 +6929,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.416x + -11435.601</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -5992,8 +6946,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" t="n">
-        <v>109.143</v>
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-109.143</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.93089e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.396</v>
       </c>
       <c r="F15" t="n">
         <v>0.2126113263100747</v>
@@ -6018,7 +6981,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.727x + -11468.043</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -6035,8 +6998,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" t="n">
-        <v>106.725</v>
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-106.725</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.92741e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.45699999999999</v>
       </c>
       <c r="F16" t="n">
         <v>0.3853431843905843</v>
@@ -6061,7 +7033,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.433x + -11676.233</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -6078,8 +7050,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" t="n">
-        <v>108.109</v>
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-108.109</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.92711e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.498</v>
       </c>
       <c r="F17" t="n">
         <v>0.3312520345965826</v>
@@ -6104,7 +7085,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.257x + -11042.483</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -6121,8 +7102,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="C18" t="n">
-        <v>115.366</v>
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-115.366</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.92538e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.541</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -6147,7 +7137,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 19.702x + -8057.979</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -6164,8 +7154,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="C19" t="n">
-        <v>103.657</v>
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-103.657</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.92352e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.61499999999999</v>
       </c>
       <c r="F19" t="n">
         <v>0.6011164811750711</v>
@@ -6190,7 +7189,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.465x + -11809.416</t>
         </is>
       </c>
       <c r="Y19" t="n">
@@ -6207,8 +7206,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="n">
-        <v>103.911</v>
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-103.911</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.92278e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.658</v>
       </c>
       <c r="F20" t="n">
         <v>0.4060632175973847</v>
@@ -6233,7 +7241,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.233x + -11595.304</t>
         </is>
       </c>
       <c r="Y20" t="n">
@@ -6250,8 +7258,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="n">
-        <v>108.898</v>
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-108.898</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.92051e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.7</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -6276,7 +7293,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.049x + -9258.846</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -6293,8 +7310,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="n">
-        <v>102.782</v>
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-102.782</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.92126e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.748</v>
       </c>
       <c r="F22" t="n">
         <v>0.3460987541429899</v>
@@ -6319,7 +7345,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.659x + -11563.321</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -6482,8 +7508,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>393.725</v>
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-393.725</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.35159e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.379</v>
       </c>
       <c r="F2" t="n">
         <v>0.3355328595150014</v>
@@ -6508,7 +7543,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 10.542x + -5076.239</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -6525,8 +7560,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>278.3680000000001</v>
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-278.3680000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.28991e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.65600000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0.1603454460234977</v>
@@ -6551,7 +7595,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 14.678x + -6259.777</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -6568,8 +7612,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>227.635</v>
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-227.635</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.21697e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.571</v>
       </c>
       <c r="F4" t="n">
         <v>0.6273173030063035</v>
@@ -6594,7 +7647,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 18.208x + -7592.345</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -6611,8 +7664,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>198.654</v>
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-198.654</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.16364e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.12</v>
       </c>
       <c r="F5" t="n">
         <v>0.4251616491959277</v>
@@ -6637,7 +7699,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 19.918x + -8153.215</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -6654,8 +7716,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>181.672</v>
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-181.672</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.12615e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.468</v>
       </c>
       <c r="F6" t="n">
         <v>0.2104298985136608</v>
@@ -6680,7 +7751,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.281x + -8592.884</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -6697,8 +7768,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>168.712</v>
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-168.712</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.09917e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.755</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -6723,7 +7803,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.657x + -8593.149</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -6740,8 +7820,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>158.627</v>
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-158.627</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.07858e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.965</v>
       </c>
       <c r="F8" t="n">
         <v>0.1512018233207274</v>
@@ -6766,7 +7855,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.704x + -8896.116</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -6783,8 +7872,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>152.704</v>
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-152.704</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.06218e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.107</v>
       </c>
       <c r="F9" t="n">
         <v>0.360155359749003</v>
@@ -6809,7 +7907,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.138x + -9358.576</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -6826,8 +7924,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>145.009</v>
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-145.009</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.05109e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.29000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>0.1289736245424689</v>
@@ -6852,7 +7959,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.381x + -8897.997</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -6869,8 +7976,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>140.537</v>
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-140.537</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.04068e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.393</v>
       </c>
       <c r="F11" t="n">
         <v>0.2649344826764415</v>
@@ -6895,7 +8011,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.351x + -9576.223</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -7058,8 +8174,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>248.224</v>
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-248.224</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.16062e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.358</v>
       </c>
       <c r="F2" t="n">
         <v>0.1533710651901444</v>
@@ -7084,7 +8209,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 15.651x + -8041.755</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -7101,8 +8226,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>174.905</v>
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-174.905</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.06331e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.718</v>
       </c>
       <c r="F3" t="n">
         <v>0.167238872282497</v>
@@ -7127,7 +8261,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 20.238x + -9910.927</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -7144,8 +8278,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>151.73</v>
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-151.73</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.02365e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.161</v>
       </c>
       <c r="F4" t="n">
         <v>0.118683459369862</v>
@@ -7170,7 +8313,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.874x + -10531.451</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -7187,8 +8330,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>140.738</v>
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-140.738</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.00137e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.40600000000001</v>
       </c>
       <c r="F5" t="n">
         <v>0.4456917023317447</v>
@@ -7213,7 +8365,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.873x + -10873.962</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -7230,8 +8382,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>133.039</v>
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-133.039</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.98912e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.601</v>
       </c>
       <c r="F6" t="n">
         <v>0.1273861864446729</v>
@@ -7256,7 +8417,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.296x + -10421.739</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -7273,8 +8434,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>127.572</v>
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-127.572</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.97741e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.742</v>
       </c>
       <c r="F7" t="n">
         <v>0.05249041822420263</v>
@@ -7299,7 +8469,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.202x + -10718.833</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -7316,8 +8486,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>124.5119999999999</v>
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-124.5119999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.97057e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.855</v>
       </c>
       <c r="F8" t="n">
         <v>0.1700647641337131</v>
@@ -7342,7 +8521,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.800x + -10854.508</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -7359,8 +8538,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>118.5140000000001</v>
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-118.5140000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.96572e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.97499999999999</v>
       </c>
       <c r="F9" t="n">
         <v>0.5752312257961332</v>
@@ -7385,7 +8573,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.141x + -11833.508</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -7402,8 +8590,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>119.23</v>
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-119.23</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.95921e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.054</v>
       </c>
       <c r="F10" t="n">
         <v>0.2813013731631299</v>
@@ -7428,7 +8625,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.099x + -11191.991</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -7445,8 +8642,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>115.397</v>
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-115.397</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.95583e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.151</v>
       </c>
       <c r="F11" t="n">
         <v>0.09319130765298622</v>
@@ -7471,7 +8677,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.179x + -11088.938</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -7488,8 +8694,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="n">
-        <v>115.532</v>
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-115.532</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.95296e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.20099999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0.3599413389630866</v>
@@ -7514,7 +8729,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 26.189x + -11435.848</t>
         </is>
       </c>
       <c r="Y12" t="n">
@@ -7531,8 +8746,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" t="n">
-        <v>111.609</v>
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-111.609</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.94949e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.303</v>
       </c>
       <c r="F13" t="n">
         <v>0.1708077574308895</v>
@@ -7557,7 +8781,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.829x + -11145.944</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -7574,8 +8798,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="C14" t="n">
-        <v>105.909</v>
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-105.909</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.94769e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.392</v>
       </c>
       <c r="F14" t="n">
         <v>0.5627007889638423</v>
@@ -7600,7 +8833,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.565x + -11825.718</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -7617,8 +8850,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" t="n">
-        <v>109.815</v>
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-109.815</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.94521e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.419</v>
       </c>
       <c r="F15" t="n">
         <v>0.2204768402855436</v>
@@ -7643,7 +8885,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 25.916x + -10963.163</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -7660,8 +8902,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" t="n">
-        <v>106.6619999999999</v>
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-106.6619999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.94213e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.486</v>
       </c>
       <c r="F16" t="n">
         <v>0.4084886904978213</v>
@@ -7686,7 +8937,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.726x + -11663.678</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -7703,8 +8954,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" t="n">
-        <v>105.321</v>
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-105.321</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.94177e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.547</v>
       </c>
       <c r="F17" t="n">
         <v>0.3421720146806932</v>
@@ -7729,7 +8989,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.323x + -11367.490</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -7746,8 +9006,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="C18" t="n">
-        <v>104.587</v>
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-104.587</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.93998e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.598</v>
       </c>
       <c r="F18" t="n">
         <v>0.3530225523922933</v>
@@ -7772,7 +9041,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.356x + -11271.295</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -7789,8 +9058,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="C19" t="n">
-        <v>102.743</v>
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-102.743</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.93884e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.655</v>
       </c>
       <c r="F19" t="n">
         <v>0.50489475641645</v>
@@ -7815,7 +9093,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.334x + -11585.463</t>
         </is>
       </c>
       <c r="Y19" t="n">
@@ -7832,8 +9110,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="n">
-        <v>101.33</v>
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-101.33</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.93564e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.729</v>
       </c>
       <c r="F20" t="n">
         <v>0.2225979619249348</v>
@@ -7858,7 +9145,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.440x + -11087.491</t>
         </is>
       </c>
       <c r="Y20" t="n">
@@ -7875,8 +9162,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="n">
-        <v>100.533</v>
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-100.533</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.93534e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.773</v>
       </c>
       <c r="F21" t="n">
         <v>0.08864719402297366</v>
@@ -7901,7 +9197,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.784x + -11127.632</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -7918,8 +9214,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="n">
-        <v>99.27299999999997</v>
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-99.27299999999997</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.93414e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.828</v>
       </c>
       <c r="F22" t="n">
         <v>0.2331695885852351</v>
@@ -7944,7 +9249,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 28.537x + -11332.965</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -8107,8 +9412,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="n">
-        <v>375.6270000000001</v>
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-375.6270000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.22643e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.02800000000001</v>
       </c>
       <c r="F2" t="n">
         <v>0.3090341367424562</v>
@@ -8133,7 +9447,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 11.197x + -5404.923</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -8150,8 +9464,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
-        <v>250.0069999999999</v>
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-250.0069999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.16105e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.399</v>
       </c>
       <c r="F3" t="n">
         <v>0.2408363026047992</v>
@@ -8176,7 +9499,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 16.638x + -7005.263</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -8193,8 +9516,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="n">
-        <v>203.114</v>
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-203.114</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.09133e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.236</v>
       </c>
       <c r="F4" t="n">
         <v>0.3624615440235107</v>
@@ -8219,7 +9551,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 20.052x + -8202.643</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -8236,8 +9568,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
-        <v>178.4640000000001</v>
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-178.4640000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.04231e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.7</v>
       </c>
       <c r="F5" t="n">
         <v>0.06844359911676329</v>
@@ -8262,7 +9603,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 21.874x + -8793.680</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -8279,8 +9620,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="n">
-        <v>157.437</v>
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-157.437</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.01126e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.06100000000001</v>
       </c>
       <c r="F6" t="n">
         <v>0.1555675523765995</v>
@@ -8305,7 +9655,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.747x + -9406.969</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -8322,8 +9672,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="n">
-        <v>150.675</v>
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-150.675</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.99036e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.277</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -8348,7 +9707,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.481x + -8700.101</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -8365,8 +9724,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="n">
-        <v>146.104</v>
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-146.104</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.97612e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.42100000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0.0005794371424074043</v>
@@ -8391,7 +9759,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 22.976x + -8746.054</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -8408,8 +9776,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
-        <v>137.07</v>
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-137.07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.9661e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.605</v>
       </c>
       <c r="F9" t="n">
         <v>0.03656112523676364</v>
@@ -8434,7 +9811,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 23.548x + -8815.579</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -8451,8 +9828,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="n">
-        <v>130.099</v>
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-130.099</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.95805e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.70999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>0.8745145247774707</v>
@@ -8477,7 +9863,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 27.703x + -10328.277</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -8494,8 +9880,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="n">
-        <v>129.637</v>
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-129.637</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.95183e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.83199999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0.0576374564442183</v>
@@ -8520,7 +9915,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>y = 24.131x + -8761.432</t>
         </is>
       </c>
       <c r="Y11" t="n">

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -588,19 +588,19 @@
       <c r="K2" t="n">
         <v>87.15972788560832</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 20.156x + -10528.520</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-10528.52042150222</v>
       </c>
       <c r="Y2" t="n">
         <v>460.6808130661087</v>
       </c>
       <c r="Z2" t="n">
-        <v>190601270.4768265</v>
+        <v>192.894</v>
       </c>
       <c r="AA2" t="n">
         <v>4.644509464842502e-07</v>
@@ -640,19 +640,19 @@
       <c r="K3" t="n">
         <v>87.52229951283391</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 23.110x + -11894.280</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-11894.28030228045</v>
       </c>
       <c r="Y3" t="n">
         <v>453.9903085353594</v>
       </c>
       <c r="Z3" t="n">
-        <v>254353603.7316092</v>
+        <v>167.724</v>
       </c>
       <c r="AA3" t="n">
         <v>4.389297176198378e-07</v>
@@ -692,19 +692,19 @@
       <c r="K4" t="n">
         <v>87.57404826736281</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 23.604x + -11916.574</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11916.57385893646</v>
       </c>
       <c r="Y4" t="n">
         <v>447.7894253377514</v>
       </c>
       <c r="Z4" t="n">
-        <v>244588629.4254274</v>
+        <v>156.5880000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>4.242214339888221e-07</v>
@@ -744,19 +744,19 @@
       <c r="K5" t="n">
         <v>87.6177591529958</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 24.037x + -11929.575</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-11929.57493990915</v>
       </c>
       <c r="Y5" t="n">
         <v>441.8343123082274</v>
       </c>
       <c r="Z5" t="n">
-        <v>181461776.0191447</v>
+        <v>146.3920000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>4.12948038816336e-07</v>
@@ -796,19 +796,19 @@
       <c r="K6" t="n">
         <v>87.80851140963313</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 26.132x + -12825.707</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-12825.70675385108</v>
       </c>
       <c r="Y6" t="n">
         <v>435.9848026626581</v>
       </c>
       <c r="Z6" t="n">
-        <v>119033721.8569947</v>
+        <v>140.352</v>
       </c>
       <c r="AA6" t="n">
         <v>4.054320414649394e-07</v>
@@ -848,19 +848,19 @@
       <c r="K7" t="n">
         <v>87.65940662234762</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 24.466x + -11753.455</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11753.45510055545</v>
       </c>
       <c r="Y7" t="n">
         <v>430.2772136153836</v>
       </c>
       <c r="Z7" t="n">
-        <v>352070846.4447082</v>
+        <v>137.215</v>
       </c>
       <c r="AA7" t="n">
         <v>3.984371058527456e-07</v>
@@ -900,19 +900,19 @@
       <c r="K8" t="n">
         <v>87.82088398768474</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 26.280x + -12489.765</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12489.76538931573</v>
       </c>
       <c r="Y8" t="n">
         <v>424.9842492674028</v>
       </c>
       <c r="Z8" t="n">
-        <v>116039973.4921873</v>
+        <v>133.602</v>
       </c>
       <c r="AA8" t="n">
         <v>3.931125257048022e-07</v>
@@ -952,19 +952,19 @@
       <c r="K9" t="n">
         <v>87.74775265988983</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 25.426x + -11877.666</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11877.6660878247</v>
       </c>
       <c r="Y9" t="n">
         <v>420.0882347847049</v>
       </c>
       <c r="Z9" t="n">
-        <v>114679807.782176</v>
+        <v>131.738</v>
       </c>
       <c r="AA9" t="n">
         <v>3.883145652609311e-07</v>
@@ -1004,19 +1004,19 @@
       <c r="K10" t="n">
         <v>87.83208426718163</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 26.416x + -12204.342</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-12204.34182404864</v>
       </c>
       <c r="Y10" t="n">
         <v>415.6446530382878</v>
       </c>
       <c r="Z10" t="n">
-        <v>309683257.2436185</v>
+        <v>128.581</v>
       </c>
       <c r="AA10" t="n">
         <v>3.840786656903262e-07</v>
@@ -1056,19 +1056,19 @@
       <c r="K11" t="n">
         <v>87.88271007747976</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 27.049x + -12358.873</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-12358.87300405674</v>
       </c>
       <c r="Y11" t="n">
         <v>411.6109132545095</v>
       </c>
       <c r="Z11" t="n">
-        <v>336354412.5253681</v>
+        <v>124.093</v>
       </c>
       <c r="AA11" t="n">
         <v>3.798725309185535e-07</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1254,19 +1254,19 @@
       <c r="K2" t="n">
         <v>87.2868729892753</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 21.102x + -10893.998</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-10893.99816159297</v>
       </c>
       <c r="Y2" t="n">
         <v>447.1435381167894</v>
       </c>
       <c r="Z2" t="n">
-        <v>248521665.1200158</v>
+        <v>152.723</v>
       </c>
       <c r="AA2" t="n">
         <v>4.527610517887826e-07</v>
@@ -1306,19 +1306,19 @@
       <c r="K3" t="n">
         <v>87.5769512123931</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 23.632x + -11504.339</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-11504.33945863282</v>
       </c>
       <c r="Y3" t="n">
         <v>433.2531990944827</v>
       </c>
       <c r="Z3" t="n">
-        <v>826482560.508213</v>
+        <v>131.984</v>
       </c>
       <c r="AA3" t="n">
         <v>4.243705039226735e-07</v>
@@ -1358,19 +1358,19 @@
       <c r="K4" t="n">
         <v>87.60942894374718</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 23.953x + -11430.260</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11430.26001686559</v>
       </c>
       <c r="Y4" t="n">
         <v>427.8721024992129</v>
       </c>
       <c r="Z4" t="n">
-        <v>175318940.6701232</v>
+        <v>129.28</v>
       </c>
       <c r="AA4" t="n">
         <v>4.159682414055889e-07</v>
@@ -1410,19 +1410,19 @@
       <c r="K5" t="n">
         <v>87.5998281694382</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 23.858x + -11224.706</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-11224.70583769813</v>
       </c>
       <c r="Y5" t="n">
         <v>423.6562047663102</v>
       </c>
       <c r="Z5" t="n">
-        <v>346651457.6429015</v>
+        <v>124.1009999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>4.087172028732938e-07</v>
@@ -1462,19 +1462,19 @@
       <c r="K6" t="n">
         <v>87.80859278634296</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 26.133x + -12214.074</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-12214.07350323225</v>
       </c>
       <c r="Y6" t="n">
         <v>419.4514387968316</v>
       </c>
       <c r="Z6" t="n">
-        <v>114790085.4256744</v>
+        <v>119.293</v>
       </c>
       <c r="AA6" t="n">
         <v>4.036382757990266e-07</v>
@@ -1514,19 +1514,19 @@
       <c r="K7" t="n">
         <v>87.76536653264944</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 25.627x + -11820.217</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11820.21700253824</v>
       </c>
       <c r="Y7" t="n">
         <v>415.2260026280111</v>
       </c>
       <c r="Z7" t="n">
-        <v>175938969.3848063</v>
+        <v>117.867</v>
       </c>
       <c r="AA7" t="n">
         <v>3.996979035424695e-07</v>
@@ -1566,19 +1566,19 @@
       <c r="K8" t="n">
         <v>87.80262087592632</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 26.062x + -11887.292</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11887.29217957252</v>
       </c>
       <c r="Y8" t="n">
         <v>411.1281362983607</v>
       </c>
       <c r="Z8" t="n">
-        <v>448424714.3112966</v>
+        <v>116.985</v>
       </c>
       <c r="AA8" t="n">
         <v>3.9640601027699e-07</v>
@@ -1618,19 +1618,19 @@
       <c r="K9" t="n">
         <v>87.85089048505542</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 26.648x + -12030.072</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12030.07192896979</v>
       </c>
       <c r="Y9" t="n">
         <v>407.3281667431311</v>
       </c>
       <c r="Z9" t="n">
-        <v>222657263.1626075</v>
+        <v>113.1130000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>3.922137922553009e-07</v>
@@ -1670,19 +1670,19 @@
       <c r="K10" t="n">
         <v>87.92629413956762</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 27.618x + -12366.105</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-12366.10545753141</v>
       </c>
       <c r="Y10" t="n">
         <v>403.7111005908142</v>
       </c>
       <c r="Z10" t="n">
-        <v>109990427.2364046</v>
+        <v>113.2769999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>3.904469143793302e-07</v>
@@ -1722,19 +1722,19 @@
       <c r="K11" t="n">
         <v>87.97949672654772</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 28.345x + -12585.917</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-12585.91718424231</v>
       </c>
       <c r="Y11" t="n">
         <v>400.2978906122345</v>
       </c>
       <c r="Z11" t="n">
-        <v>175910043.9011849</v>
+        <v>110.489</v>
       </c>
       <c r="AA11" t="n">
         <v>3.877393003707262e-07</v>
@@ -1774,19 +1774,19 @@
       <c r="K12" t="n">
         <v>87.91906736815051</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 27.522x + -12076.695</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-12076.69488488927</v>
       </c>
       <c r="Y12" t="n">
         <v>397.0421710001932</v>
       </c>
       <c r="Z12" t="n">
-        <v>432892730.2027784</v>
+        <v>111.1540000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>3.854281908457652e-07</v>
@@ -1826,19 +1826,19 @@
       <c r="K13" t="n">
         <v>87.91606963940927</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 27.482x + -11945.455</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11945.45472151515</v>
       </c>
       <c r="Y13" t="n">
         <v>393.8312251500885</v>
       </c>
       <c r="Z13" t="n">
-        <v>214386918.522717</v>
+        <v>110.27</v>
       </c>
       <c r="AA13" t="n">
         <v>3.83453242085289e-07</v>
@@ -1878,19 +1878,19 @@
       <c r="K14" t="n">
         <v>87.97033293113847</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 28.217x + -12168.587</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-12168.58682462352</v>
       </c>
       <c r="Y14" t="n">
         <v>390.6896074290457</v>
       </c>
       <c r="Z14" t="n">
-        <v>212840888.1988895</v>
+        <v>107.432</v>
       </c>
       <c r="AA14" t="n">
         <v>3.812314796101391e-07</v>
@@ -1930,19 +1930,19 @@
       <c r="K15" t="n">
         <v>87.99980391079097</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 28.633x + -12247.848</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-12247.84783957728</v>
       </c>
       <c r="Y15" t="n">
         <v>387.6458344404541</v>
       </c>
       <c r="Z15" t="n">
-        <v>211057674.0037495</v>
+        <v>106.785</v>
       </c>
       <c r="AA15" t="n">
         <v>3.795525456519262e-07</v>
@@ -1982,19 +1982,19 @@
       <c r="K16" t="n">
         <v>87.93312207283692</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 27.709x + -11721.623</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11721.62250437071</v>
       </c>
       <c r="Y16" t="n">
         <v>384.6164933954831</v>
       </c>
       <c r="Z16" t="n">
-        <v>314338859.8930665</v>
+        <v>106.9449999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>3.776512885782103e-07</v>
@@ -2034,19 +2034,19 @@
       <c r="K17" t="n">
         <v>87.29025771961543</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 21.129x + -8707.147</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-8707.14723446308</v>
       </c>
       <c r="Y17" t="n">
         <v>381.5022735022956</v>
       </c>
       <c r="Z17" t="n">
-        <v>159568288.1963896</v>
+        <v>112.684</v>
       </c>
       <c r="AA17" t="n">
         <v>3.761299651783017e-07</v>
@@ -2086,19 +2086,19 @@
       <c r="K18" t="n">
         <v>88.08667786806856</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 29.935x + -12491.809</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-12491.80891613518</v>
       </c>
       <c r="Y18" t="n">
         <v>378.491303530022</v>
       </c>
       <c r="Z18" t="n">
-        <v>411653892.8842936</v>
+        <v>102.746</v>
       </c>
       <c r="AA18" t="n">
         <v>3.737574662623318e-07</v>
@@ -2138,19 +2138,19 @@
       <c r="K19" t="n">
         <v>88.04864330120701</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 29.351x + -12118.932</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-12118.93204433167</v>
       </c>
       <c r="Y19" t="n">
         <v>375.4657874272673</v>
       </c>
       <c r="Z19" t="n">
-        <v>510651316.4201289</v>
+        <v>103.851</v>
       </c>
       <c r="AA19" t="n">
         <v>3.729394438623448e-07</v>
@@ -2190,19 +2190,19 @@
       <c r="K20" t="n">
         <v>88.10185855007521</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 30.174x + -12363.801</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-12363.80096203343</v>
       </c>
       <c r="Y20" t="n">
         <v>372.4565979316113</v>
       </c>
       <c r="Z20" t="n">
-        <v>208924720.4130622</v>
+        <v>103.498</v>
       </c>
       <c r="AA20" t="n">
         <v>3.715255539773576e-07</v>
@@ -2242,19 +2242,19 @@
       <c r="K21" t="n">
         <v>87.97360636318649</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 28.263x + -11432.831</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-11432.83107502408</v>
       </c>
       <c r="Y21" t="n">
         <v>369.4988003359341</v>
       </c>
       <c r="Z21" t="n">
-        <v>200975065.0416353</v>
+        <v>103.721</v>
       </c>
       <c r="AA21" t="n">
         <v>3.698263627206813e-07</v>
@@ -2294,19 +2294,19 @@
       <c r="K22" t="n">
         <v>88.13005146655154</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 30.629x + -12330.557</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-12330.55693840722</v>
       </c>
       <c r="Y22" t="n">
         <v>366.5550037701313</v>
       </c>
       <c r="Z22" t="n">
-        <v>398585036.2710235</v>
+        <v>98.95100000000002</v>
       </c>
       <c r="AA22" t="n">
         <v>3.675113956423256e-07</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2492,19 +2492,19 @@
       <c r="K2" t="n">
         <v>87.16748780124932</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 20.211x + -10616.009</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-10616.00920003734</v>
       </c>
       <c r="Y2" t="n">
         <v>452.6281176346285</v>
       </c>
       <c r="Z2" t="n">
-        <v>26965155.80394516</v>
+        <v>185.812</v>
       </c>
       <c r="AA2" t="n">
         <v>4.570549146996892e-07</v>
@@ -2544,19 +2544,19 @@
       <c r="K3" t="n">
         <v>87.6572350131018</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 24.443x + -12113.065</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-12113.06451025192</v>
       </c>
       <c r="Y3" t="n">
         <v>438.8395897881512</v>
       </c>
       <c r="Z3" t="n">
-        <v>359097936.60583</v>
+        <v>135.001</v>
       </c>
       <c r="AA3" t="n">
         <v>4.103164652903575e-07</v>
@@ -2596,19 +2596,19 @@
       <c r="K4" t="n">
         <v>87.63265752327231</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 24.189x + -11731.888</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11731.88806083015</v>
       </c>
       <c r="Y4" t="n">
         <v>433.5301124149074</v>
       </c>
       <c r="Z4" t="n">
-        <v>473453006.0500076</v>
+        <v>126.095</v>
       </c>
       <c r="AA4" t="n">
         <v>3.996858848909126e-07</v>
@@ -2648,19 +2648,19 @@
       <c r="K5" t="n">
         <v>87.82827567892951</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 26.370x + -12691.811</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-12691.81067537729</v>
       </c>
       <c r="Y5" t="n">
         <v>429.4146456355481</v>
       </c>
       <c r="Z5" t="n">
-        <v>937038313.5798287</v>
+        <v>117.0359999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>3.922750191135162e-07</v>
@@ -2700,19 +2700,19 @@
       <c r="K6" t="n">
         <v>87.9857801852595</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 28.434x + -13581.757</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13581.75687219688</v>
       </c>
       <c r="Y6" t="n">
         <v>425.2499391865626</v>
       </c>
       <c r="Z6" t="n">
-        <v>174058529.8754412</v>
+        <v>114.115</v>
       </c>
       <c r="AA6" t="n">
         <v>3.885166556966715e-07</v>
@@ -2752,19 +2752,19 @@
       <c r="K7" t="n">
         <v>87.88563877351126</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 27.086x + -12742.011</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-12742.01062557794</v>
       </c>
       <c r="Y7" t="n">
         <v>421.1003245100919</v>
       </c>
       <c r="Z7" t="n">
-        <v>172255243.7655863</v>
+        <v>111.591</v>
       </c>
       <c r="AA7" t="n">
         <v>3.837094757095452e-07</v>
@@ -2804,19 +2804,19 @@
       <c r="K8" t="n">
         <v>87.84211171119026</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 26.539x + -12321.753</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12321.75268154482</v>
       </c>
       <c r="Y8" t="n">
         <v>416.9846873740198</v>
       </c>
       <c r="Z8" t="n">
-        <v>113804099.6270947</v>
+        <v>113.765</v>
       </c>
       <c r="AA8" t="n">
         <v>3.811227722378589e-07</v>
@@ -2856,19 +2856,19 @@
       <c r="K9" t="n">
         <v>87.81077802907492</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 26.159x + -11994.225</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11994.22531311118</v>
       </c>
       <c r="Y9" t="n">
         <v>413.1611690987959</v>
       </c>
       <c r="Z9" t="n">
-        <v>451251565.2286672</v>
+        <v>111.04</v>
       </c>
       <c r="AA9" t="n">
         <v>3.773477702498862e-07</v>
@@ -2908,19 +2908,19 @@
       <c r="K10" t="n">
         <v>88.01800130936564</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 28.897x + -13193.131</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-13193.13106233725</v>
       </c>
       <c r="Y10" t="n">
         <v>409.6060133392238</v>
       </c>
       <c r="Z10" t="n">
-        <v>111933477.1832741</v>
+        <v>108.559</v>
       </c>
       <c r="AA10" t="n">
         <v>3.747474974519782e-07</v>
@@ -2960,19 +2960,19 @@
       <c r="K11" t="n">
         <v>87.85323310865101</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 26.677x + -11998.704</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11998.70370759429</v>
       </c>
       <c r="Y11" t="n">
         <v>406.291196330672</v>
       </c>
       <c r="Z11" t="n">
-        <v>241710295.472166</v>
+        <v>108.541</v>
       </c>
       <c r="AA11" t="n">
         <v>3.723001494175352e-07</v>
@@ -3012,19 +3012,19 @@
       <c r="K12" t="n">
         <v>87.98135449886084</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 28.372x + -12691.912</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-12691.91203782742</v>
       </c>
       <c r="Y12" t="n">
         <v>403.2006337661914</v>
       </c>
       <c r="Z12" t="n">
-        <v>109859829.8334279</v>
+        <v>106.826</v>
       </c>
       <c r="AA12" t="n">
         <v>3.69921281257965e-07</v>
@@ -3064,19 +3064,19 @@
       <c r="K13" t="n">
         <v>87.88812665941559</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 27.118x + -11990.528</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11990.52759832771</v>
       </c>
       <c r="Y13" t="n">
         <v>400.2078102795967</v>
       </c>
       <c r="Z13" t="n">
-        <v>327357146.2944426</v>
+        <v>104.324</v>
       </c>
       <c r="AA13" t="n">
         <v>3.676299454202607e-07</v>
@@ -3116,19 +3116,19 @@
       <c r="K14" t="n">
         <v>88.08061811441863</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 29.840x + -13156.683</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-13156.68338917681</v>
       </c>
       <c r="Y14" t="n">
         <v>397.3039047447717</v>
       </c>
       <c r="Z14" t="n">
-        <v>108215599.8261663</v>
+        <v>102.521</v>
       </c>
       <c r="AA14" t="n">
         <v>3.655139131372438e-07</v>
@@ -3168,19 +3168,19 @@
       <c r="K15" t="n">
         <v>88.05976693628509</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 29.519x + -12896.858</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-12896.85828247652</v>
       </c>
       <c r="Y15" t="n">
         <v>394.4754215025944</v>
       </c>
       <c r="Z15" t="n">
-        <v>216120754.9197448</v>
+        <v>102.628</v>
       </c>
       <c r="AA15" t="n">
         <v>3.640811067707824e-07</v>
@@ -3220,19 +3220,19 @@
       <c r="K16" t="n">
         <v>88.12428578359595</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 30.535x + -13256.571</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-13256.57052013853</v>
       </c>
       <c r="Y16" t="n">
         <v>391.6535537013432</v>
       </c>
       <c r="Z16" t="n">
-        <v>106803197.7981032</v>
+        <v>99.24499999999995</v>
       </c>
       <c r="AA16" t="n">
         <v>3.622292421104758e-07</v>
@@ -3272,19 +3272,19 @@
       <c r="K17" t="n">
         <v>87.96101903435023</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 28.088x + -12033.088</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-12033.08820502537</v>
       </c>
       <c r="Y17" t="n">
         <v>388.8202918079034</v>
       </c>
       <c r="Z17" t="n">
-        <v>106321943.3405277</v>
+        <v>100.254</v>
       </c>
       <c r="AA17" t="n">
         <v>3.602866626102672e-07</v>
@@ -3324,19 +3324,19 @@
       <c r="K18" t="n">
         <v>88.06409994133189</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 29.585x + -12606.354</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-12606.35367654404</v>
       </c>
       <c r="Y18" t="n">
         <v>385.9786399679244</v>
       </c>
       <c r="Z18" t="n">
-        <v>104982839.9092089</v>
+        <v>103.455</v>
       </c>
       <c r="AA18" t="n">
         <v>3.597788761976473e-07</v>
@@ -3376,19 +3376,19 @@
       <c r="K19" t="n">
         <v>88.08612077263473</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 29.926x + -12652.627</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-12652.62730287282</v>
       </c>
       <c r="Y19" t="n">
         <v>383.193660630813</v>
       </c>
       <c r="Z19" t="n">
-        <v>158330930.3102843</v>
+        <v>101.533</v>
       </c>
       <c r="AA19" t="n">
         <v>3.581488370121684e-07</v>
@@ -3428,19 +3428,19 @@
       <c r="K20" t="n">
         <v>88.17568511874825</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 31.396x + -13197.963</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-13197.96299407448</v>
       </c>
       <c r="Y20" t="n">
         <v>380.3892537577049</v>
       </c>
       <c r="Z20" t="n">
-        <v>122669349.6537943</v>
+        <v>99.31200000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>3.566569641173602e-07</v>
@@ -3480,19 +3480,19 @@
       <c r="K21" t="n">
         <v>88.08851357296426</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 29.963x + -12456.513</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-12456.51290675694</v>
       </c>
       <c r="Y21" t="n">
         <v>377.6029800248166</v>
       </c>
       <c r="Z21" t="n">
-        <v>264623826.9931263</v>
+        <v>99.928</v>
       </c>
       <c r="AA21" t="n">
         <v>3.553098167449959e-07</v>
@@ -3532,19 +3532,19 @@
       <c r="K22" t="n">
         <v>88.15884904291873</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 31.109x + -12847.917</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-12847.91731832053</v>
       </c>
       <c r="Y22" t="n">
         <v>374.7994787884469</v>
       </c>
       <c r="Z22" t="n">
-        <v>103380966.1128163</v>
+        <v>97.21699999999998</v>
       </c>
       <c r="AA22" t="n">
         <v>3.535345658232639e-07</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -3730,19 +3730,19 @@
       <c r="K2" t="n">
         <v>84.98650107467778</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.399x + -5628.870</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5628.87012266916</v>
       </c>
       <c r="Y2" t="n">
         <v>419.1303278562062</v>
       </c>
       <c r="Z2" t="n">
-        <v>237956021.5373747</v>
+        <v>380.9300000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>6.480821461489034e-07</v>
@@ -3782,19 +3782,19 @@
       <c r="K3" t="n">
         <v>86.26403278851514</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.315x + -6739.300</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6739.300166576242</v>
       </c>
       <c r="Y3" t="n">
         <v>394.8625556246611</v>
       </c>
       <c r="Z3" t="n">
-        <v>215315559.1440443</v>
+        <v>280.449</v>
       </c>
       <c r="AA3" t="n">
         <v>5.237797684194312e-07</v>
@@ -3834,19 +3834,19 @@
       <c r="K4" t="n">
         <v>86.74681597819193</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.593x + -7506.888</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7506.888128436009</v>
       </c>
       <c r="Y4" t="n">
         <v>387.3357926059832</v>
       </c>
       <c r="Z4" t="n">
-        <v>738117220.2832026</v>
+        <v>238.361</v>
       </c>
       <c r="AA4" t="n">
         <v>4.798370131338431e-07</v>
@@ -3886,19 +3886,19 @@
       <c r="K5" t="n">
         <v>86.84154626007687</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.122x + -7557.433</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7557.432651308401</v>
       </c>
       <c r="Y5" t="n">
         <v>382.6967082059697</v>
       </c>
       <c r="Z5" t="n">
-        <v>416303536.7261785</v>
+        <v>215.98</v>
       </c>
       <c r="AA5" t="n">
         <v>4.544229231216149e-07</v>
@@ -3938,19 +3938,19 @@
       <c r="K6" t="n">
         <v>87.3257801807214</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 21.410x + -8910.350</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8910.349587609531</v>
       </c>
       <c r="Y6" t="n">
         <v>378.3127078468118</v>
       </c>
       <c r="Z6" t="n">
-        <v>835726160.7478653</v>
+        <v>192.5579999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>4.368865707032969e-07</v>
@@ -3990,19 +3990,19 @@
       <c r="K7" t="n">
         <v>87.44871536883718</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 22.443x + -9214.317</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9214.317363509028</v>
       </c>
       <c r="Y7" t="n">
         <v>373.7850177928881</v>
       </c>
       <c r="Z7" t="n">
-        <v>101714626.979459</v>
+        <v>180.6729999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>4.24173743246501e-07</v>
@@ -4042,19 +4042,19 @@
       <c r="K8" t="n">
         <v>87.53264740503607</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 23.207x + -9385.325</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9385.325435555385</v>
       </c>
       <c r="Y8" t="n">
         <v>369.097428751326</v>
       </c>
       <c r="Z8" t="n">
-        <v>100454669.8107652</v>
+        <v>171.162</v>
       </c>
       <c r="AA8" t="n">
         <v>4.140593860886103e-07</v>
@@ -4094,19 +4094,19 @@
       <c r="K9" t="n">
         <v>87.65431667172342</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 24.412x + -9752.118</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9752.118087275996</v>
       </c>
       <c r="Y9" t="n">
         <v>364.4769137966321</v>
       </c>
       <c r="Z9" t="n">
-        <v>395702668.9113705</v>
+        <v>162.43</v>
       </c>
       <c r="AA9" t="n">
         <v>4.06252290539382e-07</v>
@@ -4146,19 +4146,19 @@
       <c r="K10" t="n">
         <v>87.4022985224036</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 22.041x + -8582.619</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8582.618510701705</v>
       </c>
       <c r="Y10" t="n">
         <v>360.0930713471144</v>
       </c>
       <c r="Z10" t="n">
-        <v>195787986.5454111</v>
+        <v>162.006</v>
       </c>
       <c r="AA10" t="n">
         <v>3.997722683862532e-07</v>
@@ -4198,19 +4198,19 @@
       <c r="K11" t="n">
         <v>87.72653360673159</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 25.189x + -9770.345</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9770.344659172164</v>
       </c>
       <c r="Y11" t="n">
         <v>356.0744743652321</v>
       </c>
       <c r="Z11" t="n">
-        <v>199362276.6665109</v>
+        <v>149.661</v>
       </c>
       <c r="AA11" t="n">
         <v>3.930753301313009e-07</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4396,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.91999548823703</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.019x + -7342.529</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7342.52900072193</v>
       </c>
       <c r="Y2" t="n">
         <v>454.4833827394576</v>
       </c>
       <c r="Z2" t="n">
-        <v>187116064.863457</v>
+        <v>302.482</v>
       </c>
       <c r="AA2" t="n">
         <v>6.053319565383948e-07</v>
@@ -4448,19 +4448,19 @@
       <c r="K3" t="n">
         <v>87.22616082429083</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 20.640x + -10390.833</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10390.83339015991</v>
       </c>
       <c r="Y3" t="n">
         <v>444.3433854461406</v>
       </c>
       <c r="Z3" t="n">
-        <v>227310339.0631462</v>
+        <v>193.322</v>
       </c>
       <c r="AA3" t="n">
         <v>4.806494654655304e-07</v>
@@ -4500,19 +4500,19 @@
       <c r="K4" t="n">
         <v>87.45954092620003</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 22.539x + -11150.890</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11150.89014368775</v>
       </c>
       <c r="Y4" t="n">
         <v>439.8004021319067</v>
       </c>
       <c r="Z4" t="n">
-        <v>390233521.0034816</v>
+        <v>162.029</v>
       </c>
       <c r="AA4" t="n">
         <v>4.478198723949327e-07</v>
@@ -4552,19 +4552,19 @@
       <c r="K5" t="n">
         <v>87.53414503506045</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 23.221x + -11336.898</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-11336.89800182589</v>
       </c>
       <c r="Y5" t="n">
         <v>435.8094655228695</v>
       </c>
       <c r="Z5" t="n">
-        <v>238000145.2117721</v>
+        <v>149.549</v>
       </c>
       <c r="AA5" t="n">
         <v>4.322508734925884e-07</v>
@@ -4604,19 +4604,19 @@
       <c r="K6" t="n">
         <v>87.74917473387549</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 25.442x + -12337.346</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-12337.34640091743</v>
       </c>
       <c r="Y6" t="n">
         <v>431.6658538150863</v>
       </c>
       <c r="Z6" t="n">
-        <v>353424793.0110175</v>
+        <v>137.68</v>
       </c>
       <c r="AA6" t="n">
         <v>4.219761535761566e-07</v>
@@ -4656,19 +4656,19 @@
       <c r="K7" t="n">
         <v>87.71348244619193</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 25.045x + -11976.821</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11976.82073371826</v>
       </c>
       <c r="Y7" t="n">
         <v>427.4226578433824</v>
       </c>
       <c r="Z7" t="n">
-        <v>175691224.9325576</v>
+        <v>132.2180000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>4.141469311108859e-07</v>
@@ -4708,19 +4708,19 @@
       <c r="K8" t="n">
         <v>87.69605277979372</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 24.855x + -11729.212</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11729.21161930763</v>
       </c>
       <c r="Y8" t="n">
         <v>423.3585406084665</v>
       </c>
       <c r="Z8" t="n">
-        <v>117607723.5857834</v>
+        <v>126.747</v>
       </c>
       <c r="AA8" t="n">
         <v>4.074363927913332e-07</v>
@@ -4760,19 +4760,19 @@
       <c r="K9" t="n">
         <v>87.7401998997705</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 25.341x + -11836.717</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11836.7168398624</v>
       </c>
       <c r="Y9" t="n">
         <v>419.5172831610098</v>
       </c>
       <c r="Z9" t="n">
-        <v>343081960.8524319</v>
+        <v>126.2839999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>4.035195149594637e-07</v>
@@ -4812,19 +4812,19 @@
       <c r="K10" t="n">
         <v>87.6356424929412</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 24.219x + -11153.355</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11153.35516706003</v>
       </c>
       <c r="Y10" t="n">
         <v>415.9383678094663</v>
       </c>
       <c r="Z10" t="n">
-        <v>429213198.5914063</v>
+        <v>123.458</v>
       </c>
       <c r="AA10" t="n">
         <v>3.985999351391694e-07</v>
@@ -4864,19 +4864,19 @@
       <c r="K11" t="n">
         <v>87.78529593462031</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 25.858x + -11838.617</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11838.61701463857</v>
       </c>
       <c r="Y11" t="n">
         <v>412.5809664772147</v>
       </c>
       <c r="Z11" t="n">
-        <v>899655013.5080864</v>
+        <v>119.3849999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>3.952566190074919e-07</v>
@@ -4916,19 +4916,19 @@
       <c r="K12" t="n">
         <v>87.84936577478415</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 26.629x + -12099.651</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-12099.65098283132</v>
       </c>
       <c r="Y12" t="n">
         <v>409.317182516985</v>
       </c>
       <c r="Z12" t="n">
-        <v>334834501.7323543</v>
+        <v>114.622</v>
       </c>
       <c r="AA12" t="n">
         <v>3.909901082707743e-07</v>
@@ -4968,19 +4968,19 @@
       <c r="K13" t="n">
         <v>87.86399750088029</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 26.811x + -12075.262</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-12075.26208024579</v>
       </c>
       <c r="Y13" t="n">
         <v>406.1401869914395</v>
       </c>
       <c r="Z13" t="n">
-        <v>222870366.8784933</v>
+        <v>115.45</v>
       </c>
       <c r="AA13" t="n">
         <v>3.892524334501335e-07</v>
@@ -5020,19 +5020,19 @@
       <c r="K14" t="n">
         <v>87.85234410351843</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 26.666x + -11892.427</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-11892.42657330367</v>
       </c>
       <c r="Y14" t="n">
         <v>403.0748855677115</v>
       </c>
       <c r="Z14" t="n">
-        <v>348849294.0173115</v>
+        <v>112.47</v>
       </c>
       <c r="AA14" t="n">
         <v>3.858002570018155e-07</v>
@@ -5072,19 +5072,19 @@
       <c r="K15" t="n">
         <v>87.78208836734723</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 25.820x + -11390.898</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11390.89846302218</v>
       </c>
       <c r="Y15" t="n">
         <v>400.0886233086401</v>
       </c>
       <c r="Z15" t="n">
-        <v>108984313.132315</v>
+        <v>111.931</v>
       </c>
       <c r="AA15" t="n">
         <v>3.835552427151432e-07</v>
@@ -5124,19 +5124,19 @@
       <c r="K16" t="n">
         <v>87.94582166090663</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 27.880x + -12253.841</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-12253.84147005952</v>
       </c>
       <c r="Y16" t="n">
         <v>397.0504871857528</v>
       </c>
       <c r="Z16" t="n">
-        <v>216152544.8316074</v>
+        <v>109.052</v>
       </c>
       <c r="AA16" t="n">
         <v>3.812783269214345e-07</v>
@@ -5176,19 +5176,19 @@
       <c r="K17" t="n">
         <v>87.94780186405562</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 27.907x + -12158.414</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-12158.414116309</v>
       </c>
       <c r="Y17" t="n">
         <v>394.0754869934265</v>
       </c>
       <c r="Z17" t="n">
-        <v>323781627.2760304</v>
+        <v>108.99</v>
       </c>
       <c r="AA17" t="n">
         <v>3.792557680674301e-07</v>
@@ -5228,19 +5228,19 @@
       <c r="K18" t="n">
         <v>87.9343229594916</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 27.725x + -11970.203</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-11970.20292691997</v>
       </c>
       <c r="Y18" t="n">
         <v>391.2051689590616</v>
       </c>
       <c r="Z18" t="n">
-        <v>107339580.1232407</v>
+        <v>110.14</v>
       </c>
       <c r="AA18" t="n">
         <v>3.77760869651101e-07</v>
@@ -5280,19 +5280,19 @@
       <c r="K19" t="n">
         <v>87.87411261549317</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 26.939x + -11512.475</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-11512.47549531506</v>
       </c>
       <c r="Y19" t="n">
         <v>388.3791891831955</v>
       </c>
       <c r="Z19" t="n">
-        <v>211220147.9162743</v>
+        <v>104.009</v>
       </c>
       <c r="AA19" t="n">
         <v>3.743627944763477e-07</v>
@@ -5332,19 +5332,19 @@
       <c r="K20" t="n">
         <v>87.9132204823778</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 27.444x + -11638.896</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-11638.89637173298</v>
       </c>
       <c r="Y20" t="n">
         <v>385.5153749469669</v>
       </c>
       <c r="Z20" t="n">
-        <v>105835037.7178549</v>
+        <v>106.473</v>
       </c>
       <c r="AA20" t="n">
         <v>3.736006616054055e-07</v>
@@ -5384,19 +5384,19 @@
       <c r="K21" t="n">
         <v>87.98631334448017</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 28.441x + -11981.094</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-11981.09387389747</v>
       </c>
       <c r="Y21" t="n">
         <v>382.6047261406154</v>
       </c>
       <c r="Z21" t="n">
-        <v>156162063.6326108</v>
+        <v>103.8749999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>3.716763761359019e-07</v>
@@ -5436,19 +5436,19 @@
       <c r="K22" t="n">
         <v>88.10965037978816</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 30.299x + -12706.022</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-12706.02240559245</v>
       </c>
       <c r="Y22" t="n">
         <v>379.749870447119</v>
       </c>
       <c r="Z22" t="n">
-        <v>154933492.0837362</v>
+        <v>101.895</v>
       </c>
       <c r="AA22" t="n">
         <v>3.70021274462572e-07</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5634,19 +5634,19 @@
       <c r="K2" t="n">
         <v>84.30208605106759</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.022x + -4753.425</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-4753.424589584552</v>
       </c>
       <c r="Y2" t="n">
         <v>407.9444048816297</v>
       </c>
       <c r="Z2" t="n">
-        <v>332515989.0284235</v>
+        <v>415.287</v>
       </c>
       <c r="AA2" t="n">
         <v>7.164514322357864e-07</v>
@@ -5686,19 +5686,19 @@
       <c r="K3" t="n">
         <v>85.91565009022914</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.004x + -6004.551</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6004.551330662123</v>
       </c>
       <c r="Y3" t="n">
         <v>386.2412426836281</v>
       </c>
       <c r="Z3" t="n">
-        <v>111598513.6450507</v>
+        <v>300.403</v>
       </c>
       <c r="AA3" t="n">
         <v>5.628143140030422e-07</v>
@@ -5738,19 +5738,19 @@
       <c r="K4" t="n">
         <v>86.50723530051565</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.384x + -6831.824</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6831.823986951316</v>
       </c>
       <c r="Y4" t="n">
         <v>379.3038843014611</v>
       </c>
       <c r="Z4" t="n">
-        <v>413031317.0144475</v>
+        <v>254.292</v>
       </c>
       <c r="AA4" t="n">
         <v>5.088121567821781e-07</v>
@@ -5790,19 +5790,19 @@
       <c r="K5" t="n">
         <v>86.85070831700442</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.175x + -7452.966</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7452.965955708944</v>
       </c>
       <c r="Y5" t="n">
         <v>374.5719261859737</v>
       </c>
       <c r="Z5" t="n">
-        <v>152892436.3082632</v>
+        <v>223.92</v>
       </c>
       <c r="AA5" t="n">
         <v>4.766402512075581e-07</v>
@@ -5842,19 +5842,19 @@
       <c r="K6" t="n">
         <v>87.15456286429219</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 20.119x + -8163.711</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8163.710795533659</v>
       </c>
       <c r="Y6" t="n">
         <v>369.9265806455115</v>
       </c>
       <c r="Z6" t="n">
-        <v>301771025.1762537</v>
+        <v>203.7020000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>4.561796761078541e-07</v>
@@ -5894,19 +5894,19 @@
       <c r="K7" t="n">
         <v>87.2028090156015</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 20.467x + -8138.085</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8138.084730669253</v>
       </c>
       <c r="Y7" t="n">
         <v>365.090233529936</v>
       </c>
       <c r="Z7" t="n">
-        <v>694411073.1949362</v>
+        <v>189.032</v>
       </c>
       <c r="AA7" t="n">
         <v>4.400790055181719e-07</v>
@@ -5946,19 +5946,19 @@
       <c r="K8" t="n">
         <v>87.3724872257356</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 21.791x + -8556.790</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8556.790384070811</v>
       </c>
       <c r="Y8" t="n">
         <v>360.2783639012237</v>
       </c>
       <c r="Z8" t="n">
-        <v>192911236.803858</v>
+        <v>177.703</v>
       </c>
       <c r="AA8" t="n">
         <v>4.28346261217713e-07</v>
@@ -5998,19 +5998,19 @@
       <c r="K9" t="n">
         <v>87.40992378631864</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 22.106x + -8532.472</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8532.471943589499</v>
       </c>
       <c r="Y9" t="n">
         <v>355.6587425423492</v>
       </c>
       <c r="Z9" t="n">
-        <v>193140130.2899781</v>
+        <v>169.3899999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>4.18716131799048e-07</v>
@@ -6050,19 +6050,19 @@
       <c r="K10" t="n">
         <v>87.45605437544947</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 22.508x + -8558.562</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8558.562107446602</v>
       </c>
       <c r="Y10" t="n">
         <v>351.3973577719283</v>
       </c>
       <c r="Z10" t="n">
-        <v>285939520.9280819</v>
+        <v>163.521</v>
       </c>
       <c r="AA10" t="n">
         <v>4.115268052404907e-07</v>
@@ -6102,19 +6102,19 @@
       <c r="K11" t="n">
         <v>87.35327508706726</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 21.632x + -8073.836</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8073.835542757663</v>
       </c>
       <c r="Y11" t="n">
         <v>347.5386268559336</v>
       </c>
       <c r="Z11" t="n">
-        <v>282811632.505776</v>
+        <v>158.2640000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>4.051327352762345e-07</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6300,19 +6300,19 @@
       <c r="K2" t="n">
         <v>86.30431200438761</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 15.482x + -7987.922</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7987.922226105684</v>
       </c>
       <c r="Y2" t="n">
         <v>446.0148829950641</v>
       </c>
       <c r="Z2" t="n">
-        <v>84978574.93709195</v>
+        <v>261.571</v>
       </c>
       <c r="AA2" t="n">
         <v>5.775022325785147e-07</v>
@@ -6352,19 +6352,19 @@
       <c r="K3" t="n">
         <v>87.31236314362366</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 21.303x + -10453.379</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10453.37906471734</v>
       </c>
       <c r="Y3" t="n">
         <v>434.2343672011721</v>
       </c>
       <c r="Z3" t="n">
-        <v>177951294.6077994</v>
+        <v>177.236</v>
       </c>
       <c r="AA3" t="n">
         <v>4.748872196471541e-07</v>
@@ -6404,19 +6404,19 @@
       <c r="K4" t="n">
         <v>87.3468866723552</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 21.580x + -10342.095</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10342.09511917656</v>
       </c>
       <c r="Y4" t="n">
         <v>429.2795170630448</v>
       </c>
       <c r="Z4" t="n">
-        <v>351478646.8944843</v>
+        <v>157.1960000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>4.489664134397564e-07</v>
@@ -6456,19 +6456,19 @@
       <c r="K5" t="n">
         <v>87.4567537694181</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 22.514x + -10665.842</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10665.8415541838</v>
       </c>
       <c r="Y5" t="n">
         <v>425.1959236977404</v>
       </c>
       <c r="Z5" t="n">
-        <v>235351636.5837735</v>
+        <v>145.2930000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>4.359411526968289e-07</v>
@@ -6508,19 +6508,19 @@
       <c r="K6" t="n">
         <v>87.58175752045857</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 23.679x + -11109.854</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-11109.85438935966</v>
       </c>
       <c r="Y6" t="n">
         <v>420.9383043666102</v>
       </c>
       <c r="Z6" t="n">
-        <v>344486988.1805056</v>
+        <v>136.829</v>
       </c>
       <c r="AA6" t="n">
         <v>4.272586588934582e-07</v>
@@ -6560,19 +6560,19 @@
       <c r="K7" t="n">
         <v>87.68095563085834</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 24.693x + -11470.745</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11470.74473171246</v>
       </c>
       <c r="Y7" t="n">
         <v>416.6609056134988</v>
       </c>
       <c r="Z7" t="n">
-        <v>454622194.7657275</v>
+        <v>129.434</v>
       </c>
       <c r="AA7" t="n">
         <v>4.196190617590498e-07</v>
@@ -6612,19 +6612,19 @@
       <c r="K8" t="n">
         <v>87.59691453622732</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 23.829x + -10899.961</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10899.96096864557</v>
       </c>
       <c r="Y8" t="n">
         <v>412.5604978648525</v>
       </c>
       <c r="Z8" t="n">
-        <v>112641204.4043455</v>
+        <v>129.434</v>
       </c>
       <c r="AA8" t="n">
         <v>4.14776932130355e-07</v>
@@ -6664,19 +6664,19 @@
       <c r="K9" t="n">
         <v>87.85833213739475</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 26.740x + -12184.708</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12184.70842095018</v>
       </c>
       <c r="Y9" t="n">
         <v>408.678924756534</v>
       </c>
       <c r="Z9" t="n">
-        <v>111774879.4283397</v>
+        <v>122.062</v>
       </c>
       <c r="AA9" t="n">
         <v>4.096945883440376e-07</v>
@@ -6716,19 +6716,19 @@
       <c r="K10" t="n">
         <v>87.7208202390443</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 25.126x + -11277.142</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11277.14185148296</v>
       </c>
       <c r="Y10" t="n">
         <v>405.128482187097</v>
       </c>
       <c r="Z10" t="n">
-        <v>331854691.1554563</v>
+        <v>121.4230000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>4.061919148170452e-07</v>
@@ -6768,19 +6768,19 @@
       <c r="K11" t="n">
         <v>87.72867139211171</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 25.212x + -11202.344</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11202.34366021609</v>
       </c>
       <c r="Y11" t="n">
         <v>401.7374751353441</v>
       </c>
       <c r="Z11" t="n">
-        <v>437438252.4191567</v>
+        <v>118.37</v>
       </c>
       <c r="AA11" t="n">
         <v>4.01959212551893e-07</v>
@@ -6820,19 +6820,19 @@
       <c r="K12" t="n">
         <v>87.79845730324153</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 26.012x + -11467.553</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-11467.55342588361</v>
       </c>
       <c r="Y12" t="n">
         <v>398.4736651690069</v>
       </c>
       <c r="Z12" t="n">
-        <v>217053205.7063066</v>
+        <v>117.152</v>
       </c>
       <c r="AA12" t="n">
         <v>3.994986912557351e-07</v>
@@ -6872,19 +6872,19 @@
       <c r="K13" t="n">
         <v>87.86654852666324</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 26.843x + -11745.343</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11745.34269629697</v>
       </c>
       <c r="Y13" t="n">
         <v>395.2619056066575</v>
       </c>
       <c r="Z13" t="n">
-        <v>221882014.0315479</v>
+        <v>114.402</v>
       </c>
       <c r="AA13" t="n">
         <v>3.96724520288062e-07</v>
@@ -6924,19 +6924,19 @@
       <c r="K14" t="n">
         <v>87.83201676099829</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 26.416x + -11435.601</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-11435.6013890905</v>
       </c>
       <c r="Y14" t="n">
         <v>392.0273051280593</v>
       </c>
       <c r="Z14" t="n">
-        <v>106739280.8172119</v>
+        <v>114.677</v>
       </c>
       <c r="AA14" t="n">
         <v>3.943063813999103e-07</v>
@@ -6976,19 +6976,19 @@
       <c r="K15" t="n">
         <v>87.85722191856998</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 26.727x + -11468.043</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11468.04262855224</v>
       </c>
       <c r="Y15" t="n">
         <v>388.8272275192413</v>
       </c>
       <c r="Z15" t="n">
-        <v>216422567.0752833</v>
+        <v>109.143</v>
       </c>
       <c r="AA15" t="n">
         <v>3.906950124330994e-07</v>
@@ -7028,19 +7028,19 @@
       <c r="K16" t="n">
         <v>87.91231771813393</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 27.433x + -11676.233</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11676.23337937664</v>
       </c>
       <c r="Y16" t="n">
         <v>385.6623818984777</v>
       </c>
       <c r="Z16" t="n">
-        <v>217053825.2136868</v>
+        <v>106.725</v>
       </c>
       <c r="AA16" t="n">
         <v>3.88113878768437e-07</v>
@@ -7080,19 +7080,19 @@
       <c r="K17" t="n">
         <v>87.81897619692099</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 26.257x + -11042.483</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-11042.48341330128</v>
       </c>
       <c r="Y17" t="n">
         <v>382.5544036487379</v>
       </c>
       <c r="Z17" t="n">
-        <v>156182389.0318249</v>
+        <v>108.109</v>
       </c>
       <c r="AA17" t="n">
         <v>3.866932251064737e-07</v>
@@ -7132,19 +7132,19 @@
       <c r="K18" t="n">
         <v>87.09435177645804</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 19.702x + -8057.979</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8057.979069796295</v>
       </c>
       <c r="Y18" t="n">
         <v>379.4769297440737</v>
       </c>
       <c r="Z18" t="n">
-        <v>515933647.3736491</v>
+        <v>115.366</v>
       </c>
       <c r="AA18" t="n">
         <v>3.850403723704442e-07</v>
@@ -7184,19 +7184,19 @@
       <c r="K19" t="n">
         <v>87.98796477474913</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 28.465x + -11809.416</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-11809.41632763514</v>
       </c>
       <c r="Y19" t="n">
         <v>376.4565916099552</v>
       </c>
       <c r="Z19" t="n">
-        <v>103033300.711237</v>
+        <v>103.657</v>
       </c>
       <c r="AA19" t="n">
         <v>3.824612640744002e-07</v>
@@ -7236,19 +7236,19 @@
       <c r="K20" t="n">
         <v>87.97144659451202</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 28.233x + -11595.304</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-11595.30394880118</v>
       </c>
       <c r="Y20" t="n">
         <v>373.3676814466969</v>
       </c>
       <c r="Z20" t="n">
-        <v>101526739.8696273</v>
+        <v>103.911</v>
       </c>
       <c r="AA20" t="n">
         <v>3.809198333641624e-07</v>
@@ -7288,19 +7288,19 @@
       <c r="K21" t="n">
         <v>87.51577827187131</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 23.049x + -9258.846</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9258.845952607056</v>
       </c>
       <c r="Y21" t="n">
         <v>370.3318818464714</v>
       </c>
       <c r="Z21" t="n">
-        <v>111811650.035345</v>
+        <v>108.898</v>
       </c>
       <c r="AA21" t="n">
         <v>3.792846845877749e-07</v>
@@ -7340,19 +7340,19 @@
       <c r="K22" t="n">
         <v>88.00158543006893</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 28.659x + -11563.321</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-11563.32149353308</v>
       </c>
       <c r="Y22" t="n">
         <v>367.3208433238416</v>
       </c>
       <c r="Z22" t="n">
-        <v>349314556.1951188</v>
+        <v>102.782</v>
       </c>
       <c r="AA22" t="n">
         <v>3.779635824933687e-07</v>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7538,19 +7538,19 @@
       <c r="K2" t="n">
         <v>84.58138443730105</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.542x + -5076.239</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5076.239441812922</v>
       </c>
       <c r="Y2" t="n">
         <v>407.9722052818478</v>
       </c>
       <c r="Z2" t="n">
-        <v>664932994.7204992</v>
+        <v>393.725</v>
       </c>
       <c r="AA2" t="n">
         <v>7.207750306963229e-07</v>
@@ -7590,19 +7590,19 @@
       <c r="K3" t="n">
         <v>86.10257211204122</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.678x + -6259.777</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6259.776557979794</v>
       </c>
       <c r="Y3" t="n">
         <v>384.2056505935366</v>
       </c>
       <c r="Z3" t="n">
-        <v>160366462.3266262</v>
+        <v>278.3680000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>5.498404646487141e-07</v>
@@ -7642,19 +7642,19 @@
       <c r="K4" t="n">
         <v>86.85636092540231</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 18.208x + -7592.345</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7592.345015751976</v>
       </c>
       <c r="Y4" t="n">
         <v>377.1802059422451</v>
       </c>
       <c r="Z4" t="n">
-        <v>205446605.1174258</v>
+        <v>227.635</v>
       </c>
       <c r="AA4" t="n">
         <v>4.943888532198906e-07</v>
@@ -7694,19 +7694,19 @@
       <c r="K5" t="n">
         <v>87.12585401084098</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 19.918x + -8153.215</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8153.215156702091</v>
       </c>
       <c r="Y5" t="n">
         <v>372.7751086175262</v>
       </c>
       <c r="Z5" t="n">
-        <v>101512622.2244934</v>
+        <v>198.654</v>
       </c>
       <c r="AA5" t="n">
         <v>4.637422447401791e-07</v>
@@ -7746,19 +7746,19 @@
       <c r="K6" t="n">
         <v>87.30968270270574</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 21.281x + -8592.884</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8592.884326206267</v>
       </c>
       <c r="Y6" t="n">
         <v>368.6221191779746</v>
       </c>
       <c r="Z6" t="n">
-        <v>302451889.9287871</v>
+        <v>181.672</v>
       </c>
       <c r="AA6" t="n">
         <v>4.449715321288874e-07</v>
@@ -7798,19 +7798,19 @@
       <c r="K7" t="n">
         <v>87.35629203936875</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 21.657x + -8593.149</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8593.148600568107</v>
       </c>
       <c r="Y7" t="n">
         <v>364.2640681413171</v>
       </c>
       <c r="Z7" t="n">
-        <v>396827873.48667</v>
+        <v>168.712</v>
       </c>
       <c r="AA7" t="n">
         <v>4.308082413939267e-07</v>
@@ -7850,19 +7850,19 @@
       <c r="K8" t="n">
         <v>87.47807250315246</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 22.704x + -8896.116</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8896.116349278796</v>
       </c>
       <c r="Y8" t="n">
         <v>359.8727291974537</v>
       </c>
       <c r="Z8" t="n">
-        <v>390775907.6157731</v>
+        <v>158.627</v>
       </c>
       <c r="AA8" t="n">
         <v>4.206757934116415e-07</v>
@@ -7902,19 +7902,19 @@
       <c r="K9" t="n">
         <v>87.62764350509046</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 24.138x + -9358.576</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9358.576339660338</v>
       </c>
       <c r="Y9" t="n">
         <v>355.6000456648105</v>
       </c>
       <c r="Z9" t="n">
-        <v>385922392.4631255</v>
+        <v>152.704</v>
       </c>
       <c r="AA9" t="n">
         <v>4.134157118207357e-07</v>
@@ -7954,19 +7954,19 @@
       <c r="K10" t="n">
         <v>87.55097369441968</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 23.381x + -8897.997</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8897.997046131297</v>
       </c>
       <c r="Y10" t="n">
         <v>351.5281863840216</v>
       </c>
       <c r="Z10" t="n">
-        <v>477110066.2016164</v>
+        <v>145.009</v>
       </c>
       <c r="AA10" t="n">
         <v>4.061003800676828e-07</v>
@@ -8006,19 +8006,19 @@
       <c r="K11" t="n">
         <v>87.7410947813129</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 25.351x + -9576.223</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9576.223069857489</v>
       </c>
       <c r="Y11" t="n">
         <v>347.6232157561738</v>
       </c>
       <c r="Z11" t="n">
-        <v>422618805.0285129</v>
+        <v>140.537</v>
       </c>
       <c r="AA11" t="n">
         <v>4.012325572343066e-07</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -8204,19 +8204,19 @@
       <c r="K2" t="n">
         <v>86.34408499697118</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 15.651x + -8041.755</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8041.755187989226</v>
       </c>
       <c r="Y2" t="n">
         <v>446.0615595429655</v>
       </c>
       <c r="Z2" t="n">
-        <v>49464944.57555766</v>
+        <v>248.224</v>
       </c>
       <c r="AA2" t="n">
         <v>5.718361790685231e-07</v>
@@ -8256,19 +8256,19 @@
       <c r="K3" t="n">
         <v>87.17115866982472</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 20.238x + -9910.927</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9910.926835935528</v>
       </c>
       <c r="Y3" t="n">
         <v>434.7989703482187</v>
       </c>
       <c r="Z3" t="n">
-        <v>712446686.4799011</v>
+        <v>174.905</v>
       </c>
       <c r="AA3" t="n">
         <v>4.7944172539051e-07</v>
@@ -8308,19 +8308,19 @@
       <c r="K4" t="n">
         <v>87.38250855412426</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 21.874x + -10531.451</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10531.45082497798</v>
       </c>
       <c r="Y4" t="n">
         <v>429.7643533837178</v>
       </c>
       <c r="Z4" t="n">
-        <v>176218480.1840758</v>
+        <v>151.73</v>
       </c>
       <c r="AA4" t="n">
         <v>4.528820728558591e-07</v>
@@ -8360,19 +8360,19 @@
       <c r="K5" t="n">
         <v>87.49667151033833</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 22.873x + -10873.962</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10873.96235495501</v>
       </c>
       <c r="Y5" t="n">
         <v>425.250014563747</v>
       </c>
       <c r="Z5" t="n">
-        <v>348281728.977523</v>
+        <v>140.738</v>
       </c>
       <c r="AA5" t="n">
         <v>4.389175667214527e-07</v>
@@ -8412,19 +8412,19 @@
       <c r="K6" t="n">
         <v>87.43192785567331</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 22.296x + -10421.739</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10421.73861125145</v>
       </c>
       <c r="Y6" t="n">
         <v>420.4541593279544</v>
       </c>
       <c r="Z6" t="n">
-        <v>344473786.5084239</v>
+        <v>133.039</v>
       </c>
       <c r="AA6" t="n">
         <v>4.292759090466947e-07</v>
@@ -8464,19 +8464,19 @@
       <c r="K7" t="n">
         <v>87.53207240313291</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 23.202x + -10718.833</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10718.83333377476</v>
       </c>
       <c r="Y7" t="n">
         <v>415.4928506164291</v>
       </c>
       <c r="Z7" t="n">
-        <v>905917161.1646137</v>
+        <v>127.572</v>
       </c>
       <c r="AA7" t="n">
         <v>4.218264874034907e-07</v>
@@ -8516,19 +8516,19 @@
       <c r="K8" t="n">
         <v>87.59404176537804</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 23.800x + -10854.508</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10854.50825440769</v>
       </c>
       <c r="Y8" t="n">
         <v>410.6932870237622</v>
       </c>
       <c r="Z8" t="n">
-        <v>448082915.096775</v>
+        <v>124.5119999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>4.162164143340568e-07</v>
@@ -8568,19 +8568,19 @@
       <c r="K9" t="n">
         <v>87.80924670836981</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 26.141x + -11833.508</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11833.50793657148</v>
       </c>
       <c r="Y9" t="n">
         <v>406.1558589451604</v>
       </c>
       <c r="Z9" t="n">
-        <v>332301901.3206196</v>
+        <v>118.5140000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>4.109958591551783e-07</v>
@@ -8620,19 +8620,19 @@
       <c r="K10" t="n">
         <v>87.71843829331985</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 25.099x + -11191.991</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11191.99089146436</v>
       </c>
       <c r="Y10" t="n">
         <v>401.9571716444201</v>
       </c>
       <c r="Z10" t="n">
-        <v>227694574.6184389</v>
+        <v>119.23</v>
       </c>
       <c r="AA10" t="n">
         <v>4.069792562363318e-07</v>
@@ -8672,19 +8672,19 @@
       <c r="K11" t="n">
         <v>87.72565101633602</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 25.179x + -11088.938</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11088.9380627502</v>
       </c>
       <c r="Y11" t="n">
         <v>398.0315089045411</v>
       </c>
       <c r="Z11" t="n">
-        <v>162656832.7226542</v>
+        <v>115.397</v>
       </c>
       <c r="AA11" t="n">
         <v>4.029520022061135e-07</v>
@@ -8724,19 +8724,19 @@
       <c r="K12" t="n">
         <v>87.81329754196575</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 26.189x + -11435.848</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-11435.84828978607</v>
       </c>
       <c r="Y12" t="n">
         <v>394.3663317785396</v>
       </c>
       <c r="Z12" t="n">
-        <v>322183951.9662494</v>
+        <v>115.532</v>
       </c>
       <c r="AA12" t="n">
         <v>4.005688885956205e-07</v>
@@ -8776,19 +8776,19 @@
       <c r="K13" t="n">
         <v>87.78284089096459</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 25.829x + -11145.944</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11145.94417561867</v>
       </c>
       <c r="Y13" t="n">
         <v>390.8797159972684</v>
       </c>
       <c r="Z13" t="n">
-        <v>159626181.9120257</v>
+        <v>111.609</v>
       </c>
       <c r="AA13" t="n">
         <v>3.965582726027328e-07</v>
@@ -8828,19 +8828,19 @@
       <c r="K14" t="n">
         <v>87.92232514794816</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 27.565x + -11825.718</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-11825.7179390845</v>
       </c>
       <c r="Y14" t="n">
         <v>387.5367382017457</v>
       </c>
       <c r="Z14" t="n">
-        <v>211283577.515597</v>
+        <v>105.909</v>
       </c>
       <c r="AA14" t="n">
         <v>3.934330596012159e-07</v>
@@ -8880,19 +8880,19 @@
       <c r="K15" t="n">
         <v>87.79026631901429</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 25.916x + -10963.163</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10963.16330667192</v>
       </c>
       <c r="Y15" t="n">
         <v>384.2435141102533</v>
       </c>
       <c r="Z15" t="n">
-        <v>157013075.8890429</v>
+        <v>109.815</v>
       </c>
       <c r="AA15" t="n">
         <v>3.919390020539939e-07</v>
@@ -8932,19 +8932,19 @@
       <c r="K16" t="n">
         <v>87.93441783095179</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 27.726x + -11663.678</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11663.67757229711</v>
       </c>
       <c r="Y16" t="n">
         <v>381.0008670321984</v>
       </c>
       <c r="Z16" t="n">
-        <v>103747707.3303173</v>
+        <v>106.6619999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>3.892789259204391e-07</v>
@@ -8984,19 +8984,19 @@
       <c r="K17" t="n">
         <v>87.90393481292853</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 27.323x + -11367.490</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-11367.48987197617</v>
       </c>
       <c r="Y17" t="n">
         <v>377.7220627897996</v>
       </c>
       <c r="Z17" t="n">
-        <v>514012192.685697</v>
+        <v>105.321</v>
       </c>
       <c r="AA17" t="n">
         <v>3.873320049307927e-07</v>
@@ -9036,19 +9036,19 @@
       <c r="K18" t="n">
         <v>87.9064504720627</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 27.356x + -11271.295</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-11271.29471457049</v>
       </c>
       <c r="Y18" t="n">
         <v>374.5527151661101</v>
       </c>
       <c r="Z18" t="n">
-        <v>212232685.4184781</v>
+        <v>104.587</v>
       </c>
       <c r="AA18" t="n">
         <v>3.85349753708965e-07</v>
@@ -9088,19 +9088,19 @@
       <c r="K19" t="n">
         <v>87.97865480775026</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 28.334x + -11585.463</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-11585.46290314838</v>
       </c>
       <c r="Y19" t="n">
         <v>371.3988009369948</v>
       </c>
       <c r="Z19" t="n">
-        <v>302960231.9717601</v>
+        <v>102.743</v>
       </c>
       <c r="AA19" t="n">
         <v>3.833658351484886e-07</v>
@@ -9140,19 +9140,19 @@
       <c r="K20" t="n">
         <v>87.91287197858743</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 27.440x + -11087.491</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-11087.49140504981</v>
       </c>
       <c r="Y20" t="n">
         <v>368.2134716012623</v>
       </c>
       <c r="Z20" t="n">
-        <v>400428346.9202821</v>
+        <v>101.33</v>
       </c>
       <c r="AA20" t="n">
         <v>3.806417972160746e-07</v>
@@ -9192,19 +9192,19 @@
       <c r="K21" t="n">
         <v>87.93871331944476</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 27.784x + -11127.632</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-11127.63190125026</v>
       </c>
       <c r="Y21" t="n">
         <v>365.0742796957069</v>
       </c>
       <c r="Z21" t="n">
-        <v>198553279.7935685</v>
+        <v>100.533</v>
       </c>
       <c r="AA21" t="n">
         <v>3.792317453037878e-07</v>
@@ -9244,19 +9244,19 @@
       <c r="K22" t="n">
         <v>87.99303877125151</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 28.537x + -11332.965</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-11332.96529429052</v>
       </c>
       <c r="Y22" t="n">
         <v>361.9240765072328</v>
       </c>
       <c r="Z22" t="n">
-        <v>99000463.198246</v>
+        <v>99.27299999999997</v>
       </c>
       <c r="AA22" t="n">
         <v>3.773292748369564e-07</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -9442,19 +9442,19 @@
       <c r="K2" t="n">
         <v>84.89641936567848</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.197x + -5404.923</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5404.922887160995</v>
       </c>
       <c r="Y2" t="n">
         <v>407.7407320082067</v>
       </c>
       <c r="Z2" t="n">
-        <v>337489321.5219505</v>
+        <v>375.6270000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>6.504215717871749e-07</v>
@@ -9494,19 +9494,19 @@
       <c r="K3" t="n">
         <v>86.56053363199396</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.638x + -7005.263</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7005.26348855395</v>
       </c>
       <c r="Y3" t="n">
         <v>380.7046700202453</v>
       </c>
       <c r="Z3" t="n">
-        <v>206907814.4940717</v>
+        <v>250.0069999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>4.936258015863929e-07</v>
@@ -9546,19 +9546,19 @@
       <c r="K4" t="n">
         <v>87.14506056677826</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 20.052x + -8202.643</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8202.642918390571</v>
       </c>
       <c r="Y4" t="n">
         <v>373.3274848692083</v>
       </c>
       <c r="Z4" t="n">
-        <v>205592457.0210522</v>
+        <v>203.114</v>
       </c>
       <c r="AA4" t="n">
         <v>4.481677780507303e-07</v>
@@ -9598,19 +9598,19 @@
       <c r="K5" t="n">
         <v>87.38244622427608</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 21.874x + -8793.680</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8793.679850124627</v>
       </c>
       <c r="Y5" t="n">
         <v>368.4710785370489</v>
       </c>
       <c r="Z5" t="n">
-        <v>200433486.6227811</v>
+        <v>178.4640000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>4.242455604650512e-07</v>
@@ -9650,19 +9650,19 @@
       <c r="K6" t="n">
         <v>87.58863587287293</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 23.747x + -9406.969</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9406.968541564451</v>
       </c>
       <c r="Y6" t="n">
         <v>363.6699620977606</v>
       </c>
       <c r="Z6" t="n">
-        <v>641576592.0366459</v>
+        <v>157.437</v>
       </c>
       <c r="AA6" t="n">
         <v>4.078205554322477e-07</v>
@@ -9702,19 +9702,19 @@
       <c r="K7" t="n">
         <v>87.45309475640305</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 22.481x + -8700.101</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8700.101075581944</v>
       </c>
       <c r="Y7" t="n">
         <v>358.5567049748257</v>
       </c>
       <c r="Z7" t="n">
-        <v>194574662.7637895</v>
+        <v>150.675</v>
       </c>
       <c r="AA7" t="n">
         <v>3.980646115841885e-07</v>
@@ -9754,19 +9754,19 @@
       <c r="K8" t="n">
         <v>87.50780406106331</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 22.976x + -8746.054</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8746.053549221731</v>
       </c>
       <c r="Y8" t="n">
         <v>353.2594697064274</v>
       </c>
       <c r="Z8" t="n">
-        <v>191884537.7166275</v>
+        <v>146.104</v>
       </c>
       <c r="AA8" t="n">
         <v>3.91681072647163e-07</v>
@@ -9806,19 +9806,19 @@
       <c r="K9" t="n">
         <v>87.56832152919188</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 23.548x + -8815.579</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8815.579496827868</v>
       </c>
       <c r="Y9" t="n">
         <v>348.1448526875594</v>
       </c>
       <c r="Z9" t="n">
-        <v>188760106.866369</v>
+        <v>137.07</v>
       </c>
       <c r="AA9" t="n">
         <v>3.848303036038166e-07</v>
@@ -9858,19 +9858,19 @@
       <c r="K10" t="n">
         <v>87.93266750370438</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 27.703x + -10328.277</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10328.27698914494</v>
       </c>
       <c r="Y10" t="n">
         <v>343.3575751524845</v>
       </c>
       <c r="Z10" t="n">
-        <v>93097461.29632474</v>
+        <v>130.099</v>
       </c>
       <c r="AA10" t="n">
         <v>3.806756731335172e-07</v>
@@ -9910,19 +9910,19 @@
       <c r="K11" t="n">
         <v>87.62702090976043</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 24.131x + -8761.432</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8761.431537887789</v>
       </c>
       <c r="Y11" t="n">
         <v>338.9885421096196</v>
       </c>
       <c r="Z11" t="n">
-        <v>298561497.6883295</v>
+        <v>129.637</v>
       </c>
       <c r="AA11" t="n">
         <v>3.764243893188474e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>87.15972788560832</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 20.156x + -10528.520</t>
-        </is>
+      <c r="W2" t="n">
+        <v>20.1561106702584</v>
       </c>
       <c r="X2" t="n">
         <v>-10528.52042150222</v>
@@ -600,7 +598,7 @@
         <v>460.6808130661087</v>
       </c>
       <c r="Z2" t="n">
-        <v>192.894</v>
+        <v>190601270.4768265</v>
       </c>
       <c r="AA2" t="n">
         <v>4.644509464842502e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>87.52229951283391</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 23.110x + -11894.280</t>
-        </is>
+      <c r="W3" t="n">
+        <v>23.11016206508113</v>
       </c>
       <c r="X3" t="n">
         <v>-11894.28030228045</v>
@@ -652,7 +648,7 @@
         <v>453.9903085353594</v>
       </c>
       <c r="Z3" t="n">
-        <v>167.724</v>
+        <v>254353603.7316092</v>
       </c>
       <c r="AA3" t="n">
         <v>4.389297176198378e-07</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>87.57404826736281</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 23.604x + -11916.574</t>
-        </is>
+      <c r="W4" t="n">
+        <v>23.60374103942669</v>
       </c>
       <c r="X4" t="n">
         <v>-11916.57385893646</v>
@@ -704,7 +698,7 @@
         <v>447.7894253377514</v>
       </c>
       <c r="Z4" t="n">
-        <v>156.5880000000001</v>
+        <v>244588629.4254274</v>
       </c>
       <c r="AA4" t="n">
         <v>4.242214339888221e-07</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>87.6177591529958</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 24.037x + -11929.575</t>
-        </is>
+      <c r="W5" t="n">
+        <v>24.03735103107618</v>
       </c>
       <c r="X5" t="n">
         <v>-11929.57493990915</v>
@@ -756,7 +748,7 @@
         <v>441.8343123082274</v>
       </c>
       <c r="Z5" t="n">
-        <v>146.3920000000001</v>
+        <v>181461776.0191447</v>
       </c>
       <c r="AA5" t="n">
         <v>4.12948038816336e-07</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>87.80851140963313</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 26.132x + -12825.707</t>
-        </is>
+      <c r="W6" t="n">
+        <v>26.13193448314385</v>
       </c>
       <c r="X6" t="n">
         <v>-12825.70675385108</v>
@@ -808,7 +798,7 @@
         <v>435.9848026626581</v>
       </c>
       <c r="Z6" t="n">
-        <v>140.352</v>
+        <v>119033721.8569947</v>
       </c>
       <c r="AA6" t="n">
         <v>4.054320414649394e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>87.65940662234762</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 24.466x + -11753.455</t>
-        </is>
+      <c r="W7" t="n">
+        <v>24.46554989254422</v>
       </c>
       <c r="X7" t="n">
         <v>-11753.45510055545</v>
@@ -860,7 +848,7 @@
         <v>430.2772136153836</v>
       </c>
       <c r="Z7" t="n">
-        <v>137.215</v>
+        <v>352070846.4447082</v>
       </c>
       <c r="AA7" t="n">
         <v>3.984371058527456e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>87.82088398768474</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 26.280x + -12489.765</t>
-        </is>
+      <c r="W8" t="n">
+        <v>26.2804506968728</v>
       </c>
       <c r="X8" t="n">
         <v>-12489.76538931573</v>
@@ -912,7 +898,7 @@
         <v>424.9842492674028</v>
       </c>
       <c r="Z8" t="n">
-        <v>133.602</v>
+        <v>116039973.4921873</v>
       </c>
       <c r="AA8" t="n">
         <v>3.931125257048022e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>87.74775265988983</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 25.426x + -11877.666</t>
-        </is>
+      <c r="W9" t="n">
+        <v>25.42627719299446</v>
       </c>
       <c r="X9" t="n">
         <v>-11877.6660878247</v>
@@ -964,7 +948,7 @@
         <v>420.0882347847049</v>
       </c>
       <c r="Z9" t="n">
-        <v>131.738</v>
+        <v>114679807.782176</v>
       </c>
       <c r="AA9" t="n">
         <v>3.883145652609311e-07</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>87.83208426718163</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 26.416x + -12204.342</t>
-        </is>
+      <c r="W10" t="n">
+        <v>26.41635621116027</v>
       </c>
       <c r="X10" t="n">
         <v>-12204.34182404864</v>
@@ -1016,7 +998,7 @@
         <v>415.6446530382878</v>
       </c>
       <c r="Z10" t="n">
-        <v>128.581</v>
+        <v>309683257.2436185</v>
       </c>
       <c r="AA10" t="n">
         <v>3.840786656903262e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>87.88271007747976</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 27.049x + -12358.873</t>
-        </is>
+      <c r="W11" t="n">
+        <v>27.04858506982115</v>
       </c>
       <c r="X11" t="n">
         <v>-12358.87300405674</v>
@@ -1068,7 +1048,7 @@
         <v>411.6109132545095</v>
       </c>
       <c r="Z11" t="n">
-        <v>124.093</v>
+        <v>336354412.5253681</v>
       </c>
       <c r="AA11" t="n">
         <v>3.798725309185535e-07</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>87.2868729892753</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 21.102x + -10893.998</t>
-        </is>
+      <c r="W2" t="n">
+        <v>21.10219978021449</v>
       </c>
       <c r="X2" t="n">
         <v>-10893.99816159297</v>
@@ -1266,7 +1244,7 @@
         <v>447.1435381167894</v>
       </c>
       <c r="Z2" t="n">
-        <v>152.723</v>
+        <v>248521665.1200158</v>
       </c>
       <c r="AA2" t="n">
         <v>4.527610517887826e-07</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>87.5769512123931</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 23.632x + -11504.339</t>
-        </is>
+      <c r="W3" t="n">
+        <v>23.63205341832907</v>
       </c>
       <c r="X3" t="n">
         <v>-11504.33945863282</v>
@@ -1318,7 +1294,7 @@
         <v>433.2531990944827</v>
       </c>
       <c r="Z3" t="n">
-        <v>131.984</v>
+        <v>826482560.508213</v>
       </c>
       <c r="AA3" t="n">
         <v>4.243705039226735e-07</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>87.60942894374718</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 23.953x + -11430.260</t>
-        </is>
+      <c r="W4" t="n">
+        <v>23.95349344292101</v>
       </c>
       <c r="X4" t="n">
         <v>-11430.26001686559</v>
@@ -1370,7 +1344,7 @@
         <v>427.8721024992129</v>
       </c>
       <c r="Z4" t="n">
-        <v>129.28</v>
+        <v>175318940.6701232</v>
       </c>
       <c r="AA4" t="n">
         <v>4.159682414055889e-07</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>87.5998281694382</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 23.858x + -11224.706</t>
-        </is>
+      <c r="W5" t="n">
+        <v>23.85756708838235</v>
       </c>
       <c r="X5" t="n">
         <v>-11224.70583769813</v>
@@ -1422,7 +1394,7 @@
         <v>423.6562047663102</v>
       </c>
       <c r="Z5" t="n">
-        <v>124.1009999999999</v>
+        <v>346651457.6429015</v>
       </c>
       <c r="AA5" t="n">
         <v>4.087172028732938e-07</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>87.80859278634296</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 26.133x + -12214.074</t>
-        </is>
+      <c r="W6" t="n">
+        <v>26.1329058253196</v>
       </c>
       <c r="X6" t="n">
         <v>-12214.07350323225</v>
@@ -1474,7 +1444,7 @@
         <v>419.4514387968316</v>
       </c>
       <c r="Z6" t="n">
-        <v>119.293</v>
+        <v>114790085.4256744</v>
       </c>
       <c r="AA6" t="n">
         <v>4.036382757990266e-07</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>87.76536653264944</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 25.627x + -11820.217</t>
-        </is>
+      <c r="W7" t="n">
+        <v>25.62689850182742</v>
       </c>
       <c r="X7" t="n">
         <v>-11820.21700253824</v>
@@ -1526,7 +1494,7 @@
         <v>415.2260026280111</v>
       </c>
       <c r="Z7" t="n">
-        <v>117.867</v>
+        <v>175938969.3848063</v>
       </c>
       <c r="AA7" t="n">
         <v>3.996979035424695e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>87.80262087592632</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 26.062x + -11887.292</t>
-        </is>
+      <c r="W8" t="n">
+        <v>26.06181391361173</v>
       </c>
       <c r="X8" t="n">
         <v>-11887.29217957252</v>
@@ -1578,7 +1544,7 @@
         <v>411.1281362983607</v>
       </c>
       <c r="Z8" t="n">
-        <v>116.985</v>
+        <v>448424714.3112966</v>
       </c>
       <c r="AA8" t="n">
         <v>3.9640601027699e-07</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>87.85089048505542</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 26.648x + -12030.072</t>
-        </is>
+      <c r="W9" t="n">
+        <v>26.64773770317868</v>
       </c>
       <c r="X9" t="n">
         <v>-12030.07192896979</v>
@@ -1630,7 +1594,7 @@
         <v>407.3281667431311</v>
       </c>
       <c r="Z9" t="n">
-        <v>113.1130000000001</v>
+        <v>222657263.1626075</v>
       </c>
       <c r="AA9" t="n">
         <v>3.922137922553009e-07</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>87.92629413956762</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 27.618x + -12366.105</t>
-        </is>
+      <c r="W10" t="n">
+        <v>27.61759058771168</v>
       </c>
       <c r="X10" t="n">
         <v>-12366.10545753141</v>
@@ -1682,7 +1644,7 @@
         <v>403.7111005908142</v>
       </c>
       <c r="Z10" t="n">
-        <v>113.2769999999999</v>
+        <v>109990427.2364046</v>
       </c>
       <c r="AA10" t="n">
         <v>3.904469143793302e-07</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>87.97949672654772</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 28.345x + -12585.917</t>
-        </is>
+      <c r="W11" t="n">
+        <v>28.34542643957678</v>
       </c>
       <c r="X11" t="n">
         <v>-12585.91718424231</v>
@@ -1734,7 +1694,7 @@
         <v>400.2978906122345</v>
       </c>
       <c r="Z11" t="n">
-        <v>110.489</v>
+        <v>175910043.9011849</v>
       </c>
       <c r="AA11" t="n">
         <v>3.877393003707262e-07</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>87.91906736815051</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 27.522x + -12076.695</t>
-        </is>
+      <c r="W12" t="n">
+        <v>27.52159482215613</v>
       </c>
       <c r="X12" t="n">
         <v>-12076.69488488927</v>
@@ -1786,7 +1744,7 @@
         <v>397.0421710001932</v>
       </c>
       <c r="Z12" t="n">
-        <v>111.1540000000001</v>
+        <v>432892730.2027784</v>
       </c>
       <c r="AA12" t="n">
         <v>3.854281908457652e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>87.91606963940927</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 27.482x + -11945.455</t>
-        </is>
+      <c r="W13" t="n">
+        <v>27.48197021391608</v>
       </c>
       <c r="X13" t="n">
         <v>-11945.45472151515</v>
@@ -1838,7 +1794,7 @@
         <v>393.8312251500885</v>
       </c>
       <c r="Z13" t="n">
-        <v>110.27</v>
+        <v>214386918.522717</v>
       </c>
       <c r="AA13" t="n">
         <v>3.83453242085289e-07</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>87.97033293113847</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 28.217x + -12168.587</t>
-        </is>
+      <c r="W14" t="n">
+        <v>28.21734255105922</v>
       </c>
       <c r="X14" t="n">
         <v>-12168.58682462352</v>
@@ -1890,7 +1844,7 @@
         <v>390.6896074290457</v>
       </c>
       <c r="Z14" t="n">
-        <v>107.432</v>
+        <v>212840888.1988895</v>
       </c>
       <c r="AA14" t="n">
         <v>3.812314796101391e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>87.99980391079097</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 28.633x + -12247.848</t>
-        </is>
+      <c r="W15" t="n">
+        <v>28.63344364617319</v>
       </c>
       <c r="X15" t="n">
         <v>-12247.84783957728</v>
@@ -1942,7 +1894,7 @@
         <v>387.6458344404541</v>
       </c>
       <c r="Z15" t="n">
-        <v>106.785</v>
+        <v>211057674.0037495</v>
       </c>
       <c r="AA15" t="n">
         <v>3.795525456519262e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>87.93312207283692</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 27.709x + -11721.623</t>
-        </is>
+      <c r="W16" t="n">
+        <v>27.70890491712827</v>
       </c>
       <c r="X16" t="n">
         <v>-11721.62250437071</v>
@@ -1994,7 +1944,7 @@
         <v>384.6164933954831</v>
       </c>
       <c r="Z16" t="n">
-        <v>106.9449999999999</v>
+        <v>314338859.8930665</v>
       </c>
       <c r="AA16" t="n">
         <v>3.776512885782103e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>87.29025771961543</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 21.129x + -8707.147</t>
-        </is>
+      <c r="W17" t="n">
+        <v>21.12859788937235</v>
       </c>
       <c r="X17" t="n">
         <v>-8707.14723446308</v>
@@ -2046,7 +1994,7 @@
         <v>381.5022735022956</v>
       </c>
       <c r="Z17" t="n">
-        <v>112.684</v>
+        <v>159568288.1963896</v>
       </c>
       <c r="AA17" t="n">
         <v>3.761299651783017e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>88.08667786806856</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 29.935x + -12491.809</t>
-        </is>
+      <c r="W18" t="n">
+        <v>29.93457259153982</v>
       </c>
       <c r="X18" t="n">
         <v>-12491.80891613518</v>
@@ -2098,7 +2044,7 @@
         <v>378.491303530022</v>
       </c>
       <c r="Z18" t="n">
-        <v>102.746</v>
+        <v>411653892.8842936</v>
       </c>
       <c r="AA18" t="n">
         <v>3.737574662623318e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>88.04864330120701</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 29.351x + -12118.932</t>
-        </is>
+      <c r="W19" t="n">
+        <v>29.35066920045311</v>
       </c>
       <c r="X19" t="n">
         <v>-12118.93204433167</v>
@@ -2150,7 +2094,7 @@
         <v>375.4657874272673</v>
       </c>
       <c r="Z19" t="n">
-        <v>103.851</v>
+        <v>510651316.4201289</v>
       </c>
       <c r="AA19" t="n">
         <v>3.729394438623448e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>88.10185855007521</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 30.174x + -12363.801</t>
-        </is>
+      <c r="W20" t="n">
+        <v>30.17415636788073</v>
       </c>
       <c r="X20" t="n">
         <v>-12363.80096203343</v>
@@ -2202,7 +2144,7 @@
         <v>372.4565979316113</v>
       </c>
       <c r="Z20" t="n">
-        <v>103.498</v>
+        <v>208924720.4130622</v>
       </c>
       <c r="AA20" t="n">
         <v>3.715255539773576e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>87.97360636318649</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 28.263x + -11432.831</t>
-        </is>
+      <c r="W21" t="n">
+        <v>28.26296291251735</v>
       </c>
       <c r="X21" t="n">
         <v>-11432.83107502408</v>
@@ -2254,7 +2194,7 @@
         <v>369.4988003359341</v>
       </c>
       <c r="Z21" t="n">
-        <v>103.721</v>
+        <v>200975065.0416353</v>
       </c>
       <c r="AA21" t="n">
         <v>3.698263627206813e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>88.13005146655154</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 30.629x + -12330.557</t>
-        </is>
+      <c r="W22" t="n">
+        <v>30.62941788190355</v>
       </c>
       <c r="X22" t="n">
         <v>-12330.55693840722</v>
@@ -2306,7 +2244,7 @@
         <v>366.5550037701313</v>
       </c>
       <c r="Z22" t="n">
-        <v>98.95100000000002</v>
+        <v>398585036.2710235</v>
       </c>
       <c r="AA22" t="n">
         <v>3.675113956423256e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>87.16748780124932</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 20.211x + -10616.009</t>
-        </is>
+      <c r="W2" t="n">
+        <v>20.21142054751816</v>
       </c>
       <c r="X2" t="n">
         <v>-10616.00920003734</v>
@@ -2504,7 +2440,7 @@
         <v>452.6281176346285</v>
       </c>
       <c r="Z2" t="n">
-        <v>185.812</v>
+        <v>26965155.80394516</v>
       </c>
       <c r="AA2" t="n">
         <v>4.570549146996892e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>87.6572350131018</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 24.443x + -12113.065</t>
-        </is>
+      <c r="W3" t="n">
+        <v>24.44284646434752</v>
       </c>
       <c r="X3" t="n">
         <v>-12113.06451025192</v>
@@ -2556,7 +2490,7 @@
         <v>438.8395897881512</v>
       </c>
       <c r="Z3" t="n">
-        <v>135.001</v>
+        <v>359097936.60583</v>
       </c>
       <c r="AA3" t="n">
         <v>4.103164652903575e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>87.63265752327231</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 24.189x + -11731.888</t>
-        </is>
+      <c r="W4" t="n">
+        <v>24.18879896270412</v>
       </c>
       <c r="X4" t="n">
         <v>-11731.88806083015</v>
@@ -2608,7 +2540,7 @@
         <v>433.5301124149074</v>
       </c>
       <c r="Z4" t="n">
-        <v>126.095</v>
+        <v>473453006.0500076</v>
       </c>
       <c r="AA4" t="n">
         <v>3.996858848909126e-07</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>87.82827567892951</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 26.370x + -12691.811</t>
-        </is>
+      <c r="W5" t="n">
+        <v>26.36998513322005</v>
       </c>
       <c r="X5" t="n">
         <v>-12691.81067537729</v>
@@ -2660,7 +2590,7 @@
         <v>429.4146456355481</v>
       </c>
       <c r="Z5" t="n">
-        <v>117.0359999999999</v>
+        <v>937038313.5798287</v>
       </c>
       <c r="AA5" t="n">
         <v>3.922750191135162e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>87.9857801852595</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 28.434x + -13581.757</t>
-        </is>
+      <c r="W6" t="n">
+        <v>28.43392464212173</v>
       </c>
       <c r="X6" t="n">
         <v>-13581.75687219688</v>
@@ -2712,7 +2640,7 @@
         <v>425.2499391865626</v>
       </c>
       <c r="Z6" t="n">
-        <v>114.115</v>
+        <v>174058529.8754412</v>
       </c>
       <c r="AA6" t="n">
         <v>3.885166556966715e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>87.88563877351126</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 27.086x + -12742.011</t>
-        </is>
+      <c r="W7" t="n">
+        <v>27.08608537804733</v>
       </c>
       <c r="X7" t="n">
         <v>-12742.01062557794</v>
@@ -2764,7 +2690,7 @@
         <v>421.1003245100919</v>
       </c>
       <c r="Z7" t="n">
-        <v>111.591</v>
+        <v>172255243.7655863</v>
       </c>
       <c r="AA7" t="n">
         <v>3.837094757095452e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>87.84211171119026</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 26.539x + -12321.753</t>
-        </is>
+      <c r="W8" t="n">
+        <v>26.53922676840831</v>
       </c>
       <c r="X8" t="n">
         <v>-12321.75268154482</v>
@@ -2816,7 +2740,7 @@
         <v>416.9846873740198</v>
       </c>
       <c r="Z8" t="n">
-        <v>113.765</v>
+        <v>113804099.6270947</v>
       </c>
       <c r="AA8" t="n">
         <v>3.811227722378589e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>87.81077802907492</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 26.159x + -11994.225</t>
-        </is>
+      <c r="W9" t="n">
+        <v>26.15901667477477</v>
       </c>
       <c r="X9" t="n">
         <v>-11994.22531311118</v>
@@ -2868,7 +2790,7 @@
         <v>413.1611690987959</v>
       </c>
       <c r="Z9" t="n">
-        <v>111.04</v>
+        <v>451251565.2286672</v>
       </c>
       <c r="AA9" t="n">
         <v>3.773477702498862e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>88.01800130936564</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 28.897x + -13193.131</t>
-        </is>
+      <c r="W10" t="n">
+        <v>28.89654969394406</v>
       </c>
       <c r="X10" t="n">
         <v>-13193.13106233725</v>
@@ -2920,7 +2840,7 @@
         <v>409.6060133392238</v>
       </c>
       <c r="Z10" t="n">
-        <v>108.559</v>
+        <v>111933477.1832741</v>
       </c>
       <c r="AA10" t="n">
         <v>3.747474974519782e-07</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>87.85323310865101</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 26.677x + -11998.704</t>
-        </is>
+      <c r="W11" t="n">
+        <v>26.67684388052558</v>
       </c>
       <c r="X11" t="n">
         <v>-11998.70370759429</v>
@@ -2972,7 +2890,7 @@
         <v>406.291196330672</v>
       </c>
       <c r="Z11" t="n">
-        <v>108.541</v>
+        <v>241710295.472166</v>
       </c>
       <c r="AA11" t="n">
         <v>3.723001494175352e-07</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>87.98135449886084</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 28.372x + -12691.912</t>
-        </is>
+      <c r="W12" t="n">
+        <v>28.37153454577687</v>
       </c>
       <c r="X12" t="n">
         <v>-12691.91203782742</v>
@@ -3024,7 +2940,7 @@
         <v>403.2006337661914</v>
       </c>
       <c r="Z12" t="n">
-        <v>106.826</v>
+        <v>109859829.8334279</v>
       </c>
       <c r="AA12" t="n">
         <v>3.69921281257965e-07</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>87.88812665941559</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 27.118x + -11990.528</t>
-        </is>
+      <c r="W13" t="n">
+        <v>27.11802302793079</v>
       </c>
       <c r="X13" t="n">
         <v>-11990.52759832771</v>
@@ -3076,7 +2990,7 @@
         <v>400.2078102795967</v>
       </c>
       <c r="Z13" t="n">
-        <v>104.324</v>
+        <v>327357146.2944426</v>
       </c>
       <c r="AA13" t="n">
         <v>3.676299454202607e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>88.08061811441863</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 29.840x + -13156.683</t>
-        </is>
+      <c r="W14" t="n">
+        <v>29.83999460472886</v>
       </c>
       <c r="X14" t="n">
         <v>-13156.68338917681</v>
@@ -3128,7 +3040,7 @@
         <v>397.3039047447717</v>
       </c>
       <c r="Z14" t="n">
-        <v>102.521</v>
+        <v>108215599.8261663</v>
       </c>
       <c r="AA14" t="n">
         <v>3.655139131372438e-07</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>88.05976693628509</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 29.519x + -12896.858</t>
-        </is>
+      <c r="W15" t="n">
+        <v>29.51907062672297</v>
       </c>
       <c r="X15" t="n">
         <v>-12896.85828247652</v>
@@ -3180,7 +3090,7 @@
         <v>394.4754215025944</v>
       </c>
       <c r="Z15" t="n">
-        <v>102.628</v>
+        <v>216120754.9197448</v>
       </c>
       <c r="AA15" t="n">
         <v>3.640811067707824e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>88.12428578359595</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 30.535x + -13256.571</t>
-        </is>
+      <c r="W16" t="n">
+        <v>30.53520034536186</v>
       </c>
       <c r="X16" t="n">
         <v>-13256.57052013853</v>
@@ -3232,7 +3140,7 @@
         <v>391.6535537013432</v>
       </c>
       <c r="Z16" t="n">
-        <v>99.24499999999995</v>
+        <v>106803197.7981032</v>
       </c>
       <c r="AA16" t="n">
         <v>3.622292421104758e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>87.96101903435023</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 28.088x + -12033.088</t>
-        </is>
+      <c r="W17" t="n">
+        <v>28.08833991609548</v>
       </c>
       <c r="X17" t="n">
         <v>-12033.08820502537</v>
@@ -3284,7 +3190,7 @@
         <v>388.8202918079034</v>
       </c>
       <c r="Z17" t="n">
-        <v>100.254</v>
+        <v>106321943.3405277</v>
       </c>
       <c r="AA17" t="n">
         <v>3.602866626102672e-07</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>88.06409994133189</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 29.585x + -12606.354</t>
-        </is>
+      <c r="W18" t="n">
+        <v>29.58519181281325</v>
       </c>
       <c r="X18" t="n">
         <v>-12606.35367654404</v>
@@ -3336,7 +3240,7 @@
         <v>385.9786399679244</v>
       </c>
       <c r="Z18" t="n">
-        <v>103.455</v>
+        <v>104982839.9092089</v>
       </c>
       <c r="AA18" t="n">
         <v>3.597788761976473e-07</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>88.08612077263473</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 29.926x + -12652.627</t>
-        </is>
+      <c r="W19" t="n">
+        <v>29.92585269978194</v>
       </c>
       <c r="X19" t="n">
         <v>-12652.62730287282</v>
@@ -3388,7 +3290,7 @@
         <v>383.193660630813</v>
       </c>
       <c r="Z19" t="n">
-        <v>101.533</v>
+        <v>158330930.3102843</v>
       </c>
       <c r="AA19" t="n">
         <v>3.581488370121684e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>88.17568511874825</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 31.396x + -13197.963</t>
-        </is>
+      <c r="W20" t="n">
+        <v>31.39612385328766</v>
       </c>
       <c r="X20" t="n">
         <v>-13197.96299407448</v>
@@ -3440,7 +3340,7 @@
         <v>380.3892537577049</v>
       </c>
       <c r="Z20" t="n">
-        <v>99.31200000000001</v>
+        <v>122669349.6537943</v>
       </c>
       <c r="AA20" t="n">
         <v>3.566569641173602e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>88.08851357296426</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 29.963x + -12456.513</t>
-        </is>
+      <c r="W21" t="n">
+        <v>29.96334177061874</v>
       </c>
       <c r="X21" t="n">
         <v>-12456.51290675694</v>
@@ -3492,7 +3390,7 @@
         <v>377.6029800248166</v>
       </c>
       <c r="Z21" t="n">
-        <v>99.928</v>
+        <v>264623826.9931263</v>
       </c>
       <c r="AA21" t="n">
         <v>3.553098167449959e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>88.15884904291873</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 31.109x + -12847.917</t>
-        </is>
+      <c r="W22" t="n">
+        <v>31.10883258305458</v>
       </c>
       <c r="X22" t="n">
         <v>-12847.91731832053</v>
@@ -3544,7 +3440,7 @@
         <v>374.7994787884469</v>
       </c>
       <c r="Z22" t="n">
-        <v>97.21699999999998</v>
+        <v>103380966.1128163</v>
       </c>
       <c r="AA22" t="n">
         <v>3.535345658232639e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.98650107467778</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.399x + -5628.870</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.39911969021538</v>
       </c>
       <c r="X2" t="n">
         <v>-5628.87012266916</v>
@@ -3742,7 +3636,7 @@
         <v>419.1303278562062</v>
       </c>
       <c r="Z2" t="n">
-        <v>380.9300000000001</v>
+        <v>237956021.5373747</v>
       </c>
       <c r="AA2" t="n">
         <v>6.480821461489034e-07</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>86.26403278851514</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.315x + -6739.300</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.31452287733149</v>
       </c>
       <c r="X3" t="n">
         <v>-6739.300166576242</v>
@@ -3794,7 +3686,7 @@
         <v>394.8625556246611</v>
       </c>
       <c r="Z3" t="n">
-        <v>280.449</v>
+        <v>215315559.1440443</v>
       </c>
       <c r="AA3" t="n">
         <v>5.237797684194312e-07</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>86.74681597819193</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.593x + -7506.888</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.59328562237409</v>
       </c>
       <c r="X4" t="n">
         <v>-7506.888128436009</v>
@@ -3846,7 +3736,7 @@
         <v>387.3357926059832</v>
       </c>
       <c r="Z4" t="n">
-        <v>238.361</v>
+        <v>738117220.2832026</v>
       </c>
       <c r="AA4" t="n">
         <v>4.798370131338431e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>86.84154626007687</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.122x + -7557.433</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.12207346971224</v>
       </c>
       <c r="X5" t="n">
         <v>-7557.432651308401</v>
@@ -3898,7 +3786,7 @@
         <v>382.6967082059697</v>
       </c>
       <c r="Z5" t="n">
-        <v>215.98</v>
+        <v>416303536.7261785</v>
       </c>
       <c r="AA5" t="n">
         <v>4.544229231216149e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>87.3257801807214</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.410x + -8910.350</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.40967156011307</v>
       </c>
       <c r="X6" t="n">
         <v>-8910.349587609531</v>
@@ -3950,7 +3836,7 @@
         <v>378.3127078468118</v>
       </c>
       <c r="Z6" t="n">
-        <v>192.5579999999999</v>
+        <v>835726160.7478653</v>
       </c>
       <c r="AA6" t="n">
         <v>4.368865707032969e-07</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>87.44871536883718</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.443x + -9214.317</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.44277477716732</v>
       </c>
       <c r="X7" t="n">
         <v>-9214.317363509028</v>
@@ -4002,7 +3886,7 @@
         <v>373.7850177928881</v>
       </c>
       <c r="Z7" t="n">
-        <v>180.6729999999999</v>
+        <v>101714626.979459</v>
       </c>
       <c r="AA7" t="n">
         <v>4.24173743246501e-07</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>87.53264740503607</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 23.207x + -9385.325</t>
-        </is>
+      <c r="W8" t="n">
+        <v>23.20720504156621</v>
       </c>
       <c r="X8" t="n">
         <v>-9385.325435555385</v>
@@ -4054,7 +3936,7 @@
         <v>369.097428751326</v>
       </c>
       <c r="Z8" t="n">
-        <v>171.162</v>
+        <v>100454669.8107652</v>
       </c>
       <c r="AA8" t="n">
         <v>4.140593860886103e-07</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>87.65431667172342</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 24.412x + -9752.118</t>
-        </is>
+      <c r="W9" t="n">
+        <v>24.41240237640588</v>
       </c>
       <c r="X9" t="n">
         <v>-9752.118087275996</v>
@@ -4106,7 +3986,7 @@
         <v>364.4769137966321</v>
       </c>
       <c r="Z9" t="n">
-        <v>162.43</v>
+        <v>395702668.9113705</v>
       </c>
       <c r="AA9" t="n">
         <v>4.06252290539382e-07</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>87.4022985224036</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 22.041x + -8582.619</t>
-        </is>
+      <c r="W10" t="n">
+        <v>22.04122222861748</v>
       </c>
       <c r="X10" t="n">
         <v>-8582.618510701705</v>
@@ -4158,7 +4036,7 @@
         <v>360.0930713471144</v>
       </c>
       <c r="Z10" t="n">
-        <v>162.006</v>
+        <v>195787986.5454111</v>
       </c>
       <c r="AA10" t="n">
         <v>3.997722683862532e-07</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>87.72653360673159</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 25.189x + -9770.345</t>
-        </is>
+      <c r="W11" t="n">
+        <v>25.18871910416521</v>
       </c>
       <c r="X11" t="n">
         <v>-9770.344659172164</v>
@@ -4210,7 +4086,7 @@
         <v>356.0744743652321</v>
       </c>
       <c r="Z11" t="n">
-        <v>149.661</v>
+        <v>199362276.6665109</v>
       </c>
       <c r="AA11" t="n">
         <v>3.930753301313009e-07</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.91999548823703</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.019x + -7342.529</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.0193231526774</v>
       </c>
       <c r="X2" t="n">
         <v>-7342.52900072193</v>
@@ -4408,7 +4282,7 @@
         <v>454.4833827394576</v>
       </c>
       <c r="Z2" t="n">
-        <v>302.482</v>
+        <v>187116064.863457</v>
       </c>
       <c r="AA2" t="n">
         <v>6.053319565383948e-07</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>87.22616082429083</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 20.640x + -10390.833</t>
-        </is>
+      <c r="W3" t="n">
+        <v>20.639628307175</v>
       </c>
       <c r="X3" t="n">
         <v>-10390.83339015991</v>
@@ -4460,7 +4332,7 @@
         <v>444.3433854461406</v>
       </c>
       <c r="Z3" t="n">
-        <v>193.322</v>
+        <v>227310339.0631462</v>
       </c>
       <c r="AA3" t="n">
         <v>4.806494654655304e-07</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>87.45954092620003</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 22.539x + -11150.890</t>
-        </is>
+      <c r="W4" t="n">
+        <v>22.53853554475871</v>
       </c>
       <c r="X4" t="n">
         <v>-11150.89014368775</v>
@@ -4512,7 +4382,7 @@
         <v>439.8004021319067</v>
       </c>
       <c r="Z4" t="n">
-        <v>162.029</v>
+        <v>390233521.0034816</v>
       </c>
       <c r="AA4" t="n">
         <v>4.478198723949327e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>87.53414503506045</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 23.221x + -11336.898</t>
-        </is>
+      <c r="W5" t="n">
+        <v>23.22131730709238</v>
       </c>
       <c r="X5" t="n">
         <v>-11336.89800182589</v>
@@ -4564,7 +4432,7 @@
         <v>435.8094655228695</v>
       </c>
       <c r="Z5" t="n">
-        <v>149.549</v>
+        <v>238000145.2117721</v>
       </c>
       <c r="AA5" t="n">
         <v>4.322508734925884e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>87.74917473387549</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 25.442x + -12337.346</t>
-        </is>
+      <c r="W6" t="n">
+        <v>25.44235809931627</v>
       </c>
       <c r="X6" t="n">
         <v>-12337.34640091743</v>
@@ -4616,7 +4482,7 @@
         <v>431.6658538150863</v>
       </c>
       <c r="Z6" t="n">
-        <v>137.68</v>
+        <v>353424793.0110175</v>
       </c>
       <c r="AA6" t="n">
         <v>4.219761535761566e-07</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>87.71348244619193</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 25.045x + -11976.821</t>
-        </is>
+      <c r="W7" t="n">
+        <v>25.04479354257609</v>
       </c>
       <c r="X7" t="n">
         <v>-11976.82073371826</v>
@@ -4668,7 +4532,7 @@
         <v>427.4226578433824</v>
       </c>
       <c r="Z7" t="n">
-        <v>132.2180000000001</v>
+        <v>175691224.9325576</v>
       </c>
       <c r="AA7" t="n">
         <v>4.141469311108859e-07</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>87.69605277979372</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 24.855x + -11729.212</t>
-        </is>
+      <c r="W8" t="n">
+        <v>24.85512427709604</v>
       </c>
       <c r="X8" t="n">
         <v>-11729.21161930763</v>
@@ -4720,7 +4582,7 @@
         <v>423.3585406084665</v>
       </c>
       <c r="Z8" t="n">
-        <v>126.747</v>
+        <v>117607723.5857834</v>
       </c>
       <c r="AA8" t="n">
         <v>4.074363927913332e-07</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>87.7401998997705</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 25.341x + -11836.717</t>
-        </is>
+      <c r="W9" t="n">
+        <v>25.34120910511185</v>
       </c>
       <c r="X9" t="n">
         <v>-11836.7168398624</v>
@@ -4772,7 +4632,7 @@
         <v>419.5172831610098</v>
       </c>
       <c r="Z9" t="n">
-        <v>126.2839999999999</v>
+        <v>343081960.8524319</v>
       </c>
       <c r="AA9" t="n">
         <v>4.035195149594637e-07</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>87.6356424929412</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 24.219x + -11153.355</t>
-        </is>
+      <c r="W10" t="n">
+        <v>24.21937175877649</v>
       </c>
       <c r="X10" t="n">
         <v>-11153.35516706003</v>
@@ -4824,7 +4682,7 @@
         <v>415.9383678094663</v>
       </c>
       <c r="Z10" t="n">
-        <v>123.458</v>
+        <v>429213198.5914063</v>
       </c>
       <c r="AA10" t="n">
         <v>3.985999351391694e-07</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>87.78529593462031</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 25.858x + -11838.617</t>
-        </is>
+      <c r="W11" t="n">
+        <v>25.8577396104478</v>
       </c>
       <c r="X11" t="n">
         <v>-11838.61701463857</v>
@@ -4876,7 +4732,7 @@
         <v>412.5809664772147</v>
       </c>
       <c r="Z11" t="n">
-        <v>119.3849999999999</v>
+        <v>899655013.5080864</v>
       </c>
       <c r="AA11" t="n">
         <v>3.952566190074919e-07</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>87.84936577478415</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 26.629x + -12099.651</t>
-        </is>
+      <c r="W12" t="n">
+        <v>26.6288278269505</v>
       </c>
       <c r="X12" t="n">
         <v>-12099.65098283132</v>
@@ -4928,7 +4782,7 @@
         <v>409.317182516985</v>
       </c>
       <c r="Z12" t="n">
-        <v>114.622</v>
+        <v>334834501.7323543</v>
       </c>
       <c r="AA12" t="n">
         <v>3.909901082707743e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>87.86399750088029</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 26.811x + -12075.262</t>
-        </is>
+      <c r="W13" t="n">
+        <v>26.81140751899467</v>
       </c>
       <c r="X13" t="n">
         <v>-12075.26208024579</v>
@@ -4980,7 +4832,7 @@
         <v>406.1401869914395</v>
       </c>
       <c r="Z13" t="n">
-        <v>115.45</v>
+        <v>222870366.8784933</v>
       </c>
       <c r="AA13" t="n">
         <v>3.892524334501335e-07</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>87.85234410351843</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 26.666x + -11892.427</t>
-        </is>
+      <c r="W14" t="n">
+        <v>26.66579086864423</v>
       </c>
       <c r="X14" t="n">
         <v>-11892.42657330367</v>
@@ -5032,7 +4882,7 @@
         <v>403.0748855677115</v>
       </c>
       <c r="Z14" t="n">
-        <v>112.47</v>
+        <v>348849294.0173115</v>
       </c>
       <c r="AA14" t="n">
         <v>3.858002570018155e-07</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>87.78208836734723</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 25.820x + -11390.898</t>
-        </is>
+      <c r="W15" t="n">
+        <v>25.82030657160209</v>
       </c>
       <c r="X15" t="n">
         <v>-11390.89846302218</v>
@@ -5084,7 +4932,7 @@
         <v>400.0886233086401</v>
       </c>
       <c r="Z15" t="n">
-        <v>111.931</v>
+        <v>108984313.132315</v>
       </c>
       <c r="AA15" t="n">
         <v>3.835552427151432e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>87.94582166090663</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 27.880x + -12253.841</t>
-        </is>
+      <c r="W16" t="n">
+        <v>27.88035848616979</v>
       </c>
       <c r="X16" t="n">
         <v>-12253.84147005952</v>
@@ -5136,7 +4982,7 @@
         <v>397.0504871857528</v>
       </c>
       <c r="Z16" t="n">
-        <v>109.052</v>
+        <v>216152544.8316074</v>
       </c>
       <c r="AA16" t="n">
         <v>3.812783269214345e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>87.94780186405562</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 27.907x + -12158.414</t>
-        </is>
+      <c r="W17" t="n">
+        <v>27.90728380479156</v>
       </c>
       <c r="X17" t="n">
         <v>-12158.414116309</v>
@@ -5188,7 +5032,7 @@
         <v>394.0754869934265</v>
       </c>
       <c r="Z17" t="n">
-        <v>108.99</v>
+        <v>323781627.2760304</v>
       </c>
       <c r="AA17" t="n">
         <v>3.792557680674301e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>87.9343229594916</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 27.725x + -11970.203</t>
-        </is>
+      <c r="W18" t="n">
+        <v>27.72502753962861</v>
       </c>
       <c r="X18" t="n">
         <v>-11970.20292691997</v>
@@ -5240,7 +5082,7 @@
         <v>391.2051689590616</v>
       </c>
       <c r="Z18" t="n">
-        <v>110.14</v>
+        <v>107339580.1232407</v>
       </c>
       <c r="AA18" t="n">
         <v>3.77760869651101e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>87.87411261549317</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 26.939x + -11512.475</t>
-        </is>
+      <c r="W19" t="n">
+        <v>26.9390959888367</v>
       </c>
       <c r="X19" t="n">
         <v>-11512.47549531506</v>
@@ -5292,7 +5132,7 @@
         <v>388.3791891831955</v>
       </c>
       <c r="Z19" t="n">
-        <v>104.009</v>
+        <v>211220147.9162743</v>
       </c>
       <c r="AA19" t="n">
         <v>3.743627944763477e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>87.9132204823778</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 27.444x + -11638.896</t>
-        </is>
+      <c r="W20" t="n">
+        <v>27.44441493183694</v>
       </c>
       <c r="X20" t="n">
         <v>-11638.89637173298</v>
@@ -5344,7 +5182,7 @@
         <v>385.5153749469669</v>
       </c>
       <c r="Z20" t="n">
-        <v>106.473</v>
+        <v>105835037.7178549</v>
       </c>
       <c r="AA20" t="n">
         <v>3.736006616054055e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>87.98631334448017</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 28.441x + -11981.094</t>
-        </is>
+      <c r="W21" t="n">
+        <v>28.44145923289737</v>
       </c>
       <c r="X21" t="n">
         <v>-11981.09387389747</v>
@@ -5396,7 +5232,7 @@
         <v>382.6047261406154</v>
       </c>
       <c r="Z21" t="n">
-        <v>103.8749999999999</v>
+        <v>156162063.6326108</v>
       </c>
       <c r="AA21" t="n">
         <v>3.716763761359019e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>88.10965037978816</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 30.299x + -12706.022</t>
-        </is>
+      <c r="W22" t="n">
+        <v>30.29862204706572</v>
       </c>
       <c r="X22" t="n">
         <v>-12706.02240559245</v>
@@ -5448,7 +5282,7 @@
         <v>379.749870447119</v>
       </c>
       <c r="Z22" t="n">
-        <v>101.895</v>
+        <v>154933492.0837362</v>
       </c>
       <c r="AA22" t="n">
         <v>3.70021274462572e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>84.30208605106759</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.022x + -4753.425</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.02240022290733</v>
       </c>
       <c r="X2" t="n">
         <v>-4753.424589584552</v>
@@ -5646,7 +5478,7 @@
         <v>407.9444048816297</v>
       </c>
       <c r="Z2" t="n">
-        <v>415.287</v>
+        <v>332515989.0284235</v>
       </c>
       <c r="AA2" t="n">
         <v>7.164514322357864e-07</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.91565009022914</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.004x + -6004.551</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.00435722688345</v>
       </c>
       <c r="X3" t="n">
         <v>-6004.551330662123</v>
@@ -5698,7 +5528,7 @@
         <v>386.2412426836281</v>
       </c>
       <c r="Z3" t="n">
-        <v>300.403</v>
+        <v>111598513.6450507</v>
       </c>
       <c r="AA3" t="n">
         <v>5.628143140030422e-07</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>86.50723530051565</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.384x + -6831.824</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.38380869726791</v>
       </c>
       <c r="X4" t="n">
         <v>-6831.823986951316</v>
@@ -5750,7 +5578,7 @@
         <v>379.3038843014611</v>
       </c>
       <c r="Z4" t="n">
-        <v>254.292</v>
+        <v>413031317.0144475</v>
       </c>
       <c r="AA4" t="n">
         <v>5.088121567821781e-07</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>86.85070831700442</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.175x + -7452.966</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.17490180102939</v>
       </c>
       <c r="X5" t="n">
         <v>-7452.965955708944</v>
@@ -5802,7 +5628,7 @@
         <v>374.5719261859737</v>
       </c>
       <c r="Z5" t="n">
-        <v>223.92</v>
+        <v>152892436.3082632</v>
       </c>
       <c r="AA5" t="n">
         <v>4.766402512075581e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>87.15456286429219</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 20.119x + -8163.711</t>
-        </is>
+      <c r="W6" t="n">
+        <v>20.11946334980769</v>
       </c>
       <c r="X6" t="n">
         <v>-8163.710795533659</v>
@@ -5854,7 +5678,7 @@
         <v>369.9265806455115</v>
       </c>
       <c r="Z6" t="n">
-        <v>203.7020000000001</v>
+        <v>301771025.1762537</v>
       </c>
       <c r="AA6" t="n">
         <v>4.561796761078541e-07</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>87.2028090156015</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 20.467x + -8138.085</t>
-        </is>
+      <c r="W7" t="n">
+        <v>20.46705169477937</v>
       </c>
       <c r="X7" t="n">
         <v>-8138.084730669253</v>
@@ -5906,7 +5728,7 @@
         <v>365.090233529936</v>
       </c>
       <c r="Z7" t="n">
-        <v>189.032</v>
+        <v>694411073.1949362</v>
       </c>
       <c r="AA7" t="n">
         <v>4.400790055181719e-07</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>87.3724872257356</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 21.791x + -8556.790</t>
-        </is>
+      <c r="W8" t="n">
+        <v>21.79080140932779</v>
       </c>
       <c r="X8" t="n">
         <v>-8556.790384070811</v>
@@ -5958,7 +5778,7 @@
         <v>360.2783639012237</v>
       </c>
       <c r="Z8" t="n">
-        <v>177.703</v>
+        <v>192911236.803858</v>
       </c>
       <c r="AA8" t="n">
         <v>4.28346261217713e-07</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>87.40992378631864</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 22.106x + -8532.472</t>
-        </is>
+      <c r="W9" t="n">
+        <v>22.10620114261691</v>
       </c>
       <c r="X9" t="n">
         <v>-8532.471943589499</v>
@@ -6010,7 +5828,7 @@
         <v>355.6587425423492</v>
       </c>
       <c r="Z9" t="n">
-        <v>169.3899999999999</v>
+        <v>193140130.2899781</v>
       </c>
       <c r="AA9" t="n">
         <v>4.18716131799048e-07</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>87.45605437544947</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 22.508x + -8558.562</t>
-        </is>
+      <c r="W10" t="n">
+        <v>22.50760528192265</v>
       </c>
       <c r="X10" t="n">
         <v>-8558.562107446602</v>
@@ -6062,7 +5878,7 @@
         <v>351.3973577719283</v>
       </c>
       <c r="Z10" t="n">
-        <v>163.521</v>
+        <v>285939520.9280819</v>
       </c>
       <c r="AA10" t="n">
         <v>4.115268052404907e-07</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>87.35327508706726</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 21.632x + -8073.836</t>
-        </is>
+      <c r="W11" t="n">
+        <v>21.63240278869427</v>
       </c>
       <c r="X11" t="n">
         <v>-8073.835542757663</v>
@@ -6114,7 +5928,7 @@
         <v>347.5386268559336</v>
       </c>
       <c r="Z11" t="n">
-        <v>158.2640000000001</v>
+        <v>282811632.505776</v>
       </c>
       <c r="AA11" t="n">
         <v>4.051327352762345e-07</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>86.30431200438761</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 15.482x + -7987.922</t>
-        </is>
+      <c r="W2" t="n">
+        <v>15.48190698759758</v>
       </c>
       <c r="X2" t="n">
         <v>-7987.922226105684</v>
@@ -6312,7 +6124,7 @@
         <v>446.0148829950641</v>
       </c>
       <c r="Z2" t="n">
-        <v>261.571</v>
+        <v>84978574.93709195</v>
       </c>
       <c r="AA2" t="n">
         <v>5.775022325785147e-07</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>87.31236314362366</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 21.303x + -10453.379</t>
-        </is>
+      <c r="W3" t="n">
+        <v>21.30263589032044</v>
       </c>
       <c r="X3" t="n">
         <v>-10453.37906471734</v>
@@ -6364,7 +6174,7 @@
         <v>434.2343672011721</v>
       </c>
       <c r="Z3" t="n">
-        <v>177.236</v>
+        <v>177951294.6077994</v>
       </c>
       <c r="AA3" t="n">
         <v>4.748872196471541e-07</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>87.3468866723552</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 21.580x + -10342.095</t>
-        </is>
+      <c r="W4" t="n">
+        <v>21.58023999929786</v>
       </c>
       <c r="X4" t="n">
         <v>-10342.09511917656</v>
@@ -6416,7 +6224,7 @@
         <v>429.2795170630448</v>
       </c>
       <c r="Z4" t="n">
-        <v>157.1960000000001</v>
+        <v>351478646.8944843</v>
       </c>
       <c r="AA4" t="n">
         <v>4.489664134397564e-07</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>87.4567537694181</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 22.514x + -10665.842</t>
-        </is>
+      <c r="W5" t="n">
+        <v>22.51380302556043</v>
       </c>
       <c r="X5" t="n">
         <v>-10665.8415541838</v>
@@ -6468,7 +6274,7 @@
         <v>425.1959236977404</v>
       </c>
       <c r="Z5" t="n">
-        <v>145.2930000000001</v>
+        <v>235351636.5837735</v>
       </c>
       <c r="AA5" t="n">
         <v>4.359411526968289e-07</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>87.58175752045857</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 23.679x + -11109.854</t>
-        </is>
+      <c r="W6" t="n">
+        <v>23.67907861706804</v>
       </c>
       <c r="X6" t="n">
         <v>-11109.85438935966</v>
@@ -6520,7 +6324,7 @@
         <v>420.9383043666102</v>
       </c>
       <c r="Z6" t="n">
-        <v>136.829</v>
+        <v>344486988.1805056</v>
       </c>
       <c r="AA6" t="n">
         <v>4.272586588934582e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>87.68095563085834</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 24.693x + -11470.745</t>
-        </is>
+      <c r="W7" t="n">
+        <v>24.69314046551235</v>
       </c>
       <c r="X7" t="n">
         <v>-11470.74473171246</v>
@@ -6572,7 +6374,7 @@
         <v>416.6609056134988</v>
       </c>
       <c r="Z7" t="n">
-        <v>129.434</v>
+        <v>454622194.7657275</v>
       </c>
       <c r="AA7" t="n">
         <v>4.196190617590498e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>87.59691453622732</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 23.829x + -10899.961</t>
-        </is>
+      <c r="W8" t="n">
+        <v>23.82860697059664</v>
       </c>
       <c r="X8" t="n">
         <v>-10899.96096864557</v>
@@ -6624,7 +6424,7 @@
         <v>412.5604978648525</v>
       </c>
       <c r="Z8" t="n">
-        <v>129.434</v>
+        <v>112641204.4043455</v>
       </c>
       <c r="AA8" t="n">
         <v>4.14776932130355e-07</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>87.85833213739475</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 26.740x + -12184.708</t>
-        </is>
+      <c r="W9" t="n">
+        <v>26.74041733935464</v>
       </c>
       <c r="X9" t="n">
         <v>-12184.70842095018</v>
@@ -6676,7 +6474,7 @@
         <v>408.678924756534</v>
       </c>
       <c r="Z9" t="n">
-        <v>122.062</v>
+        <v>111774879.4283397</v>
       </c>
       <c r="AA9" t="n">
         <v>4.096945883440376e-07</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>87.7208202390443</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 25.126x + -11277.142</t>
-        </is>
+      <c r="W10" t="n">
+        <v>25.1255105000614</v>
       </c>
       <c r="X10" t="n">
         <v>-11277.14185148296</v>
@@ -6728,7 +6524,7 @@
         <v>405.128482187097</v>
       </c>
       <c r="Z10" t="n">
-        <v>121.4230000000001</v>
+        <v>331854691.1554563</v>
       </c>
       <c r="AA10" t="n">
         <v>4.061919148170452e-07</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>87.72867139211171</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 25.212x + -11202.344</t>
-        </is>
+      <c r="W11" t="n">
+        <v>25.212451738592</v>
       </c>
       <c r="X11" t="n">
         <v>-11202.34366021609</v>
@@ -6780,7 +6574,7 @@
         <v>401.7374751353441</v>
       </c>
       <c r="Z11" t="n">
-        <v>118.37</v>
+        <v>437438252.4191567</v>
       </c>
       <c r="AA11" t="n">
         <v>4.01959212551893e-07</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>87.79845730324153</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 26.012x + -11467.553</t>
-        </is>
+      <c r="W12" t="n">
+        <v>26.01247722288106</v>
       </c>
       <c r="X12" t="n">
         <v>-11467.55342588361</v>
@@ -6832,7 +6624,7 @@
         <v>398.4736651690069</v>
       </c>
       <c r="Z12" t="n">
-        <v>117.152</v>
+        <v>217053205.7063066</v>
       </c>
       <c r="AA12" t="n">
         <v>3.994986912557351e-07</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>87.86654852666324</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 26.843x + -11745.343</t>
-        </is>
+      <c r="W13" t="n">
+        <v>26.8434963518308</v>
       </c>
       <c r="X13" t="n">
         <v>-11745.34269629697</v>
@@ -6884,7 +6674,7 @@
         <v>395.2619056066575</v>
       </c>
       <c r="Z13" t="n">
-        <v>114.402</v>
+        <v>221882014.0315479</v>
       </c>
       <c r="AA13" t="n">
         <v>3.96724520288062e-07</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>87.83201676099829</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 26.416x + -11435.601</t>
-        </is>
+      <c r="W14" t="n">
+        <v>26.41553287888622</v>
       </c>
       <c r="X14" t="n">
         <v>-11435.6013890905</v>
@@ -6936,7 +6724,7 @@
         <v>392.0273051280593</v>
       </c>
       <c r="Z14" t="n">
-        <v>114.677</v>
+        <v>106739280.8172119</v>
       </c>
       <c r="AA14" t="n">
         <v>3.943063813999103e-07</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>87.85722191856998</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 26.727x + -11468.043</t>
-        </is>
+      <c r="W15" t="n">
+        <v>26.72654964426845</v>
       </c>
       <c r="X15" t="n">
         <v>-11468.04262855224</v>
@@ -6988,7 +6774,7 @@
         <v>388.8272275192413</v>
       </c>
       <c r="Z15" t="n">
-        <v>109.143</v>
+        <v>216422567.0752833</v>
       </c>
       <c r="AA15" t="n">
         <v>3.906950124330994e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>87.91231771813393</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 27.433x + -11676.233</t>
-        </is>
+      <c r="W16" t="n">
+        <v>27.43253680021083</v>
       </c>
       <c r="X16" t="n">
         <v>-11676.23337937664</v>
@@ -7040,7 +6824,7 @@
         <v>385.6623818984777</v>
       </c>
       <c r="Z16" t="n">
-        <v>106.725</v>
+        <v>217053825.2136868</v>
       </c>
       <c r="AA16" t="n">
         <v>3.88113878768437e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>87.81897619692099</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 26.257x + -11042.483</t>
-        </is>
+      <c r="W17" t="n">
+        <v>26.25744040055866</v>
       </c>
       <c r="X17" t="n">
         <v>-11042.48341330128</v>
@@ -7092,7 +6874,7 @@
         <v>382.5544036487379</v>
       </c>
       <c r="Z17" t="n">
-        <v>108.109</v>
+        <v>156182389.0318249</v>
       </c>
       <c r="AA17" t="n">
         <v>3.866932251064737e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>87.09435177645804</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 19.702x + -8057.979</t>
-        </is>
+      <c r="W18" t="n">
+        <v>19.70185256947746</v>
       </c>
       <c r="X18" t="n">
         <v>-8057.979069796295</v>
@@ -7144,7 +6924,7 @@
         <v>379.4769297440737</v>
       </c>
       <c r="Z18" t="n">
-        <v>115.366</v>
+        <v>515933647.3736491</v>
       </c>
       <c r="AA18" t="n">
         <v>3.850403723704442e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>87.98796477474913</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 28.465x + -11809.416</t>
-        </is>
+      <c r="W19" t="n">
+        <v>28.46482252698918</v>
       </c>
       <c r="X19" t="n">
         <v>-11809.41632763514</v>
@@ -7196,7 +6974,7 @@
         <v>376.4565916099552</v>
       </c>
       <c r="Z19" t="n">
-        <v>103.657</v>
+        <v>103033300.711237</v>
       </c>
       <c r="AA19" t="n">
         <v>3.824612640744002e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>87.97144659451202</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 28.233x + -11595.304</t>
-        </is>
+      <c r="W20" t="n">
+        <v>28.23284666278051</v>
       </c>
       <c r="X20" t="n">
         <v>-11595.30394880118</v>
@@ -7248,7 +7024,7 @@
         <v>373.3676814466969</v>
       </c>
       <c r="Z20" t="n">
-        <v>103.911</v>
+        <v>101526739.8696273</v>
       </c>
       <c r="AA20" t="n">
         <v>3.809198333641624e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>87.51577827187131</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 23.049x + -9258.846</t>
-        </is>
+      <c r="W21" t="n">
+        <v>23.04942061376361</v>
       </c>
       <c r="X21" t="n">
         <v>-9258.845952607056</v>
@@ -7300,7 +7074,7 @@
         <v>370.3318818464714</v>
       </c>
       <c r="Z21" t="n">
-        <v>108.898</v>
+        <v>111811650.035345</v>
       </c>
       <c r="AA21" t="n">
         <v>3.792846845877749e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>88.00158543006893</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 28.659x + -11563.321</t>
-        </is>
+      <c r="W22" t="n">
+        <v>28.65899013826956</v>
       </c>
       <c r="X22" t="n">
         <v>-11563.32149353308</v>
@@ -7352,7 +7124,7 @@
         <v>367.3208433238416</v>
       </c>
       <c r="Z22" t="n">
-        <v>102.782</v>
+        <v>349314556.1951188</v>
       </c>
       <c r="AA22" t="n">
         <v>3.779635824933687e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>84.58138443730105</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.542x + -5076.239</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.54233489030185</v>
       </c>
       <c r="X2" t="n">
         <v>-5076.239441812922</v>
@@ -7550,7 +7320,7 @@
         <v>407.9722052818478</v>
       </c>
       <c r="Z2" t="n">
-        <v>393.725</v>
+        <v>664932994.7204992</v>
       </c>
       <c r="AA2" t="n">
         <v>7.207750306963229e-07</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>86.10257211204122</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.678x + -6259.777</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.67823969356871</v>
       </c>
       <c r="X3" t="n">
         <v>-6259.776557979794</v>
@@ -7602,7 +7370,7 @@
         <v>384.2056505935366</v>
       </c>
       <c r="Z3" t="n">
-        <v>278.3680000000001</v>
+        <v>160366462.3266262</v>
       </c>
       <c r="AA3" t="n">
         <v>5.498404646487141e-07</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>86.85636092540231</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 18.208x + -7592.345</t>
-        </is>
+      <c r="W4" t="n">
+        <v>18.20764812775504</v>
       </c>
       <c r="X4" t="n">
         <v>-7592.345015751976</v>
@@ -7654,7 +7420,7 @@
         <v>377.1802059422451</v>
       </c>
       <c r="Z4" t="n">
-        <v>227.635</v>
+        <v>205446605.1174258</v>
       </c>
       <c r="AA4" t="n">
         <v>4.943888532198906e-07</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>87.12585401084098</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 19.918x + -8153.215</t>
-        </is>
+      <c r="W5" t="n">
+        <v>19.91816448159312</v>
       </c>
       <c r="X5" t="n">
         <v>-8153.215156702091</v>
@@ -7706,7 +7470,7 @@
         <v>372.7751086175262</v>
       </c>
       <c r="Z5" t="n">
-        <v>198.654</v>
+        <v>101512622.2244934</v>
       </c>
       <c r="AA5" t="n">
         <v>4.637422447401791e-07</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>87.30968270270574</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.281x + -8592.884</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.28138027621788</v>
       </c>
       <c r="X6" t="n">
         <v>-8592.884326206267</v>
@@ -7758,7 +7520,7 @@
         <v>368.6221191779746</v>
       </c>
       <c r="Z6" t="n">
-        <v>181.672</v>
+        <v>302451889.9287871</v>
       </c>
       <c r="AA6" t="n">
         <v>4.449715321288874e-07</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>87.35629203936875</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 21.657x + -8593.149</t>
-        </is>
+      <c r="W7" t="n">
+        <v>21.65712443419743</v>
       </c>
       <c r="X7" t="n">
         <v>-8593.148600568107</v>
@@ -7810,7 +7570,7 @@
         <v>364.2640681413171</v>
       </c>
       <c r="Z7" t="n">
-        <v>168.712</v>
+        <v>396827873.48667</v>
       </c>
       <c r="AA7" t="n">
         <v>4.308082413939267e-07</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>87.47807250315246</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 22.704x + -8896.116</t>
-        </is>
+      <c r="W8" t="n">
+        <v>22.70436923196747</v>
       </c>
       <c r="X8" t="n">
         <v>-8896.116349278796</v>
@@ -7862,7 +7620,7 @@
         <v>359.8727291974537</v>
       </c>
       <c r="Z8" t="n">
-        <v>158.627</v>
+        <v>390775907.6157731</v>
       </c>
       <c r="AA8" t="n">
         <v>4.206757934116415e-07</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>87.62764350509046</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 24.138x + -9358.576</t>
-        </is>
+      <c r="W9" t="n">
+        <v>24.13761720802264</v>
       </c>
       <c r="X9" t="n">
         <v>-9358.576339660338</v>
@@ -7914,7 +7670,7 @@
         <v>355.6000456648105</v>
       </c>
       <c r="Z9" t="n">
-        <v>152.704</v>
+        <v>385922392.4631255</v>
       </c>
       <c r="AA9" t="n">
         <v>4.134157118207357e-07</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>87.55097369441968</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 23.381x + -8897.997</t>
-        </is>
+      <c r="W10" t="n">
+        <v>23.38108078055718</v>
       </c>
       <c r="X10" t="n">
         <v>-8897.997046131297</v>
@@ -7966,7 +7720,7 @@
         <v>351.5281863840216</v>
       </c>
       <c r="Z10" t="n">
-        <v>145.009</v>
+        <v>477110066.2016164</v>
       </c>
       <c r="AA10" t="n">
         <v>4.061003800676828e-07</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>87.7410947813129</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 25.351x + -9576.223</t>
-        </is>
+      <c r="W11" t="n">
+        <v>25.35125862392669</v>
       </c>
       <c r="X11" t="n">
         <v>-9576.223069857489</v>
@@ -8018,7 +7770,7 @@
         <v>347.6232157561738</v>
       </c>
       <c r="Z11" t="n">
-        <v>140.537</v>
+        <v>422618805.0285129</v>
       </c>
       <c r="AA11" t="n">
         <v>4.012325572343066e-07</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>86.34408499697118</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 15.651x + -8041.755</t>
-        </is>
+      <c r="W2" t="n">
+        <v>15.65080144821873</v>
       </c>
       <c r="X2" t="n">
         <v>-8041.755187989226</v>
@@ -8216,7 +7966,7 @@
         <v>446.0615595429655</v>
       </c>
       <c r="Z2" t="n">
-        <v>248.224</v>
+        <v>49464944.57555766</v>
       </c>
       <c r="AA2" t="n">
         <v>5.718361790685231e-07</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>87.17115866982472</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 20.238x + -9910.927</t>
-        </is>
+      <c r="W3" t="n">
+        <v>20.23769081315276</v>
       </c>
       <c r="X3" t="n">
         <v>-9910.926835935528</v>
@@ -8268,7 +8016,7 @@
         <v>434.7989703482187</v>
       </c>
       <c r="Z3" t="n">
-        <v>174.905</v>
+        <v>712446686.4799011</v>
       </c>
       <c r="AA3" t="n">
         <v>4.7944172539051e-07</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>87.38250855412426</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 21.874x + -10531.451</t>
-        </is>
+      <c r="W4" t="n">
+        <v>21.87434653623128</v>
       </c>
       <c r="X4" t="n">
         <v>-10531.45082497798</v>
@@ -8320,7 +8066,7 @@
         <v>429.7643533837178</v>
       </c>
       <c r="Z4" t="n">
-        <v>151.73</v>
+        <v>176218480.1840758</v>
       </c>
       <c r="AA4" t="n">
         <v>4.528820728558591e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>87.49667151033833</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 22.873x + -10873.962</t>
-        </is>
+      <c r="W5" t="n">
+        <v>22.87327340244075</v>
       </c>
       <c r="X5" t="n">
         <v>-10873.96235495501</v>
@@ -8372,7 +8116,7 @@
         <v>425.250014563747</v>
       </c>
       <c r="Z5" t="n">
-        <v>140.738</v>
+        <v>348281728.977523</v>
       </c>
       <c r="AA5" t="n">
         <v>4.389175667214527e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>87.43192785567331</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 22.296x + -10421.739</t>
-        </is>
+      <c r="W6" t="n">
+        <v>22.29587139013903</v>
       </c>
       <c r="X6" t="n">
         <v>-10421.73861125145</v>
@@ -8424,7 +8166,7 @@
         <v>420.4541593279544</v>
       </c>
       <c r="Z6" t="n">
-        <v>133.039</v>
+        <v>344473786.5084239</v>
       </c>
       <c r="AA6" t="n">
         <v>4.292759090466947e-07</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>87.53207240313291</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 23.202x + -10718.833</t>
-        </is>
+      <c r="W7" t="n">
+        <v>23.20179130868673</v>
       </c>
       <c r="X7" t="n">
         <v>-10718.83333377476</v>
@@ -8476,7 +8216,7 @@
         <v>415.4928506164291</v>
       </c>
       <c r="Z7" t="n">
-        <v>127.572</v>
+        <v>905917161.1646137</v>
       </c>
       <c r="AA7" t="n">
         <v>4.218264874034907e-07</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>87.59404176537804</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 23.800x + -10854.508</t>
-        </is>
+      <c r="W8" t="n">
+        <v>23.80012163804978</v>
       </c>
       <c r="X8" t="n">
         <v>-10854.50825440769</v>
@@ -8528,7 +8266,7 @@
         <v>410.6932870237622</v>
       </c>
       <c r="Z8" t="n">
-        <v>124.5119999999999</v>
+        <v>448082915.096775</v>
       </c>
       <c r="AA8" t="n">
         <v>4.162164143340568e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>87.80924670836981</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 26.141x + -11833.508</t>
-        </is>
+      <c r="W9" t="n">
+        <v>26.14071389635892</v>
       </c>
       <c r="X9" t="n">
         <v>-11833.50793657148</v>
@@ -8580,7 +8316,7 @@
         <v>406.1558589451604</v>
       </c>
       <c r="Z9" t="n">
-        <v>118.5140000000001</v>
+        <v>332301901.3206196</v>
       </c>
       <c r="AA9" t="n">
         <v>4.109958591551783e-07</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>87.71843829331985</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 25.099x + -11191.991</t>
-        </is>
+      <c r="W10" t="n">
+        <v>25.09925181224669</v>
       </c>
       <c r="X10" t="n">
         <v>-11191.99089146436</v>
@@ -8632,7 +8366,7 @@
         <v>401.9571716444201</v>
       </c>
       <c r="Z10" t="n">
-        <v>119.23</v>
+        <v>227694574.6184389</v>
       </c>
       <c r="AA10" t="n">
         <v>4.069792562363318e-07</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>87.72565101633602</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 25.179x + -11088.938</t>
-        </is>
+      <c r="W11" t="n">
+        <v>25.17893402795078</v>
       </c>
       <c r="X11" t="n">
         <v>-11088.9380627502</v>
@@ -8684,7 +8416,7 @@
         <v>398.0315089045411</v>
       </c>
       <c r="Z11" t="n">
-        <v>115.397</v>
+        <v>162656832.7226542</v>
       </c>
       <c r="AA11" t="n">
         <v>4.029520022061135e-07</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>87.81329754196575</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 26.189x + -11435.848</t>
-        </is>
+      <c r="W12" t="n">
+        <v>26.18918636428014</v>
       </c>
       <c r="X12" t="n">
         <v>-11435.84828978607</v>
@@ -8736,7 +8466,7 @@
         <v>394.3663317785396</v>
       </c>
       <c r="Z12" t="n">
-        <v>115.532</v>
+        <v>322183951.9662494</v>
       </c>
       <c r="AA12" t="n">
         <v>4.005688885956205e-07</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>87.78284089096459</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 25.829x + -11145.944</t>
-        </is>
+      <c r="W13" t="n">
+        <v>25.82907897366553</v>
       </c>
       <c r="X13" t="n">
         <v>-11145.94417561867</v>
@@ -8788,7 +8516,7 @@
         <v>390.8797159972684</v>
       </c>
       <c r="Z13" t="n">
-        <v>111.609</v>
+        <v>159626181.9120257</v>
       </c>
       <c r="AA13" t="n">
         <v>3.965582726027328e-07</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>87.92232514794816</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 27.565x + -11825.718</t>
-        </is>
+      <c r="W14" t="n">
+        <v>27.56478643485267</v>
       </c>
       <c r="X14" t="n">
         <v>-11825.7179390845</v>
@@ -8840,7 +8566,7 @@
         <v>387.5367382017457</v>
       </c>
       <c r="Z14" t="n">
-        <v>105.909</v>
+        <v>211283577.515597</v>
       </c>
       <c r="AA14" t="n">
         <v>3.934330596012159e-07</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>87.79026631901429</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 25.916x + -10963.163</t>
-        </is>
+      <c r="W15" t="n">
+        <v>25.9159596897849</v>
       </c>
       <c r="X15" t="n">
         <v>-10963.16330667192</v>
@@ -8892,7 +8616,7 @@
         <v>384.2435141102533</v>
       </c>
       <c r="Z15" t="n">
-        <v>109.815</v>
+        <v>157013075.8890429</v>
       </c>
       <c r="AA15" t="n">
         <v>3.919390020539939e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>87.93441783095179</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 27.726x + -11663.678</t>
-        </is>
+      <c r="W16" t="n">
+        <v>27.72630204445711</v>
       </c>
       <c r="X16" t="n">
         <v>-11663.67757229711</v>
@@ -8944,7 +8666,7 @@
         <v>381.0008670321984</v>
       </c>
       <c r="Z16" t="n">
-        <v>106.6619999999999</v>
+        <v>103747707.3303173</v>
       </c>
       <c r="AA16" t="n">
         <v>3.892789259204391e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>87.90393481292853</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 27.323x + -11367.490</t>
-        </is>
+      <c r="W17" t="n">
+        <v>27.32272703207274</v>
       </c>
       <c r="X17" t="n">
         <v>-11367.48987197617</v>
@@ -8996,7 +8716,7 @@
         <v>377.7220627897996</v>
       </c>
       <c r="Z17" t="n">
-        <v>105.321</v>
+        <v>514012192.685697</v>
       </c>
       <c r="AA17" t="n">
         <v>3.873320049307927e-07</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>87.9064504720627</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 27.356x + -11271.295</t>
-        </is>
+      <c r="W18" t="n">
+        <v>27.35558796752993</v>
       </c>
       <c r="X18" t="n">
         <v>-11271.29471457049</v>
@@ -9048,7 +8766,7 @@
         <v>374.5527151661101</v>
       </c>
       <c r="Z18" t="n">
-        <v>104.587</v>
+        <v>212232685.4184781</v>
       </c>
       <c r="AA18" t="n">
         <v>3.85349753708965e-07</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>87.97865480775026</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 28.334x + -11585.463</t>
-        </is>
+      <c r="W19" t="n">
+        <v>28.33361037370389</v>
       </c>
       <c r="X19" t="n">
         <v>-11585.46290314838</v>
@@ -9100,7 +8816,7 @@
         <v>371.3988009369948</v>
       </c>
       <c r="Z19" t="n">
-        <v>102.743</v>
+        <v>302960231.9717601</v>
       </c>
       <c r="AA19" t="n">
         <v>3.833658351484886e-07</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>87.91287197858743</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 27.440x + -11087.491</t>
-        </is>
+      <c r="W20" t="n">
+        <v>27.43982827175756</v>
       </c>
       <c r="X20" t="n">
         <v>-11087.49140504981</v>
@@ -9152,7 +8866,7 @@
         <v>368.2134716012623</v>
       </c>
       <c r="Z20" t="n">
-        <v>101.33</v>
+        <v>400428346.9202821</v>
       </c>
       <c r="AA20" t="n">
         <v>3.806417972160746e-07</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>87.93871331944476</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 27.784x + -11127.632</t>
-        </is>
+      <c r="W21" t="n">
+        <v>27.78413056553261</v>
       </c>
       <c r="X21" t="n">
         <v>-11127.63190125026</v>
@@ -9204,7 +8916,7 @@
         <v>365.0742796957069</v>
       </c>
       <c r="Z21" t="n">
-        <v>100.533</v>
+        <v>198553279.7935685</v>
       </c>
       <c r="AA21" t="n">
         <v>3.792317453037878e-07</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>87.99303877125151</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 28.537x + -11332.965</t>
-        </is>
+      <c r="W22" t="n">
+        <v>28.53684637346715</v>
       </c>
       <c r="X22" t="n">
         <v>-11332.96529429052</v>
@@ -9256,7 +8966,7 @@
         <v>361.9240765072328</v>
       </c>
       <c r="Z22" t="n">
-        <v>99.27299999999997</v>
+        <v>99000463.198246</v>
       </c>
       <c r="AA22" t="n">
         <v>3.773292748369564e-07</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>84.89641936567848</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.197x + -5404.923</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.19687740708324</v>
       </c>
       <c r="X2" t="n">
         <v>-5404.922887160995</v>
@@ -9454,7 +9162,7 @@
         <v>407.7407320082067</v>
       </c>
       <c r="Z2" t="n">
-        <v>375.6270000000001</v>
+        <v>337489321.5219505</v>
       </c>
       <c r="AA2" t="n">
         <v>6.504215717871749e-07</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>86.56053363199396</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.638x + -7005.263</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.63831917910231</v>
       </c>
       <c r="X3" t="n">
         <v>-7005.26348855395</v>
@@ -9506,7 +9212,7 @@
         <v>380.7046700202453</v>
       </c>
       <c r="Z3" t="n">
-        <v>250.0069999999999</v>
+        <v>206907814.4940717</v>
       </c>
       <c r="AA3" t="n">
         <v>4.936258015863929e-07</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>87.14506056677826</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 20.052x + -8202.643</t>
-        </is>
+      <c r="W4" t="n">
+        <v>20.05238789549495</v>
       </c>
       <c r="X4" t="n">
         <v>-8202.642918390571</v>
@@ -9558,7 +9262,7 @@
         <v>373.3274848692083</v>
       </c>
       <c r="Z4" t="n">
-        <v>203.114</v>
+        <v>205592457.0210522</v>
       </c>
       <c r="AA4" t="n">
         <v>4.481677780507303e-07</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>87.38244622427608</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 21.874x + -8793.680</t>
-        </is>
+      <c r="W5" t="n">
+        <v>21.87382493336156</v>
       </c>
       <c r="X5" t="n">
         <v>-8793.679850124627</v>
@@ -9610,7 +9312,7 @@
         <v>368.4710785370489</v>
       </c>
       <c r="Z5" t="n">
-        <v>178.4640000000001</v>
+        <v>200433486.6227811</v>
       </c>
       <c r="AA5" t="n">
         <v>4.242455604650512e-07</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>87.58863587287293</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 23.747x + -9406.969</t>
-        </is>
+      <c r="W6" t="n">
+        <v>23.74670272912869</v>
       </c>
       <c r="X6" t="n">
         <v>-9406.968541564451</v>
@@ -9662,7 +9362,7 @@
         <v>363.6699620977606</v>
       </c>
       <c r="Z6" t="n">
-        <v>157.437</v>
+        <v>641576592.0366459</v>
       </c>
       <c r="AA6" t="n">
         <v>4.078205554322477e-07</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>87.45309475640305</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.481x + -8700.101</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.48141600116517</v>
       </c>
       <c r="X7" t="n">
         <v>-8700.101075581944</v>
@@ -9714,7 +9412,7 @@
         <v>358.5567049748257</v>
       </c>
       <c r="Z7" t="n">
-        <v>150.675</v>
+        <v>194574662.7637895</v>
       </c>
       <c r="AA7" t="n">
         <v>3.980646115841885e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>87.50780406106331</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 22.976x + -8746.054</t>
-        </is>
+      <c r="W8" t="n">
+        <v>22.97557735749044</v>
       </c>
       <c r="X8" t="n">
         <v>-8746.053549221731</v>
@@ -9766,7 +9462,7 @@
         <v>353.2594697064274</v>
       </c>
       <c r="Z8" t="n">
-        <v>146.104</v>
+        <v>191884537.7166275</v>
       </c>
       <c r="AA8" t="n">
         <v>3.91681072647163e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>87.56832152919188</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 23.548x + -8815.579</t>
-        </is>
+      <c r="W9" t="n">
+        <v>23.54808634414038</v>
       </c>
       <c r="X9" t="n">
         <v>-8815.579496827868</v>
@@ -9818,7 +9512,7 @@
         <v>348.1448526875594</v>
       </c>
       <c r="Z9" t="n">
-        <v>137.07</v>
+        <v>188760106.866369</v>
       </c>
       <c r="AA9" t="n">
         <v>3.848303036038166e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>87.93266750370438</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 27.703x + -10328.277</t>
-        </is>
+      <c r="W10" t="n">
+        <v>27.70280693916595</v>
       </c>
       <c r="X10" t="n">
         <v>-10328.27698914494</v>
@@ -9870,7 +9562,7 @@
         <v>343.3575751524845</v>
       </c>
       <c r="Z10" t="n">
-        <v>130.099</v>
+        <v>93097461.29632474</v>
       </c>
       <c r="AA10" t="n">
         <v>3.806756731335172e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>87.62702090976043</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 24.131x + -8761.432</t>
-        </is>
+      <c r="W11" t="n">
+        <v>24.1312770089516</v>
       </c>
       <c r="X11" t="n">
         <v>-8761.431537887789</v>
@@ -9922,7 +9612,7 @@
         <v>338.9885421096196</v>
       </c>
       <c r="Z11" t="n">
-        <v>129.637</v>
+        <v>298561497.6883295</v>
       </c>
       <c r="AA11" t="n">
         <v>3.764243893188474e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-192.894</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-167.724</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-156.5880000000001</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-146.3920000000001</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-140.352</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-137.215</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-133.602</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-131.738</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-128.581</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-124.093</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-380.9300000000001</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-280.449</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-238.361</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-215.98</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-192.5579999999999</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-180.6729999999999</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-171.162</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-162.43</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-162.006</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-149.661</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-415.287</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-300.403</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-254.292</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-223.92</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-203.7020000000001</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-189.032</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-177.703</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-169.3899999999999</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-163.521</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-158.2640000000001</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-393.725</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-278.3680000000001</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-227.635</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-198.654</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-181.672</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-168.712</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-158.627</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-152.704</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-145.009</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-140.537</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-375.6270000000001</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-250.0069999999999</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-203.114</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-178.4640000000001</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-157.437</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-150.675</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-146.104</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-137.07</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-130.099</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-129.637</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-192.894</v>
+        <v>117.903</v>
       </c>
       <c r="D2" t="n">
         <v>2.90149e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-167.724</v>
+        <v>113.654</v>
       </c>
       <c r="D3" t="n">
         <v>2.8692e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-156.5880000000001</v>
+        <v>107.958</v>
       </c>
       <c r="D4" t="n">
         <v>2.8499e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-146.3920000000001</v>
+        <v>103.58</v>
       </c>
       <c r="D5" t="n">
         <v>2.83647e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-140.352</v>
+        <v>102.116</v>
       </c>
       <c r="D6" t="n">
         <v>2.82578e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-137.215</v>
+        <v>95.48899999999998</v>
       </c>
       <c r="D7" t="n">
         <v>2.81836e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-133.602</v>
+        <v>94.00800000000004</v>
       </c>
       <c r="D8" t="n">
         <v>2.8107e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-131.738</v>
+        <v>89.97500000000002</v>
       </c>
       <c r="D9" t="n">
         <v>2.80569e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-128.581</v>
+        <v>88.03399999999999</v>
       </c>
       <c r="D10" t="n">
         <v>2.80002e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-124.093</v>
+        <v>85.86799999999999</v>
       </c>
       <c r="D11" t="n">
         <v>2.79627e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-152.723</v>
+        <v>124.576</v>
       </c>
       <c r="D2" t="n">
         <v>2.93127e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-131.984</v>
+        <v>102.115</v>
       </c>
       <c r="D3" t="n">
         <v>2.92917e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-129.28</v>
+        <v>95.654</v>
       </c>
       <c r="D4" t="n">
         <v>2.9212e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-124.1009999999999</v>
+        <v>92.30600000000004</v>
       </c>
       <c r="D5" t="n">
         <v>2.91187e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-119.293</v>
+        <v>91.33499999999998</v>
       </c>
       <c r="D6" t="n">
         <v>2.90558e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-117.867</v>
+        <v>88.60599999999999</v>
       </c>
       <c r="D7" t="n">
         <v>2.90046e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-116.985</v>
+        <v>86.69299999999998</v>
       </c>
       <c r="D8" t="n">
         <v>2.89592e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-113.1130000000001</v>
+        <v>84.95099999999996</v>
       </c>
       <c r="D9" t="n">
         <v>2.89145e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-113.2769999999999</v>
+        <v>84.07600000000002</v>
       </c>
       <c r="D10" t="n">
         <v>2.88963e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-110.489</v>
+        <v>82.34000000000003</v>
       </c>
       <c r="D11" t="n">
         <v>2.88777e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-111.1540000000001</v>
+        <v>79.61699999999996</v>
       </c>
       <c r="D12" t="n">
         <v>2.88503e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-110.27</v>
+        <v>78.13599999999997</v>
       </c>
       <c r="D13" t="n">
         <v>2.88355e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-107.432</v>
+        <v>77.274</v>
       </c>
       <c r="D14" t="n">
         <v>2.88254e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-106.785</v>
+        <v>76.548</v>
       </c>
       <c r="D15" t="n">
         <v>2.88131e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-106.9449999999999</v>
+        <v>74.05900000000003</v>
       </c>
       <c r="D16" t="n">
         <v>2.87906e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-112.684</v>
+        <v>66.12599999999998</v>
       </c>
       <c r="D17" t="n">
         <v>2.87923e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-102.746</v>
+        <v>72.68599999999998</v>
       </c>
       <c r="D18" t="n">
         <v>2.87619e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-103.851</v>
+        <v>71.12200000000001</v>
       </c>
       <c r="D19" t="n">
         <v>2.87722e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-103.498</v>
+        <v>70.23500000000001</v>
       </c>
       <c r="D20" t="n">
         <v>2.87617e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-103.721</v>
+        <v>68.12400000000002</v>
       </c>
       <c r="D21" t="n">
         <v>2.87411e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-98.95100000000002</v>
+        <v>67.43799999999999</v>
       </c>
       <c r="D22" t="n">
         <v>2.87422e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-185.812</v>
+        <v>130.665</v>
       </c>
       <c r="D2" t="n">
         <v>2.86232e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-135.001</v>
+        <v>107.914</v>
       </c>
       <c r="D3" t="n">
         <v>2.8313e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-126.095</v>
+        <v>100.812</v>
       </c>
       <c r="D4" t="n">
         <v>2.82244e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-117.0359999999999</v>
+        <v>99.36799999999999</v>
       </c>
       <c r="D5" t="n">
         <v>2.81385e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-114.115</v>
+        <v>98.72300000000001</v>
       </c>
       <c r="D6" t="n">
         <v>2.80933e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-111.591</v>
+        <v>94.12</v>
       </c>
       <c r="D7" t="n">
         <v>2.8037e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-113.765</v>
+        <v>91.20599999999996</v>
       </c>
       <c r="D8" t="n">
         <v>2.79929e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-111.04</v>
+        <v>88.53199999999998</v>
       </c>
       <c r="D9" t="n">
         <v>2.79486e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-108.559</v>
+        <v>88.53300000000002</v>
       </c>
       <c r="D10" t="n">
         <v>2.79076e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-108.541</v>
+        <v>84.98000000000002</v>
       </c>
       <c r="D11" t="n">
         <v>2.78869e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-106.826</v>
+        <v>84.505</v>
       </c>
       <c r="D12" t="n">
         <v>2.78439e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-104.324</v>
+        <v>81.95299999999997</v>
       </c>
       <c r="D13" t="n">
         <v>2.78444e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-102.521</v>
+        <v>82.452</v>
       </c>
       <c r="D14" t="n">
         <v>2.78023e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-102.628</v>
+        <v>80.90600000000001</v>
       </c>
       <c r="D15" t="n">
         <v>2.77878e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-99.24499999999995</v>
+        <v>80.49200000000002</v>
       </c>
       <c r="D16" t="n">
         <v>2.77814e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-100.254</v>
+        <v>77.25700000000001</v>
       </c>
       <c r="D17" t="n">
         <v>2.77535e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-103.455</v>
+        <v>76.15100000000001</v>
       </c>
       <c r="D18" t="n">
         <v>2.77327e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-101.533</v>
+        <v>75.38399999999996</v>
       </c>
       <c r="D19" t="n">
         <v>2.77195e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-99.31200000000001</v>
+        <v>75.06399999999996</v>
       </c>
       <c r="D20" t="n">
         <v>2.77176e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-99.928</v>
+        <v>72.54699999999997</v>
       </c>
       <c r="D21" t="n">
         <v>2.77071e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-97.21699999999998</v>
+        <v>72.42900000000003</v>
       </c>
       <c r="D22" t="n">
         <v>2.76954e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-380.9300000000001</v>
+        <v>122.949</v>
       </c>
       <c r="D2" t="n">
         <v>3.18192e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-280.449</v>
+        <v>81.48099999999999</v>
       </c>
       <c r="D3" t="n">
         <v>3.16511e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-238.361</v>
+        <v>72.35199999999998</v>
       </c>
       <c r="D4" t="n">
         <v>3.11561e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-215.98</v>
+        <v>65.51499999999999</v>
       </c>
       <c r="D5" t="n">
         <v>3.0739e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-192.5579999999999</v>
+        <v>67.685</v>
       </c>
       <c r="D6" t="n">
         <v>3.04238e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-180.6729999999999</v>
+        <v>66.01600000000002</v>
       </c>
       <c r="D7" t="n">
         <v>3.0168e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-171.162</v>
+        <v>63.15200000000004</v>
       </c>
       <c r="D8" t="n">
         <v>2.99736e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-162.43</v>
+        <v>61.90700000000004</v>
       </c>
       <c r="D9" t="n">
         <v>2.98304e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-162.006</v>
+        <v>55.04500000000002</v>
       </c>
       <c r="D10" t="n">
         <v>2.96941e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-149.661</v>
+        <v>56.73999999999995</v>
       </c>
       <c r="D11" t="n">
         <v>2.95913e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-302.482</v>
+        <v>126.205</v>
       </c>
       <c r="D2" t="n">
         <v>3.13678e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-193.322</v>
+        <v>110.425</v>
       </c>
       <c r="D3" t="n">
         <v>3.01041e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-162.029</v>
+        <v>103.639</v>
       </c>
       <c r="D4" t="n">
         <v>2.9619e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-149.549</v>
+        <v>100.742</v>
       </c>
       <c r="D5" t="n">
         <v>2.93403e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-137.68</v>
+        <v>99.96199999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2.91834e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-132.2180000000001</v>
+        <v>96.36699999999996</v>
       </c>
       <c r="D7" t="n">
         <v>2.90634e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-126.747</v>
+        <v>93.42700000000002</v>
       </c>
       <c r="D8" t="n">
         <v>2.89732e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-126.2839999999999</v>
+        <v>90.64200000000005</v>
       </c>
       <c r="D9" t="n">
         <v>2.89073e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-123.458</v>
+        <v>87.065</v>
       </c>
       <c r="D10" t="n">
         <v>2.88377e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-119.3849999999999</v>
+        <v>87.048</v>
       </c>
       <c r="D11" t="n">
         <v>2.87984e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-114.622</v>
+        <v>85.93200000000002</v>
       </c>
       <c r="D12" t="n">
         <v>2.87379e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-115.45</v>
+        <v>84.14599999999996</v>
       </c>
       <c r="D13" t="n">
         <v>2.87175e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-112.47</v>
+        <v>82.01800000000003</v>
       </c>
       <c r="D14" t="n">
         <v>2.86733e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-111.931</v>
+        <v>79.80900000000003</v>
       </c>
       <c r="D15" t="n">
         <v>2.86526e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-109.052</v>
+        <v>80.65700000000004</v>
       </c>
       <c r="D16" t="n">
         <v>2.8616e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-108.99</v>
+        <v>78.88200000000001</v>
       </c>
       <c r="D17" t="n">
         <v>2.85864e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-110.14</v>
+        <v>77.33299999999997</v>
       </c>
       <c r="D18" t="n">
         <v>2.85582e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-104.009</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="D19" t="n">
         <v>2.85464e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-106.473</v>
+        <v>73.96099999999996</v>
       </c>
       <c r="D20" t="n">
         <v>2.85318e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-103.8749999999999</v>
+        <v>73.87</v>
       </c>
       <c r="D21" t="n">
         <v>2.85219e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-101.895</v>
+        <v>73.55000000000001</v>
       </c>
       <c r="D22" t="n">
         <v>2.85043e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-415.287</v>
+        <v>110.528</v>
       </c>
       <c r="D2" t="n">
         <v>3.33264e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-300.403</v>
+        <v>76.30899999999997</v>
       </c>
       <c r="D3" t="n">
         <v>3.29263e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-254.292</v>
+        <v>68.392</v>
       </c>
       <c r="D4" t="n">
         <v>3.22555e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-223.92</v>
+        <v>64.28699999999998</v>
       </c>
       <c r="D5" t="n">
         <v>3.17461e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-203.7020000000001</v>
+        <v>63.44399999999996</v>
       </c>
       <c r="D6" t="n">
         <v>3.13556e-07</v>
@@ -5654,7 +5654,7 @@
         <v>0.3140501217841745</v>
       </c>
       <c r="G6" t="n">
-        <v>1.025257334128238</v>
+        <v>1.025257334128248</v>
       </c>
       <c r="H6" t="n">
         <v>1.533797163636335</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-189.032</v>
+        <v>59.33799999999997</v>
       </c>
       <c r="D7" t="n">
         <v>3.10572e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-177.703</v>
+        <v>58.24900000000002</v>
       </c>
       <c r="D8" t="n">
         <v>3.08217e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-169.3899999999999</v>
+        <v>54.84800000000001</v>
       </c>
       <c r="D9" t="n">
         <v>3.06404e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-163.521</v>
+        <v>52.55900000000003</v>
       </c>
       <c r="D10" t="n">
         <v>3.04952e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-158.2640000000001</v>
+        <v>48.81099999999998</v>
       </c>
       <c r="D11" t="n">
         <v>3.03864e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-261.571</v>
+        <v>124.96</v>
       </c>
       <c r="D2" t="n">
         <v>3.15126e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-177.236</v>
+        <v>104.848</v>
       </c>
       <c r="D3" t="n">
         <v>3.04695e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-157.1960000000001</v>
+        <v>96.53099999999995</v>
       </c>
       <c r="D4" t="n">
         <v>3.00868e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-145.2930000000001</v>
+        <v>94.52999999999997</v>
       </c>
       <c r="D5" t="n">
         <v>2.98863e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-136.829</v>
+        <v>92.78500000000003</v>
       </c>
       <c r="D6" t="n">
         <v>2.97582e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-129.434</v>
+        <v>90.541</v>
       </c>
       <c r="D7" t="n">
         <v>2.96574e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-129.434</v>
+        <v>86.721</v>
       </c>
       <c r="D8" t="n">
         <v>2.95844e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-122.062</v>
+        <v>87.43799999999999</v>
       </c>
       <c r="D9" t="n">
         <v>2.9517e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-121.4230000000001</v>
+        <v>83.87699999999995</v>
       </c>
       <c r="D10" t="n">
         <v>2.94842e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-118.37</v>
+        <v>81.40099999999995</v>
       </c>
       <c r="D11" t="n">
         <v>2.94245e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-117.152</v>
+        <v>80.79599999999999</v>
       </c>
       <c r="D12" t="n">
         <v>2.93913e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-114.402</v>
+        <v>80.49299999999999</v>
       </c>
       <c r="D13" t="n">
         <v>2.93662e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-114.677</v>
+        <v>78.20999999999998</v>
       </c>
       <c r="D14" t="n">
         <v>2.93307e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-109.143</v>
+        <v>76.49799999999999</v>
       </c>
       <c r="D15" t="n">
         <v>2.93089e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-106.725</v>
+        <v>76.19900000000001</v>
       </c>
       <c r="D16" t="n">
         <v>2.92741e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-108.109</v>
+        <v>73.32600000000002</v>
       </c>
       <c r="D17" t="n">
         <v>2.92711e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-115.366</v>
+        <v>64.48699999999997</v>
       </c>
       <c r="D18" t="n">
         <v>2.92538e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-103.657</v>
+        <v>71.99799999999999</v>
       </c>
       <c r="D19" t="n">
         <v>2.92352e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-103.911</v>
+        <v>70.68600000000004</v>
       </c>
       <c r="D20" t="n">
         <v>2.92278e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-108.898</v>
+        <v>64.14300000000003</v>
       </c>
       <c r="D21" t="n">
         <v>2.92051e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-102.782</v>
+        <v>68.22300000000001</v>
       </c>
       <c r="D22" t="n">
         <v>2.92126e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-393.725</v>
+        <v>119.722</v>
       </c>
       <c r="D2" t="n">
         <v>3.35159e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-278.3680000000001</v>
+        <v>76.97699999999998</v>
       </c>
       <c r="D3" t="n">
         <v>3.28991e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-227.635</v>
+        <v>70.84300000000002</v>
       </c>
       <c r="D4" t="n">
         <v>3.21697e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-198.654</v>
+        <v>66.61000000000001</v>
       </c>
       <c r="D5" t="n">
         <v>3.16364e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-181.672</v>
+        <v>63.959</v>
       </c>
       <c r="D6" t="n">
         <v>3.12615e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-168.712</v>
+        <v>59.96599999999995</v>
       </c>
       <c r="D7" t="n">
         <v>3.09917e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-158.627</v>
+        <v>58.38999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>3.07858e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-152.704</v>
+        <v>57.78399999999999</v>
       </c>
       <c r="D9" t="n">
         <v>3.06218e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-145.009</v>
+        <v>54.15499999999997</v>
       </c>
       <c r="D10" t="n">
         <v>3.05109e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-140.537</v>
+        <v>54.13499999999999</v>
       </c>
       <c r="D11" t="n">
         <v>3.04068e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-248.224</v>
+        <v>123.476</v>
       </c>
       <c r="D2" t="n">
         <v>3.16062e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-174.905</v>
+        <v>105.87</v>
       </c>
       <c r="D3" t="n">
         <v>3.06331e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-151.73</v>
+        <v>100.762</v>
       </c>
       <c r="D4" t="n">
         <v>3.02365e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-140.738</v>
+        <v>97.35000000000002</v>
       </c>
       <c r="D5" t="n">
         <v>3.00137e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-133.039</v>
+        <v>93.16399999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2.98912e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-127.572</v>
+        <v>91.79200000000003</v>
       </c>
       <c r="D7" t="n">
         <v>2.97741e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-124.5119999999999</v>
+        <v>88.84000000000003</v>
       </c>
       <c r="D8" t="n">
         <v>2.97057e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-118.5140000000001</v>
+        <v>87.959</v>
       </c>
       <c r="D9" t="n">
         <v>2.96572e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-119.23</v>
+        <v>84.37299999999999</v>
       </c>
       <c r="D10" t="n">
         <v>2.95921e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-115.397</v>
+        <v>82.64500000000004</v>
       </c>
       <c r="D11" t="n">
         <v>2.95583e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-115.532</v>
+        <v>80.87399999999997</v>
       </c>
       <c r="D12" t="n">
         <v>2.95296e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-111.609</v>
+        <v>78.54899999999998</v>
       </c>
       <c r="D13" t="n">
         <v>2.94949e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-105.909</v>
+        <v>78.85699999999997</v>
       </c>
       <c r="D14" t="n">
         <v>2.94769e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-109.815</v>
+        <v>75.49099999999999</v>
       </c>
       <c r="D15" t="n">
         <v>2.94521e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-106.6619999999999</v>
+        <v>75.44800000000004</v>
       </c>
       <c r="D16" t="n">
         <v>2.94213e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-105.321</v>
+        <v>73.67500000000001</v>
       </c>
       <c r="D17" t="n">
         <v>2.94177e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-104.587</v>
+        <v>72.63799999999998</v>
       </c>
       <c r="D18" t="n">
         <v>2.93998e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-102.743</v>
+        <v>71.65199999999999</v>
       </c>
       <c r="D19" t="n">
         <v>2.93884e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-101.33</v>
+        <v>69.036</v>
       </c>
       <c r="D20" t="n">
         <v>2.93564e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-100.533</v>
+        <v>68.30000000000001</v>
       </c>
       <c r="D21" t="n">
         <v>2.93534e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-99.27299999999997</v>
+        <v>67.17000000000002</v>
       </c>
       <c r="D22" t="n">
         <v>2.93414e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-375.6270000000001</v>
+        <v>119.649</v>
       </c>
       <c r="D2" t="n">
         <v>3.22643e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-250.0069999999999</v>
+        <v>72.42899999999997</v>
       </c>
       <c r="D3" t="n">
         <v>3.16105e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-203.114</v>
+        <v>64.93199999999996</v>
       </c>
       <c r="D4" t="n">
         <v>3.09133e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-178.4640000000001</v>
+        <v>61.55399999999997</v>
       </c>
       <c r="D5" t="n">
         <v>3.04231e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-157.437</v>
+        <v>59.298</v>
       </c>
       <c r="D6" t="n">
         <v>3.01126e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-150.675</v>
+        <v>54.553</v>
       </c>
       <c r="D7" t="n">
         <v>2.99036e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-146.104</v>
+        <v>52.47500000000002</v>
       </c>
       <c r="D8" t="n">
         <v>2.97612e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-137.07</v>
+        <v>50.22800000000001</v>
       </c>
       <c r="D9" t="n">
         <v>2.9661e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-130.099</v>
+        <v>52.488</v>
       </c>
       <c r="D10" t="n">
         <v>2.95805e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-129.637</v>
+        <v>46.024</v>
       </c>
       <c r="D11" t="n">
         <v>2.95183e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>117.903</v>
       </c>
+      <c r="C2" t="n">
+        <v>890.6077851114572</v>
+      </c>
       <c r="D2" t="n">
         <v>2.90149e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>113.654</v>
       </c>
+      <c r="C3" t="n">
+        <v>961.8525654459299</v>
+      </c>
       <c r="D3" t="n">
         <v>2.8692e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>107.958</v>
       </c>
+      <c r="C4" t="n">
+        <v>946.9072113896787</v>
+      </c>
       <c r="D4" t="n">
         <v>2.8499e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>103.58</v>
       </c>
+      <c r="C5" t="n">
+        <v>921.5417389754921</v>
+      </c>
       <c r="D5" t="n">
         <v>2.83647e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>102.116</v>
       </c>
+      <c r="C6" t="n">
+        <v>1020.026812405845</v>
+      </c>
       <c r="D6" t="n">
         <v>2.82578e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>95.48899999999998</v>
       </c>
+      <c r="C7" t="n">
+        <v>928.9390102933918</v>
+      </c>
       <c r="D7" t="n">
         <v>2.81836e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>94.00800000000004</v>
       </c>
+      <c r="C8" t="n">
+        <v>1024.381855985697</v>
+      </c>
       <c r="D8" t="n">
         <v>2.8107e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>89.97500000000002</v>
       </c>
+      <c r="C9" t="n">
+        <v>945.823285707609</v>
+      </c>
       <c r="D9" t="n">
         <v>2.80569e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>88.03399999999999</v>
       </c>
+      <c r="C10" t="n">
+        <v>1006.433763079279</v>
+      </c>
       <c r="D10" t="n">
         <v>2.80002e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>85.86799999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>971.720071086501</v>
       </c>
       <c r="D11" t="n">
         <v>2.79627e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>124.576</v>
       </c>
+      <c r="C2" t="n">
+        <v>1580.24712137046</v>
+      </c>
       <c r="D2" t="n">
         <v>2.93127e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>102.115</v>
       </c>
+      <c r="C3" t="n">
+        <v>909.5667837345769</v>
+      </c>
       <c r="D3" t="n">
         <v>2.92917e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>95.654</v>
       </c>
+      <c r="C4" t="n">
+        <v>842.2759028481145</v>
+      </c>
       <c r="D4" t="n">
         <v>2.9212e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>92.30600000000004</v>
       </c>
+      <c r="C5" t="n">
+        <v>804.6793442753356</v>
+      </c>
       <c r="D5" t="n">
         <v>2.91187e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>91.33499999999998</v>
       </c>
+      <c r="C6" t="n">
+        <v>893.1523794141702</v>
+      </c>
       <c r="D6" t="n">
         <v>2.90558e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>88.60599999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>862.4154699549715</v>
+      </c>
       <c r="D7" t="n">
         <v>2.90046e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>86.69299999999998</v>
       </c>
+      <c r="C8" t="n">
+        <v>886.4238925844998</v>
+      </c>
       <c r="D8" t="n">
         <v>2.89592e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>84.95099999999996</v>
       </c>
+      <c r="C9" t="n">
+        <v>862.7305395388472</v>
+      </c>
       <c r="D9" t="n">
         <v>2.89145e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>84.07600000000002</v>
       </c>
+      <c r="C10" t="n">
+        <v>948.5987199269531</v>
+      </c>
       <c r="D10" t="n">
         <v>2.88963e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>82.34000000000003</v>
       </c>
+      <c r="C11" t="n">
+        <v>956.2520471311615</v>
+      </c>
       <c r="D11" t="n">
         <v>2.88777e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>79.61699999999996</v>
       </c>
+      <c r="C12" t="n">
+        <v>880.1921895346447</v>
+      </c>
       <c r="D12" t="n">
         <v>2.88503e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>78.13599999999997</v>
       </c>
+      <c r="C13" t="n">
+        <v>910.4736548563793</v>
+      </c>
       <c r="D13" t="n">
         <v>2.88355e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>77.274</v>
       </c>
+      <c r="C14" t="n">
+        <v>945.7291628949596</v>
+      </c>
       <c r="D14" t="n">
         <v>2.88254e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>76.548</v>
       </c>
+      <c r="C15" t="n">
+        <v>955.1533662778128</v>
+      </c>
       <c r="D15" t="n">
         <v>2.88131e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>74.05900000000003</v>
       </c>
+      <c r="C16" t="n">
+        <v>916.8962655480937</v>
+      </c>
       <c r="D16" t="n">
         <v>2.87906e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>66.12599999999998</v>
       </c>
+      <c r="C17" t="n">
+        <v>671.2277256029927</v>
+      </c>
       <c r="D17" t="n">
         <v>2.87923e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>72.68599999999998</v>
       </c>
+      <c r="C18" t="n">
+        <v>1022.056529799756</v>
+      </c>
       <c r="D18" t="n">
         <v>2.87619e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>71.12200000000001</v>
       </c>
+      <c r="C19" t="n">
+        <v>960.1921589662089</v>
+      </c>
       <c r="D19" t="n">
         <v>2.87722e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>70.23500000000001</v>
       </c>
+      <c r="C20" t="n">
+        <v>994.1654071516632</v>
+      </c>
       <c r="D20" t="n">
         <v>2.87617e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>68.12400000000002</v>
       </c>
+      <c r="C21" t="n">
+        <v>881.7059512908706</v>
+      </c>
       <c r="D21" t="n">
         <v>2.87411e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>67.43799999999999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1031.773400294225</v>
       </c>
       <c r="D22" t="n">
         <v>2.87422e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>130.665</v>
       </c>
+      <c r="C2" t="n">
+        <v>1637.137769090585</v>
+      </c>
       <c r="D2" t="n">
         <v>2.86232e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>107.914</v>
       </c>
+      <c r="C3" t="n">
+        <v>957.1519682047341</v>
+      </c>
       <c r="D3" t="n">
         <v>2.8313e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>100.812</v>
       </c>
+      <c r="C4" t="n">
+        <v>845.0068402707366</v>
+      </c>
       <c r="D4" t="n">
         <v>2.82244e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>99.36799999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>888.3923006401509</v>
+      </c>
       <c r="D5" t="n">
         <v>2.81385e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>98.72300000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>952.6287203573013</v>
+      </c>
       <c r="D6" t="n">
         <v>2.80933e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>94.12</v>
       </c>
+      <c r="C7" t="n">
+        <v>938.22665299928</v>
+      </c>
       <c r="D7" t="n">
         <v>2.8037e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>91.20599999999996</v>
       </c>
+      <c r="C8" t="n">
+        <v>903.7131018676588</v>
+      </c>
       <c r="D8" t="n">
         <v>2.79929e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>88.53199999999998</v>
       </c>
+      <c r="C9" t="n">
+        <v>866.1331543797737</v>
+      </c>
       <c r="D9" t="n">
         <v>2.79486e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>88.53300000000002</v>
       </c>
+      <c r="C10" t="n">
+        <v>958.861156385086</v>
+      </c>
       <c r="D10" t="n">
         <v>2.79076e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>84.98000000000002</v>
       </c>
+      <c r="C11" t="n">
+        <v>904.8255450214347</v>
+      </c>
       <c r="D11" t="n">
         <v>2.78869e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>84.505</v>
       </c>
+      <c r="C12" t="n">
+        <v>929.3584164985765</v>
+      </c>
       <c r="D12" t="n">
         <v>2.78439e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>81.95299999999997</v>
       </c>
+      <c r="C13" t="n">
+        <v>862.7548870935294</v>
+      </c>
       <c r="D13" t="n">
         <v>2.78444e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>82.452</v>
       </c>
+      <c r="C14" t="n">
+        <v>1007.080401596257</v>
+      </c>
       <c r="D14" t="n">
         <v>2.78023e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>80.90600000000001</v>
       </c>
+      <c r="C15" t="n">
+        <v>973.603821646939</v>
+      </c>
       <c r="D15" t="n">
         <v>2.77878e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>80.49200000000002</v>
       </c>
+      <c r="C16" t="n">
+        <v>1044.613023188647</v>
+      </c>
       <c r="D16" t="n">
         <v>2.77814e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>77.25700000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>899.5130277642623</v>
+      </c>
       <c r="D17" t="n">
         <v>2.77535e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>76.15100000000001</v>
       </c>
+      <c r="C18" t="n">
+        <v>946.7389545860566</v>
+      </c>
       <c r="D18" t="n">
         <v>2.77327e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>75.38399999999996</v>
       </c>
+      <c r="C19" t="n">
+        <v>1030.288769403512</v>
+      </c>
       <c r="D19" t="n">
         <v>2.77195e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>75.06399999999996</v>
       </c>
+      <c r="C20" t="n">
+        <v>1084.648086361616</v>
+      </c>
       <c r="D20" t="n">
         <v>2.77176e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>72.54699999999997</v>
       </c>
+      <c r="C21" t="n">
+        <v>967.2723031797441</v>
+      </c>
       <c r="D21" t="n">
         <v>2.77071e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>72.42900000000003</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1044.834217967165</v>
       </c>
       <c r="D22" t="n">
         <v>2.76954e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>122.949</v>
       </c>
+      <c r="C2" t="n">
+        <v>2550.299560906143</v>
+      </c>
       <c r="D2" t="n">
         <v>3.18192e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>81.48099999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>1655.621172787767</v>
+      </c>
       <c r="D3" t="n">
         <v>3.16511e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>72.35199999999998</v>
       </c>
+      <c r="C4" t="n">
+        <v>1230.409536637037</v>
+      </c>
       <c r="D4" t="n">
         <v>3.11561e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>65.51499999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>806.1722817253687</v>
+      </c>
       <c r="D5" t="n">
         <v>3.0739e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>67.685</v>
       </c>
+      <c r="C6" t="n">
+        <v>1354.263863347428</v>
+      </c>
       <c r="D6" t="n">
         <v>3.04238e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>66.01600000000002</v>
       </c>
+      <c r="C7" t="n">
+        <v>1447.536928530887</v>
+      </c>
       <c r="D7" t="n">
         <v>3.0168e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>63.15200000000004</v>
       </c>
+      <c r="C8" t="n">
+        <v>1483.389288474473</v>
+      </c>
       <c r="D8" t="n">
         <v>2.99736e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>61.90700000000004</v>
       </c>
+      <c r="C9" t="n">
+        <v>1806.448945371396</v>
+      </c>
       <c r="D9" t="n">
         <v>2.98304e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>55.04500000000002</v>
       </c>
+      <c r="C10" t="n">
+        <v>950.2243722006416</v>
+      </c>
       <c r="D10" t="n">
         <v>2.96941e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>56.73999999999995</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1640.406650146062</v>
       </c>
       <c r="D11" t="n">
         <v>2.95913e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>126.205</v>
       </c>
+      <c r="C2" t="n">
+        <v>1311.559720985994</v>
+      </c>
       <c r="D2" t="n">
         <v>3.13678e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>110.425</v>
       </c>
+      <c r="C3" t="n">
+        <v>964.0749334639826</v>
+      </c>
       <c r="D3" t="n">
         <v>3.01041e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>103.639</v>
       </c>
+      <c r="C4" t="n">
+        <v>885.4177058125242</v>
+      </c>
       <c r="D4" t="n">
         <v>2.9619e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>100.742</v>
       </c>
+      <c r="C5" t="n">
+        <v>876.6406963489753</v>
+      </c>
       <c r="D5" t="n">
         <v>2.93403e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>99.96199999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>959.2836576395424</v>
+      </c>
       <c r="D6" t="n">
         <v>2.91834e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>96.36699999999996</v>
       </c>
+      <c r="C7" t="n">
+        <v>942.5768848752332</v>
+      </c>
       <c r="D7" t="n">
         <v>2.90634e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>93.42700000000002</v>
       </c>
+      <c r="C8" t="n">
+        <v>872.968133249761</v>
+      </c>
       <c r="D8" t="n">
         <v>2.89732e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>90.64200000000005</v>
       </c>
+      <c r="C9" t="n">
+        <v>906.5315315749058</v>
+      </c>
       <c r="D9" t="n">
         <v>2.89073e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>87.065</v>
       </c>
+      <c r="C10" t="n">
+        <v>829.2297965750013</v>
+      </c>
       <c r="D10" t="n">
         <v>2.88377e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>87.048</v>
       </c>
+      <c r="C11" t="n">
+        <v>902.4436078541372</v>
+      </c>
       <c r="D11" t="n">
         <v>2.87984e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>85.93200000000002</v>
       </c>
+      <c r="C12" t="n">
+        <v>947.9084758738557</v>
+      </c>
       <c r="D12" t="n">
         <v>2.87379e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>84.14599999999996</v>
       </c>
+      <c r="C13" t="n">
+        <v>936.0933854234609</v>
+      </c>
       <c r="D13" t="n">
         <v>2.87175e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>82.01800000000003</v>
       </c>
+      <c r="C14" t="n">
+        <v>911.382550453404</v>
+      </c>
       <c r="D14" t="n">
         <v>2.86733e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>79.80900000000003</v>
       </c>
+      <c r="C15" t="n">
+        <v>880.9208290548632</v>
+      </c>
       <c r="D15" t="n">
         <v>2.86526e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>80.65700000000004</v>
       </c>
+      <c r="C16" t="n">
+        <v>1000.279642311502</v>
+      </c>
       <c r="D16" t="n">
         <v>2.8616e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>78.88200000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>946.0488517092964</v>
+      </c>
       <c r="D17" t="n">
         <v>2.85864e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>77.33299999999997</v>
       </c>
+      <c r="C18" t="n">
+        <v>950.9904368370363</v>
+      </c>
       <c r="D18" t="n">
         <v>2.85582e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>75.56999999999999</v>
       </c>
+      <c r="C19" t="n">
+        <v>909.3965231402768</v>
+      </c>
       <c r="D19" t="n">
         <v>2.85464e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>73.96099999999996</v>
       </c>
+      <c r="C20" t="n">
+        <v>929.3812815715984</v>
+      </c>
       <c r="D20" t="n">
         <v>2.85318e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>73.87</v>
       </c>
+      <c r="C21" t="n">
+        <v>989.5159088121409</v>
+      </c>
       <c r="D21" t="n">
         <v>2.85219e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>73.55000000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1081.632682110158</v>
       </c>
       <c r="D22" t="n">
         <v>2.85043e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>110.528</v>
       </c>
+      <c r="C2" t="n">
+        <v>2945.058568658877</v>
+      </c>
       <c r="D2" t="n">
         <v>3.33264e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>76.30899999999997</v>
       </c>
+      <c r="C3" t="n">
+        <v>1861.253355109347</v>
+      </c>
       <c r="D3" t="n">
         <v>3.29263e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>68.392</v>
       </c>
+      <c r="C4" t="n">
+        <v>1289.010574430256</v>
+      </c>
       <c r="D4" t="n">
         <v>3.22555e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>64.28699999999998</v>
       </c>
+      <c r="C5" t="n">
+        <v>1107.398247280812</v>
+      </c>
       <c r="D5" t="n">
         <v>3.17461e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>63.44399999999996</v>
       </c>
+      <c r="C6" t="n">
+        <v>1470.096870481593</v>
+      </c>
       <c r="D6" t="n">
         <v>3.13556e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>59.33799999999997</v>
       </c>
+      <c r="C7" t="n">
+        <v>1168.066462900982</v>
+      </c>
       <c r="D7" t="n">
         <v>3.10572e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>58.24900000000002</v>
       </c>
+      <c r="C8" t="n">
+        <v>1392.89107352429</v>
+      </c>
       <c r="D8" t="n">
         <v>3.08217e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>54.84800000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>1201.426277241353</v>
+      </c>
       <c r="D9" t="n">
         <v>3.06404e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>52.55900000000003</v>
       </c>
+      <c r="C10" t="n">
+        <v>1279.387071224094</v>
+      </c>
       <c r="D10" t="n">
         <v>3.04952e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>48.81099999999998</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1006.686458214438</v>
       </c>
       <c r="D11" t="n">
         <v>3.03864e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>124.96</v>
       </c>
+      <c r="C2" t="n">
+        <v>1652.773084991022</v>
+      </c>
       <c r="D2" t="n">
         <v>3.15126e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>104.848</v>
       </c>
+      <c r="C3" t="n">
+        <v>980.2863676036791</v>
+      </c>
       <c r="D3" t="n">
         <v>3.04695e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>96.53099999999995</v>
       </c>
+      <c r="C4" t="n">
+        <v>816.3724175747152</v>
+      </c>
       <c r="D4" t="n">
         <v>3.00868e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>94.52999999999997</v>
       </c>
+      <c r="C5" t="n">
+        <v>810.1952590323924</v>
+      </c>
       <c r="D5" t="n">
         <v>2.98863e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>92.78500000000003</v>
       </c>
+      <c r="C6" t="n">
+        <v>854.3851242670345</v>
+      </c>
       <c r="D6" t="n">
         <v>2.97582e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>90.541</v>
       </c>
+      <c r="C7" t="n">
+        <v>889.5644239351532</v>
+      </c>
       <c r="D7" t="n">
         <v>2.96574e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>86.721</v>
       </c>
+      <c r="C8" t="n">
+        <v>844.9579815557967</v>
+      </c>
       <c r="D8" t="n">
         <v>2.95844e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>87.43799999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>959.0419467918387</v>
+      </c>
       <c r="D9" t="n">
         <v>2.9517e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>83.87699999999995</v>
       </c>
+      <c r="C10" t="n">
+        <v>877.1316939712378</v>
+      </c>
       <c r="D10" t="n">
         <v>2.94842e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>81.40099999999995</v>
       </c>
+      <c r="C11" t="n">
+        <v>870.5978815336495</v>
+      </c>
       <c r="D11" t="n">
         <v>2.94245e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>80.79599999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>861.2099389687762</v>
+      </c>
       <c r="D12" t="n">
         <v>2.93913e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>80.49299999999999</v>
       </c>
+      <c r="C13" t="n">
+        <v>940.394812631066</v>
+      </c>
       <c r="D13" t="n">
         <v>2.93662e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>78.20999999999998</v>
       </c>
+      <c r="C14" t="n">
+        <v>883.556337065977</v>
+      </c>
       <c r="D14" t="n">
         <v>2.93307e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>76.49799999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>902.0030745582178</v>
+      </c>
       <c r="D15" t="n">
         <v>2.93089e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>76.19900000000001</v>
       </c>
+      <c r="C16" t="n">
+        <v>961.8659816921156</v>
+      </c>
       <c r="D16" t="n">
         <v>2.92741e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>73.32600000000002</v>
       </c>
+      <c r="C17" t="n">
+        <v>889.8595155459149</v>
+      </c>
       <c r="D17" t="n">
         <v>2.92711e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>64.48699999999997</v>
       </c>
+      <c r="C18" t="n">
+        <v>670.3729924183323</v>
+      </c>
       <c r="D18" t="n">
         <v>2.92538e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>71.99799999999999</v>
       </c>
+      <c r="C19" t="n">
+        <v>934.442142010436</v>
+      </c>
       <c r="D19" t="n">
         <v>2.92352e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>70.68600000000004</v>
       </c>
+      <c r="C20" t="n">
+        <v>969.192656201164</v>
+      </c>
       <c r="D20" t="n">
         <v>2.92278e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>64.14300000000003</v>
       </c>
+      <c r="C21" t="n">
+        <v>686.3389498796878</v>
+      </c>
       <c r="D21" t="n">
         <v>2.92051e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>68.22300000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>959.5968483268234</v>
       </c>
       <c r="D22" t="n">
         <v>2.92126e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>119.722</v>
       </c>
+      <c r="C2" t="n">
+        <v>2002.831884046453</v>
+      </c>
       <c r="D2" t="n">
         <v>3.35159e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>76.97699999999998</v>
       </c>
+      <c r="C3" t="n">
+        <v>1572.201885023489</v>
+      </c>
       <c r="D3" t="n">
         <v>3.28991e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>70.84300000000002</v>
       </c>
+      <c r="C4" t="n">
+        <v>1440.558812132554</v>
+      </c>
       <c r="D4" t="n">
         <v>3.21697e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>66.61000000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>1189.049384993106</v>
+      </c>
       <c r="D5" t="n">
         <v>3.16364e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>63.959</v>
       </c>
+      <c r="C6" t="n">
+        <v>1063.578074062631</v>
+      </c>
       <c r="D6" t="n">
         <v>3.12615e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>59.96599999999995</v>
       </c>
+      <c r="C7" t="n">
+        <v>841.8733502328752</v>
+      </c>
       <c r="D7" t="n">
         <v>3.09917e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>58.38999999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>1169.813453066938</v>
+      </c>
       <c r="D8" t="n">
         <v>3.07858e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>57.78399999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>1310.533998997833</v>
+      </c>
       <c r="D9" t="n">
         <v>3.06218e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>54.15499999999997</v>
       </c>
+      <c r="C10" t="n">
+        <v>928.710326703539</v>
+      </c>
       <c r="D10" t="n">
         <v>3.05109e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>54.13499999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1445.18318297676</v>
       </c>
       <c r="D11" t="n">
         <v>3.04068e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>123.476</v>
       </c>
+      <c r="C2" t="n">
+        <v>1221.290708550385</v>
+      </c>
       <c r="D2" t="n">
         <v>3.16062e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>105.87</v>
       </c>
+      <c r="C3" t="n">
+        <v>880.6467379084125</v>
+      </c>
       <c r="D3" t="n">
         <v>3.06331e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>100.762</v>
       </c>
+      <c r="C4" t="n">
+        <v>820.5134001577698</v>
+      </c>
       <c r="D4" t="n">
         <v>3.02365e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>97.35000000000002</v>
       </c>
+      <c r="C5" t="n">
+        <v>826.9341288155427</v>
+      </c>
       <c r="D5" t="n">
         <v>3.00137e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>93.16399999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>788.3456379760891</v>
+      </c>
       <c r="D6" t="n">
         <v>2.98912e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>91.79200000000003</v>
       </c>
+      <c r="C7" t="n">
+        <v>807.5802699151379</v>
+      </c>
       <c r="D7" t="n">
         <v>2.97741e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>88.84000000000003</v>
       </c>
+      <c r="C8" t="n">
+        <v>818.9506023671506</v>
+      </c>
       <c r="D8" t="n">
         <v>2.97057e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>87.959</v>
       </c>
+      <c r="C9" t="n">
+        <v>887.4766272188973</v>
+      </c>
       <c r="D9" t="n">
         <v>2.96572e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>84.37299999999999</v>
       </c>
+      <c r="C10" t="n">
+        <v>846.8675302132741</v>
+      </c>
       <c r="D10" t="n">
         <v>2.95921e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>82.64500000000004</v>
       </c>
+      <c r="C11" t="n">
+        <v>855.0872161340203</v>
+      </c>
       <c r="D11" t="n">
         <v>2.95583e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>80.87399999999997</v>
       </c>
+      <c r="C12" t="n">
+        <v>856.0864387289444</v>
+      </c>
       <c r="D12" t="n">
         <v>2.95296e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>78.54899999999998</v>
       </c>
+      <c r="C13" t="n">
+        <v>847.6963118999857</v>
+      </c>
       <c r="D13" t="n">
         <v>2.94949e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>78.85699999999997</v>
       </c>
+      <c r="C14" t="n">
+        <v>950.2183831556212</v>
+      </c>
       <c r="D14" t="n">
         <v>2.94769e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>75.49099999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>812.6264557238651</v>
+      </c>
       <c r="D15" t="n">
         <v>2.94521e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>75.44800000000004</v>
       </c>
+      <c r="C16" t="n">
+        <v>925.7263499796172</v>
+      </c>
       <c r="D16" t="n">
         <v>2.94213e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>73.67500000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>846.5147418101699</v>
+      </c>
       <c r="D17" t="n">
         <v>2.94177e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>72.63799999999998</v>
       </c>
+      <c r="C18" t="n">
+        <v>944.2973591433489</v>
+      </c>
       <c r="D18" t="n">
         <v>2.93998e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>71.65199999999999</v>
       </c>
+      <c r="C19" t="n">
+        <v>999.4139095460389</v>
+      </c>
       <c r="D19" t="n">
         <v>2.93884e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>69.036</v>
       </c>
+      <c r="C20" t="n">
+        <v>873.3150677691416</v>
+      </c>
       <c r="D20" t="n">
         <v>2.93564e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>68.30000000000001</v>
       </c>
+      <c r="C21" t="n">
+        <v>887.2824936258272</v>
+      </c>
       <c r="D21" t="n">
         <v>2.93534e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>67.17000000000002</v>
+      </c>
+      <c r="C22" t="n">
+        <v>915.4447633939792</v>
       </c>
       <c r="D22" t="n">
         <v>2.93414e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>119.649</v>
       </c>
+      <c r="C2" t="n">
+        <v>1310.750005406399</v>
+      </c>
       <c r="D2" t="n">
         <v>3.22643e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>72.42899999999997</v>
       </c>
+      <c r="C3" t="n">
+        <v>1729.054801464142</v>
+      </c>
       <c r="D3" t="n">
         <v>3.16105e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>64.93199999999996</v>
       </c>
+      <c r="C4" t="n">
+        <v>1202.795213539822</v>
+      </c>
       <c r="D4" t="n">
         <v>3.09133e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>61.55399999999997</v>
       </c>
+      <c r="C5" t="n">
+        <v>1181.719827759418</v>
+      </c>
       <c r="D5" t="n">
         <v>3.04231e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>59.298</v>
       </c>
+      <c r="C6" t="n">
+        <v>1318.808614792707</v>
+      </c>
       <c r="D6" t="n">
         <v>3.01126e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>54.553</v>
       </c>
+      <c r="C7" t="n">
+        <v>909.5698410792626</v>
+      </c>
       <c r="D7" t="n">
         <v>2.99036e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>52.47500000000002</v>
       </c>
+      <c r="C8" t="n">
+        <v>997.6380588089178</v>
+      </c>
       <c r="D8" t="n">
         <v>2.97612e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>50.22800000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>1000.827568287667</v>
+      </c>
       <c r="D9" t="n">
         <v>2.9661e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>52.488</v>
       </c>
+      <c r="C10" t="n">
+        <v>1162.709569721979</v>
+      </c>
       <c r="D10" t="n">
         <v>2.95805e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>46.024</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1148.667753648627</v>
       </c>
       <c r="D11" t="n">
         <v>2.95183e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
@@ -565,7 +565,7 @@
         <v>117.903</v>
       </c>
       <c r="C2" t="n">
-        <v>890.6077851114572</v>
+        <v>302.8177253647987</v>
       </c>
       <c r="D2" t="n">
         <v>2.90149e-07</v>
@@ -598,16 +598,13 @@
         <v>-10528.52042150222</v>
       </c>
       <c r="Y2" t="n">
-        <v>460.6808130661087</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>190601270.4768265</v>
+        <v>205.6194064312845</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.644509464842502e-07</v>
+        <v>4.032164799253463e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9282272543301935</v>
+        <v>0.9464465511722279</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>113.654</v>
       </c>
       <c r="C3" t="n">
-        <v>961.8525654459299</v>
+        <v>290.4550960627769</v>
       </c>
       <c r="D3" t="n">
         <v>2.8692e-07</v>
@@ -651,16 +648,13 @@
         <v>-11894.28030228045</v>
       </c>
       <c r="Y3" t="n">
-        <v>453.9903085353594</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>254353603.7316092</v>
+        <v>208.108321673908</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.389297176198378e-07</v>
+        <v>3.77260875722687e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9350586238604292</v>
+        <v>0.9543876301513435</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>107.958</v>
       </c>
       <c r="C4" t="n">
-        <v>946.9072113896787</v>
+        <v>273.9849984164625</v>
       </c>
       <c r="D4" t="n">
         <v>2.8499e-07</v>
@@ -704,16 +698,13 @@
         <v>-11916.57385893646</v>
       </c>
       <c r="Y4" t="n">
-        <v>447.7894253377514</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>244588629.4254274</v>
+        <v>217.3507895572122</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.242214339888221e-07</v>
+        <v>3.822473323371784e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9392060758119588</v>
+        <v>0.9584167952401089</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>103.58</v>
       </c>
       <c r="C5" t="n">
-        <v>921.5417389754921</v>
+        <v>275.2814290373369</v>
       </c>
       <c r="D5" t="n">
         <v>2.83647e-07</v>
@@ -757,16 +748,13 @@
         <v>-11929.57493990915</v>
       </c>
       <c r="Y5" t="n">
-        <v>441.8343123082274</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>181461776.0191447</v>
+        <v>208.6333204619134</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.12948038816336e-07</v>
+        <v>3.565979433690029e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9425650833111668</v>
+        <v>0.9621910424214978</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>102.116</v>
       </c>
       <c r="C6" t="n">
-        <v>1020.026812405845</v>
+        <v>266.8215686313118</v>
       </c>
       <c r="D6" t="n">
         <v>2.82578e-07</v>
@@ -810,16 +798,13 @@
         <v>-12825.70675385108</v>
       </c>
       <c r="Y6" t="n">
-        <v>435.9848026626581</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>119033721.8569947</v>
+        <v>210.0684007583982</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.054320414649394e-07</v>
+        <v>3.499165336446013e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9447859928135186</v>
+        <v>0.9663952337873893</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>95.48899999999998</v>
       </c>
       <c r="C7" t="n">
-        <v>928.9390102933918</v>
+        <v>95.48899999999998</v>
       </c>
       <c r="D7" t="n">
         <v>2.81836e-07</v>
@@ -862,11 +847,10 @@
       <c r="X7" t="n">
         <v>-11753.45510055545</v>
       </c>
-      <c r="Y7" t="n">
-        <v>430.2772136153836</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>352070846.4447082</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>3.984371058527456e-07</v>
@@ -883,7 +867,7 @@
         <v>94.00800000000004</v>
       </c>
       <c r="C8" t="n">
-        <v>1024.381855985697</v>
+        <v>257.4374473854772</v>
       </c>
       <c r="D8" t="n">
         <v>2.8107e-07</v>
@@ -916,16 +900,13 @@
         <v>-12489.76538931573</v>
       </c>
       <c r="Y8" t="n">
-        <v>424.9842492674028</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>116039973.4921873</v>
+        <v>206.7975350399917</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.931125257048022e-07</v>
+        <v>3.360525695113886e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9486616057469494</v>
+        <v>0.9726779733878977</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +917,7 @@
         <v>89.97500000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>945.823285707609</v>
+        <v>89.97500000000002</v>
       </c>
       <c r="D9" t="n">
         <v>2.80569e-07</v>
@@ -968,11 +949,10 @@
       <c r="X9" t="n">
         <v>-11877.6660878247</v>
       </c>
-      <c r="Y9" t="n">
-        <v>420.0882347847049</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>114679807.782176</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>3.883145652609311e-07</v>
@@ -989,7 +969,7 @@
         <v>88.03399999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>1006.433763079279</v>
+        <v>88.03399999999999</v>
       </c>
       <c r="D10" t="n">
         <v>2.80002e-07</v>
@@ -1021,11 +1001,10 @@
       <c r="X10" t="n">
         <v>-12204.34182404864</v>
       </c>
-      <c r="Y10" t="n">
-        <v>415.6446530382878</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>309683257.2436185</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.840786656903262e-07</v>
@@ -1042,7 +1021,7 @@
         <v>85.86799999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>971.720071086501</v>
+        <v>269.1311307800545</v>
       </c>
       <c r="D11" t="n">
         <v>2.79627e-07</v>
@@ -1075,16 +1054,13 @@
         <v>-12358.87300405674</v>
       </c>
       <c r="Y11" t="n">
-        <v>411.6109132545095</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>336354412.5253681</v>
+        <v>180.090640956778</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.798725309185535e-07</v>
+        <v>3.091787715467654e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9530863457808189</v>
+        <v>0.9720610138456097</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1217,7 @@
         <v>124.576</v>
       </c>
       <c r="C2" t="n">
-        <v>1580.24712137046</v>
+        <v>124.576</v>
       </c>
       <c r="D2" t="n">
         <v>2.93127e-07</v>
@@ -1273,11 +1249,10 @@
       <c r="X2" t="n">
         <v>-10893.99816159297</v>
       </c>
-      <c r="Y2" t="n">
-        <v>447.1435381167894</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>248521665.1200158</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>4.527610517887826e-07</v>
@@ -1294,7 +1269,7 @@
         <v>102.115</v>
       </c>
       <c r="C3" t="n">
-        <v>909.5667837345769</v>
+        <v>262.8227829009394</v>
       </c>
       <c r="D3" t="n">
         <v>2.92917e-07</v>
@@ -1327,16 +1302,13 @@
         <v>-11504.33945863282</v>
       </c>
       <c r="Y3" t="n">
-        <v>433.2531990944827</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>826482560.508213</v>
+        <v>211.1558848746869</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.243705039226735e-07</v>
+        <v>3.702344286167315e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9433243622168664</v>
+        <v>0.9652384579476763</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1319,7 @@
         <v>95.654</v>
       </c>
       <c r="C4" t="n">
-        <v>842.2759028481145</v>
+        <v>281.8685431328552</v>
       </c>
       <c r="D4" t="n">
         <v>2.9212e-07</v>
@@ -1380,16 +1352,13 @@
         <v>-11430.26001686559</v>
       </c>
       <c r="Y4" t="n">
-        <v>427.8721024992129</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>175318940.6701232</v>
+        <v>185.9407069982283</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.159682414055889e-07</v>
+        <v>3.493100832784949e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9459630301299773</v>
+        <v>0.957599519040699</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1369,7 @@
         <v>92.30600000000004</v>
       </c>
       <c r="C5" t="n">
-        <v>804.6793442753356</v>
+        <v>265.5405040737633</v>
       </c>
       <c r="D5" t="n">
         <v>2.91187e-07</v>
@@ -1433,16 +1402,13 @@
         <v>-11224.70583769813</v>
       </c>
       <c r="Y5" t="n">
-        <v>423.6562047663102</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>346651457.6429015</v>
+        <v>197.4711472226433</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.087172028732938e-07</v>
+        <v>3.576641750460806e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9481504670151254</v>
+        <v>0.9648543626368208</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1419,7 @@
         <v>91.33499999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>893.1523794141702</v>
+        <v>259.9274757346853</v>
       </c>
       <c r="D6" t="n">
         <v>2.90558e-07</v>
@@ -1486,16 +1452,13 @@
         <v>-12214.07350323225</v>
       </c>
       <c r="Y6" t="n">
-        <v>419.4514387968316</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>114790085.4256744</v>
+        <v>198.0208930308652</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.036382757990266e-07</v>
+        <v>3.502524395063516e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9497215596288465</v>
+        <v>0.9681656929484953</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1469,7 @@
         <v>88.60599999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>862.4154699549715</v>
+        <v>88.60599999999999</v>
       </c>
       <c r="D7" t="n">
         <v>2.90046e-07</v>
@@ -1538,11 +1501,10 @@
       <c r="X7" t="n">
         <v>-11820.21700253824</v>
       </c>
-      <c r="Y7" t="n">
-        <v>415.2260026280111</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>175938969.3848063</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>3.996979035424695e-07</v>
@@ -1559,7 +1521,7 @@
         <v>86.69299999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>886.4238925844998</v>
+        <v>255.4970002289548</v>
       </c>
       <c r="D8" t="n">
         <v>2.89592e-07</v>
@@ -1592,16 +1554,13 @@
         <v>-11887.29217957252</v>
       </c>
       <c r="Y8" t="n">
-        <v>411.1281362983607</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>448424714.3112966</v>
+        <v>193.1596765403455</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9640601027699e-07</v>
+        <v>3.346981739486528e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9519725757353761</v>
+        <v>0.9729538221410059</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1571,7 @@
         <v>84.95099999999996</v>
       </c>
       <c r="C9" t="n">
-        <v>862.7305395388472</v>
+        <v>249.5578544077374</v>
       </c>
       <c r="D9" t="n">
         <v>2.89145e-07</v>
@@ -1645,16 +1604,13 @@
         <v>-12030.07192896979</v>
       </c>
       <c r="Y9" t="n">
-        <v>407.3281667431311</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>222657263.1626075</v>
+        <v>194.4334874421336</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.922137922553009e-07</v>
+        <v>3.308523118952052e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9533537694411272</v>
+        <v>0.9748519874485952</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1621,7 @@
         <v>84.07600000000002</v>
       </c>
       <c r="C10" t="n">
-        <v>948.5987199269531</v>
+        <v>240.8740416153209</v>
       </c>
       <c r="D10" t="n">
         <v>2.88963e-07</v>
@@ -1698,16 +1654,13 @@
         <v>-12366.10545753141</v>
       </c>
       <c r="Y10" t="n">
-        <v>403.7111005908142</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>109990427.2364046</v>
+        <v>198.9501933849894</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.904469143793302e-07</v>
+        <v>3.35100847991666e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9539474292666617</v>
+        <v>0.9771518973368867</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1671,7 @@
         <v>82.34000000000003</v>
       </c>
       <c r="C11" t="n">
-        <v>956.2520471311615</v>
+        <v>236.9251551565996</v>
       </c>
       <c r="D11" t="n">
         <v>2.88777e-07</v>
@@ -1751,16 +1704,13 @@
         <v>-12585.91718424231</v>
       </c>
       <c r="Y11" t="n">
-        <v>400.2978906122345</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>175910043.9011849</v>
+        <v>199.2442368796704</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.877393003707262e-07</v>
+        <v>3.295450946661176e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9549043810237576</v>
+        <v>0.9815095997561011</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1721,7 @@
         <v>79.61699999999996</v>
       </c>
       <c r="C12" t="n">
-        <v>880.1921895346447</v>
+        <v>234.1772421045719</v>
       </c>
       <c r="D12" t="n">
         <v>2.88503e-07</v>
@@ -1804,16 +1754,13 @@
         <v>-12076.69488488927</v>
       </c>
       <c r="Y12" t="n">
-        <v>397.0421710001932</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>432892730.2027784</v>
+        <v>198.0621409019536</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.854281908457652e-07</v>
+        <v>3.200689988467705e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9556753487634708</v>
+        <v>0.9846655729882082</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1771,7 @@
         <v>78.13599999999997</v>
       </c>
       <c r="C13" t="n">
-        <v>910.4736548563793</v>
+        <v>78.13599999999997</v>
       </c>
       <c r="D13" t="n">
         <v>2.88355e-07</v>
@@ -1856,11 +1803,10 @@
       <c r="X13" t="n">
         <v>-11945.45472151515</v>
       </c>
-      <c r="Y13" t="n">
-        <v>393.8312251500885</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>214386918.522717</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>3.83453242085289e-07</v>
@@ -1877,7 +1823,7 @@
         <v>77.274</v>
       </c>
       <c r="C14" t="n">
-        <v>945.7291628949596</v>
+        <v>229.7090224721472</v>
       </c>
       <c r="D14" t="n">
         <v>2.88254e-07</v>
@@ -1910,16 +1856,13 @@
         <v>-12168.58682462352</v>
       </c>
       <c r="Y14" t="n">
-        <v>390.6896074290457</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>212840888.1988895</v>
+        <v>195.5727570573132</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.812314796101391e-07</v>
+        <v>3.136433233952456e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9572038175700905</v>
+        <v>0.9881309171767457</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1873,7 @@
         <v>76.548</v>
       </c>
       <c r="C15" t="n">
-        <v>955.1533662778128</v>
+        <v>76.548</v>
       </c>
       <c r="D15" t="n">
         <v>2.88131e-07</v>
@@ -1962,11 +1905,10 @@
       <c r="X15" t="n">
         <v>-12247.84783957728</v>
       </c>
-      <c r="Y15" t="n">
-        <v>387.6458344404541</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>211057674.0037495</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>3.795525456519262e-07</v>
@@ -1983,7 +1925,7 @@
         <v>74.05900000000003</v>
       </c>
       <c r="C16" t="n">
-        <v>916.8962655480937</v>
+        <v>225.418444137469</v>
       </c>
       <c r="D16" t="n">
         <v>2.87906e-07</v>
@@ -2016,16 +1958,13 @@
         <v>-11721.62250437071</v>
       </c>
       <c r="Y16" t="n">
-        <v>384.6164933954831</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>314338859.8930665</v>
+        <v>192.8177723782434</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.776512885782103e-07</v>
+        <v>3.027891862134049e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9584622893124256</v>
+        <v>0.9918766156265283</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1975,7 @@
         <v>66.12599999999998</v>
       </c>
       <c r="C17" t="n">
-        <v>671.2277256029927</v>
+        <v>66.12599999999998</v>
       </c>
       <c r="D17" t="n">
         <v>2.87923e-07</v>
@@ -2068,11 +2007,10 @@
       <c r="X17" t="n">
         <v>-8707.14723446308</v>
       </c>
-      <c r="Y17" t="n">
-        <v>381.5022735022956</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>159568288.1963896</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>3.761299651783017e-07</v>
@@ -2089,7 +2027,7 @@
         <v>72.68599999999998</v>
       </c>
       <c r="C18" t="n">
-        <v>1022.056529799756</v>
+        <v>72.68599999999998</v>
       </c>
       <c r="D18" t="n">
         <v>2.87619e-07</v>
@@ -2121,11 +2059,10 @@
       <c r="X18" t="n">
         <v>-12491.80891613518</v>
       </c>
-      <c r="Y18" t="n">
-        <v>378.491303530022</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>411653892.8842936</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>3.737574662623318e-07</v>
@@ -2142,7 +2079,7 @@
         <v>71.12200000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>960.1921589662089</v>
+        <v>246.4068911744141</v>
       </c>
       <c r="D19" t="n">
         <v>2.87722e-07</v>
@@ -2175,16 +2112,13 @@
         <v>-12118.93204433167</v>
       </c>
       <c r="Y19" t="n">
-        <v>375.4657874272673</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>510651316.4201289</v>
+        <v>160.8669822103911</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.729394438623448e-07</v>
+        <v>2.711640351923484e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9602842805704072</v>
+        <v>0.985268594528368</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2129,7 @@
         <v>70.23500000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>994.1654071516632</v>
+        <v>70.23500000000001</v>
       </c>
       <c r="D20" t="n">
         <v>2.87617e-07</v>
@@ -2227,11 +2161,10 @@
       <c r="X20" t="n">
         <v>-12363.80096203343</v>
       </c>
-      <c r="Y20" t="n">
-        <v>372.4565979316113</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>208924720.4130622</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>3.715255539773576e-07</v>
@@ -2248,7 +2181,7 @@
         <v>68.12400000000002</v>
       </c>
       <c r="C21" t="n">
-        <v>881.7059512908706</v>
+        <v>239.5629693912374</v>
       </c>
       <c r="D21" t="n">
         <v>2.87411e-07</v>
@@ -2281,16 +2214,13 @@
         <v>-11432.83107502408</v>
       </c>
       <c r="Y21" t="n">
-        <v>369.4988003359341</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>200975065.0416353</v>
+        <v>161.2704641818673</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.698263627206813e-07</v>
+        <v>2.643447860558615e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9614076767052351</v>
+        <v>0.991329257085135</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2231,7 @@
         <v>67.43799999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>1031.773400294225</v>
+        <v>243.7650398693941</v>
       </c>
       <c r="D22" t="n">
         <v>2.87422e-07</v>
@@ -2334,16 +2264,13 @@
         <v>-12330.55693840722</v>
       </c>
       <c r="Y22" t="n">
-        <v>366.5550037701313</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>398585036.2710235</v>
+        <v>152.933434891729</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.675113956423256e-07</v>
+        <v>2.520487789843571e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9623619981075533</v>
+        <v>0.990943405023579</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2427,7 @@
         <v>130.665</v>
       </c>
       <c r="C2" t="n">
-        <v>1637.137769090585</v>
+        <v>331.0890688369926</v>
       </c>
       <c r="D2" t="n">
         <v>2.86232e-07</v>
@@ -2533,16 +2460,13 @@
         <v>-10616.00920003734</v>
       </c>
       <c r="Y2" t="n">
-        <v>452.6281176346285</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>26965155.80394516</v>
+        <v>164.3334829510567</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.570549146996892e-07</v>
+        <v>2.915724094203368e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9285781316048216</v>
+        <v>0.9540207238737671</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2477,7 @@
         <v>107.914</v>
       </c>
       <c r="C3" t="n">
-        <v>957.1519682047341</v>
+        <v>292.5137642988322</v>
       </c>
       <c r="D3" t="n">
         <v>2.8313e-07</v>
@@ -2586,16 +2510,13 @@
         <v>-12113.06451025192</v>
       </c>
       <c r="Y3" t="n">
-        <v>438.8395897881512</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>359097936.60583</v>
+        <v>188.3553724315657</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.103164652903575e-07</v>
+        <v>3.41831376249752e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9432058677849767</v>
+        <v>0.9585086694191687</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2527,7 @@
         <v>100.812</v>
       </c>
       <c r="C4" t="n">
-        <v>845.0068402707366</v>
+        <v>277.5059163780119</v>
       </c>
       <c r="D4" t="n">
         <v>2.82244e-07</v>
@@ -2639,16 +2560,13 @@
         <v>-11731.88806083015</v>
       </c>
       <c r="Y4" t="n">
-        <v>433.5301124149074</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>473453006.0500076</v>
+        <v>198.7351361175042</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.996858848909126e-07</v>
+        <v>3.655091836235361e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9467148891320274</v>
+        <v>0.9613600783512719</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2577,7 @@
         <v>99.36799999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>888.3923006401509</v>
+        <v>301.8068214764706</v>
       </c>
       <c r="D5" t="n">
         <v>2.81385e-07</v>
@@ -2692,16 +2610,13 @@
         <v>-12691.81067537729</v>
       </c>
       <c r="Y5" t="n">
-        <v>429.4146456355481</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>937038313.5798287</v>
+        <v>167.9146547516977</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.922750191135162e-07</v>
+        <v>3.254555733686819e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9490935729409444</v>
+        <v>0.9564297876079576</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2627,7 @@
         <v>98.72300000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>952.6287203573013</v>
+        <v>303.4240487132113</v>
       </c>
       <c r="D6" t="n">
         <v>2.80933e-07</v>
@@ -2745,16 +2660,13 @@
         <v>-13581.75687219688</v>
       </c>
       <c r="Y6" t="n">
-        <v>425.2499391865626</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>174058529.8754412</v>
+        <v>162.6004877109668</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.885166556966715e-07</v>
+        <v>3.22255554170634e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9503241131093119</v>
+        <v>0.956846782497204</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2677,7 @@
         <v>94.12</v>
       </c>
       <c r="C7" t="n">
-        <v>938.22665299928</v>
+        <v>94.12</v>
       </c>
       <c r="D7" t="n">
         <v>2.8037e-07</v>
@@ -2797,11 +2709,10 @@
       <c r="X7" t="n">
         <v>-12742.01062557794</v>
       </c>
-      <c r="Y7" t="n">
-        <v>421.1003245100919</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>172255243.7655863</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>3.837094757095452e-07</v>
@@ -2818,7 +2729,7 @@
         <v>91.20599999999996</v>
       </c>
       <c r="C8" t="n">
-        <v>903.7131018676588</v>
+        <v>345.1768799222093</v>
       </c>
       <c r="D8" t="n">
         <v>2.79929e-07</v>
@@ -2851,16 +2762,13 @@
         <v>-12321.75268154482</v>
       </c>
       <c r="Y8" t="n">
-        <v>416.9846873740198</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>113804099.6270947</v>
+        <v>109.9639618013381</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.811227722378589e-07</v>
+        <v>2.682056023768232e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9527127075400116</v>
+        <v>0.9500384981654527</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2779,7 @@
         <v>88.53199999999998</v>
       </c>
       <c r="C9" t="n">
-        <v>866.1331543797737</v>
+        <v>280.5064424021112</v>
       </c>
       <c r="D9" t="n">
         <v>2.79486e-07</v>
@@ -2904,16 +2812,13 @@
         <v>-11994.22531311118</v>
       </c>
       <c r="Y9" t="n">
-        <v>413.1611690987959</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>451251565.2286672</v>
+        <v>170.5154054530176</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.773477702498862e-07</v>
+        <v>3.092423366400777e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9539794355618256</v>
+        <v>0.9672113757295541</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2829,7 @@
         <v>88.53300000000002</v>
       </c>
       <c r="C10" t="n">
-        <v>958.861156385086</v>
+        <v>88.53300000000002</v>
       </c>
       <c r="D10" t="n">
         <v>2.79076e-07</v>
@@ -2956,11 +2861,10 @@
       <c r="X10" t="n">
         <v>-13193.13106233725</v>
       </c>
-      <c r="Y10" t="n">
-        <v>409.6060133392238</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>111933477.1832741</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.747474974519782e-07</v>
@@ -2977,7 +2881,7 @@
         <v>84.98000000000002</v>
       </c>
       <c r="C11" t="n">
-        <v>904.8255450214347</v>
+        <v>84.98000000000002</v>
       </c>
       <c r="D11" t="n">
         <v>2.78869e-07</v>
@@ -3009,11 +2913,10 @@
       <c r="X11" t="n">
         <v>-11998.70370759429</v>
       </c>
-      <c r="Y11" t="n">
-        <v>406.291196330672</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>241710295.472166</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.723001494175352e-07</v>
@@ -3030,7 +2933,7 @@
         <v>84.505</v>
       </c>
       <c r="C12" t="n">
-        <v>929.3584164985765</v>
+        <v>274.9237270265509</v>
       </c>
       <c r="D12" t="n">
         <v>2.78439e-07</v>
@@ -3063,16 +2966,13 @@
         <v>-12691.91203782742</v>
       </c>
       <c r="Y12" t="n">
-        <v>403.2006337661914</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>109859829.8334279</v>
+        <v>164.6699565474251</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.69921281257965e-07</v>
+        <v>2.918631957745541e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9564516825215468</v>
+        <v>0.9715974906284275</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2983,7 @@
         <v>81.95299999999997</v>
       </c>
       <c r="C13" t="n">
-        <v>862.7548870935294</v>
+        <v>81.95299999999997</v>
       </c>
       <c r="D13" t="n">
         <v>2.78444e-07</v>
@@ -3115,11 +3015,10 @@
       <c r="X13" t="n">
         <v>-11990.52759832771</v>
       </c>
-      <c r="Y13" t="n">
-        <v>400.2078102795967</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>327357146.2944426</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>3.676299454202607e-07</v>
@@ -3136,7 +3035,7 @@
         <v>82.452</v>
       </c>
       <c r="C14" t="n">
-        <v>1007.080401596257</v>
+        <v>82.452</v>
       </c>
       <c r="D14" t="n">
         <v>2.78023e-07</v>
@@ -3168,11 +3067,10 @@
       <c r="X14" t="n">
         <v>-13156.68338917681</v>
       </c>
-      <c r="Y14" t="n">
-        <v>397.3039047447717</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>108215599.8261663</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>3.655139131372438e-07</v>
@@ -3189,7 +3087,7 @@
         <v>80.90600000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>973.603821646939</v>
+        <v>80.90600000000001</v>
       </c>
       <c r="D15" t="n">
         <v>2.77878e-07</v>
@@ -3221,11 +3119,10 @@
       <c r="X15" t="n">
         <v>-12896.85828247652</v>
       </c>
-      <c r="Y15" t="n">
-        <v>394.4754215025944</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>216120754.9197448</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>3.640811067707824e-07</v>
@@ -3242,7 +3139,7 @@
         <v>80.49200000000002</v>
       </c>
       <c r="C16" t="n">
-        <v>1044.613023188647</v>
+        <v>261.135703839051</v>
       </c>
       <c r="D16" t="n">
         <v>2.77814e-07</v>
@@ -3275,16 +3172,13 @@
         <v>-13256.57052013853</v>
       </c>
       <c r="Y16" t="n">
-        <v>391.6535537013432</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>106803197.7981032</v>
+        <v>165.4865042386697</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.622292421104758e-07</v>
+        <v>2.779667745727118e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9593012392197026</v>
+        <v>0.9816421458788321</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3189,7 @@
         <v>77.25700000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>899.5130277642623</v>
+        <v>257.1445668614067</v>
       </c>
       <c r="D17" t="n">
         <v>2.77535e-07</v>
@@ -3328,16 +3222,13 @@
         <v>-12033.08820502537</v>
       </c>
       <c r="Y17" t="n">
-        <v>388.8202918079034</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>106321943.3405277</v>
+        <v>165.8572969197889</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.602866626102672e-07</v>
+        <v>2.752861544042429e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9599731408910596</v>
+        <v>0.9827086812037927</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3239,7 @@
         <v>76.15100000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>946.7389545860566</v>
+        <v>289.0086866513669</v>
       </c>
       <c r="D18" t="n">
         <v>2.77327e-07</v>
@@ -3381,16 +3272,13 @@
         <v>-12606.35367654404</v>
       </c>
       <c r="Y18" t="n">
-        <v>385.9786399679244</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>104982839.9092089</v>
+        <v>131.0509344060565</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.597788761976473e-07</v>
+        <v>2.535146655948013e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.960090152908484</v>
+        <v>0.9739405930192611</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3289,7 @@
         <v>75.38399999999996</v>
       </c>
       <c r="C19" t="n">
-        <v>1030.288769403512</v>
+        <v>75.38399999999996</v>
       </c>
       <c r="D19" t="n">
         <v>2.77195e-07</v>
@@ -3433,11 +3321,10 @@
       <c r="X19" t="n">
         <v>-12652.62730287282</v>
       </c>
-      <c r="Y19" t="n">
-        <v>383.193660630813</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>158330930.3102843</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.581488370121684e-07</v>
@@ -3454,7 +3341,7 @@
         <v>75.06399999999996</v>
       </c>
       <c r="C20" t="n">
-        <v>1084.648086361616</v>
+        <v>284.5045847158586</v>
       </c>
       <c r="D20" t="n">
         <v>2.77176e-07</v>
@@ -3487,16 +3374,13 @@
         <v>-13197.96299407448</v>
       </c>
       <c r="Y20" t="n">
-        <v>380.3892537577049</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>122669349.6537943</v>
+        <v>128.4446479185418</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.566569641173602e-07</v>
+        <v>2.429271300694061e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9613331270689943</v>
+        <v>0.9760738446723771</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3391,7 @@
         <v>72.54699999999997</v>
       </c>
       <c r="C21" t="n">
-        <v>967.2723031797441</v>
+        <v>72.54699999999997</v>
       </c>
       <c r="D21" t="n">
         <v>2.77071e-07</v>
@@ -3539,11 +3423,10 @@
       <c r="X21" t="n">
         <v>-12456.51290675694</v>
       </c>
-      <c r="Y21" t="n">
-        <v>377.6029800248166</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>264623826.9931263</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>3.553098167449959e-07</v>
@@ -3560,7 +3443,7 @@
         <v>72.42900000000003</v>
       </c>
       <c r="C22" t="n">
-        <v>1044.834217967165</v>
+        <v>282.0275480624616</v>
       </c>
       <c r="D22" t="n">
         <v>2.76954e-07</v>
@@ -3593,16 +3476,13 @@
         <v>-12847.91731832053</v>
       </c>
       <c r="Y22" t="n">
-        <v>374.7994787884469</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>103380966.1128163</v>
+        <v>124.3746190463408</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.535345658232639e-07</v>
+        <v>2.336777717751692e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9625544206255605</v>
+        <v>0.9801155539504124</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3639,7 @@
         <v>122.949</v>
       </c>
       <c r="C2" t="n">
-        <v>2550.299560906143</v>
+        <v>122.949</v>
       </c>
       <c r="D2" t="n">
         <v>3.18192e-07</v>
@@ -3791,11 +3671,10 @@
       <c r="X2" t="n">
         <v>-5628.87012266916</v>
       </c>
-      <c r="Y2" t="n">
-        <v>419.1303278562062</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>237956021.5373747</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>6.480821461489034e-07</v>
@@ -3812,7 +3691,7 @@
         <v>81.48099999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1655.621172787767</v>
+        <v>81.48099999999999</v>
       </c>
       <c r="D3" t="n">
         <v>3.16511e-07</v>
@@ -3844,11 +3723,10 @@
       <c r="X3" t="n">
         <v>-6739.300166576242</v>
       </c>
-      <c r="Y3" t="n">
-        <v>394.8625556246611</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>215315559.1440443</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>5.237797684194312e-07</v>
@@ -3865,7 +3743,7 @@
         <v>72.35199999999998</v>
       </c>
       <c r="C4" t="n">
-        <v>1230.409536637037</v>
+        <v>233.3176014789676</v>
       </c>
       <c r="D4" t="n">
         <v>3.11561e-07</v>
@@ -3898,16 +3776,13 @@
         <v>-7506.888128436009</v>
       </c>
       <c r="Y4" t="n">
-        <v>387.3357926059832</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>738117220.2832026</v>
+        <v>187.3028425081758</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.798370131338431e-07</v>
+        <v>2.98796695128968e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9344184471706958</v>
+        <v>0.9854269522187252</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3793,7 @@
         <v>65.51499999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>806.1722817253687</v>
+        <v>220.3646168343941</v>
       </c>
       <c r="D5" t="n">
         <v>3.0739e-07</v>
@@ -3951,16 +3826,13 @@
         <v>-7557.432651308401</v>
       </c>
       <c r="Y5" t="n">
-        <v>382.6967082059697</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>416303536.7261785</v>
+        <v>195.1664780932535</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.544229231216149e-07</v>
+        <v>3.004602596162699e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9405488265181526</v>
+        <v>0.9925260558880717</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3843,7 @@
         <v>67.685</v>
       </c>
       <c r="C6" t="n">
-        <v>1354.263863347428</v>
+        <v>215.061249151723</v>
       </c>
       <c r="D6" t="n">
         <v>3.04238e-07</v>
@@ -4004,16 +3876,13 @@
         <v>-8910.349587609531</v>
       </c>
       <c r="Y6" t="n">
-        <v>378.3127078468118</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>835726160.7478653</v>
+        <v>195.9084349649374</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.368865707032969e-07</v>
+        <v>3.020510196124189e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9449015694633687</v>
+        <v>0.9949383908443796</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3893,7 @@
         <v>66.01600000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>1447.536928530887</v>
+        <v>66.01600000000002</v>
       </c>
       <c r="D7" t="n">
         <v>3.0168e-07</v>
@@ -4056,11 +3925,10 @@
       <c r="X7" t="n">
         <v>-9214.317363509028</v>
       </c>
-      <c r="Y7" t="n">
-        <v>373.7850177928881</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>101714626.979459</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>4.24173743246501e-07</v>
@@ -4077,7 +3945,7 @@
         <v>63.15200000000004</v>
       </c>
       <c r="C8" t="n">
-        <v>1483.389288474473</v>
+        <v>317.804240613362</v>
       </c>
       <c r="D8" t="n">
         <v>2.99736e-07</v>
@@ -4110,16 +3978,13 @@
         <v>-9385.325435555385</v>
       </c>
       <c r="Y8" t="n">
-        <v>369.097428751326</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>100454669.8107652</v>
+        <v>81.08475700378105</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.140593860886103e-07</v>
+        <v>2.056186847512987e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9507388556007585</v>
+        <v>0.9697719650461623</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3995,7 @@
         <v>61.90700000000004</v>
       </c>
       <c r="C9" t="n">
-        <v>1806.448945371396</v>
+        <v>61.90700000000004</v>
       </c>
       <c r="D9" t="n">
         <v>2.98304e-07</v>
@@ -4162,11 +4027,10 @@
       <c r="X9" t="n">
         <v>-9752.118087275996</v>
       </c>
-      <c r="Y9" t="n">
-        <v>364.4769137966321</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>395702668.9113705</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>4.06252290539382e-07</v>
@@ -4183,7 +4047,7 @@
         <v>55.04500000000002</v>
       </c>
       <c r="C10" t="n">
-        <v>950.2243722006416</v>
+        <v>55.04500000000002</v>
       </c>
       <c r="D10" t="n">
         <v>2.96941e-07</v>
@@ -4215,11 +4079,10 @@
       <c r="X10" t="n">
         <v>-8582.618510701705</v>
       </c>
-      <c r="Y10" t="n">
-        <v>360.0930713471144</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>195787986.5454111</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.997722683862532e-07</v>
@@ -4236,7 +4099,7 @@
         <v>56.73999999999995</v>
       </c>
       <c r="C11" t="n">
-        <v>1640.406650146062</v>
+        <v>56.73999999999995</v>
       </c>
       <c r="D11" t="n">
         <v>2.95913e-07</v>
@@ -4268,11 +4131,10 @@
       <c r="X11" t="n">
         <v>-9770.344659172164</v>
       </c>
-      <c r="Y11" t="n">
-        <v>356.0744743652321</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>199362276.6665109</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.930753301313009e-07</v>
@@ -4435,7 +4297,7 @@
         <v>126.205</v>
       </c>
       <c r="C2" t="n">
-        <v>1311.559720985994</v>
+        <v>280.5579939401659</v>
       </c>
       <c r="D2" t="n">
         <v>3.13678e-07</v>
@@ -4468,16 +4330,13 @@
         <v>-7342.52900072193</v>
       </c>
       <c r="Y2" t="n">
-        <v>454.4833827394576</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>187116064.863457</v>
+        <v>220.3872382203104</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.053319565383948e-07</v>
+        <v>3.89563180425724e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.900390592137451</v>
+        <v>0.9559992427285021</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4347,7 @@
         <v>110.425</v>
       </c>
       <c r="C3" t="n">
-        <v>964.0749334639826</v>
+        <v>281.7588819811606</v>
       </c>
       <c r="D3" t="n">
         <v>3.01041e-07</v>
@@ -4521,16 +4380,13 @@
         <v>-10390.83339015991</v>
       </c>
       <c r="Y3" t="n">
-        <v>444.3433854461406</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>227310339.0631462</v>
+        <v>207.0263019731309</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.806494654655304e-07</v>
+        <v>4.100191533313443e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9287117044124438</v>
+        <v>0.9497249092738337</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4397,7 @@
         <v>103.639</v>
       </c>
       <c r="C4" t="n">
-        <v>885.4177058125242</v>
+        <v>275.2348459802795</v>
       </c>
       <c r="D4" t="n">
         <v>2.9619e-07</v>
@@ -4574,16 +4430,13 @@
         <v>-11150.89014368775</v>
       </c>
       <c r="Y4" t="n">
-        <v>439.8004021319067</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>390233521.0034816</v>
+        <v>208.3492609420734</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.478198723949327e-07</v>
+        <v>3.966060873997861e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9368932080426925</v>
+        <v>0.9567557407381293</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4447,7 @@
         <v>100.742</v>
       </c>
       <c r="C5" t="n">
-        <v>876.6406963489753</v>
+        <v>268.0855049254894</v>
       </c>
       <c r="D5" t="n">
         <v>2.93403e-07</v>
@@ -4627,16 +4480,13 @@
         <v>-11336.89800182589</v>
       </c>
       <c r="Y5" t="n">
-        <v>435.8094655228695</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>238000145.2117721</v>
+        <v>210.220983607323</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.322508734925884e-07</v>
+        <v>3.915809197053948e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9408174149751376</v>
+        <v>0.9599459871339387</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4497,7 @@
         <v>99.96199999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>959.2836576395424</v>
+        <v>263.3310347246658</v>
       </c>
       <c r="D6" t="n">
         <v>2.91834e-07</v>
@@ -4680,16 +4530,13 @@
         <v>-12337.34640091743</v>
       </c>
       <c r="Y6" t="n">
-        <v>431.6658538150863</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>353424793.0110175</v>
+        <v>209.1675761034443</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.219761535761566e-07</v>
+        <v>3.71661427077726e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9436392171724649</v>
+        <v>0.9632112731117727</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4547,7 @@
         <v>96.36699999999996</v>
       </c>
       <c r="C7" t="n">
-        <v>942.5768848752332</v>
+        <v>96.36699999999996</v>
       </c>
       <c r="D7" t="n">
         <v>2.90634e-07</v>
@@ -4732,11 +4579,10 @@
       <c r="X7" t="n">
         <v>-11976.82073371826</v>
       </c>
-      <c r="Y7" t="n">
-        <v>427.4226578433824</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>175691224.9325576</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>4.141469311108859e-07</v>
@@ -4753,7 +4599,7 @@
         <v>93.42700000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>872.968133249761</v>
+        <v>274.8355973576058</v>
       </c>
       <c r="D8" t="n">
         <v>2.89732e-07</v>
@@ -4786,16 +4632,13 @@
         <v>-11729.21161930763</v>
       </c>
       <c r="Y8" t="n">
-        <v>423.3585406084665</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>117607723.5857834</v>
+        <v>188.4761007503515</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.074363927913332e-07</v>
+        <v>3.468527253554726e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9478533374320448</v>
+        <v>0.9629679818500168</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4649,7 @@
         <v>90.64200000000005</v>
       </c>
       <c r="C9" t="n">
-        <v>906.5315315749058</v>
+        <v>267.4236668222663</v>
       </c>
       <c r="D9" t="n">
         <v>2.89073e-07</v>
@@ -4839,16 +4682,13 @@
         <v>-11836.7168398624</v>
       </c>
       <c r="Y9" t="n">
-        <v>419.5172831610098</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>343081960.8524319</v>
+        <v>191.756637051369</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.035195149594637e-07</v>
+        <v>3.494508374152584e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9489803524992504</v>
+        <v>0.9659690090936578</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4699,7 @@
         <v>87.065</v>
       </c>
       <c r="C10" t="n">
-        <v>829.2297965750013</v>
+        <v>261.5631668523408</v>
       </c>
       <c r="D10" t="n">
         <v>2.88377e-07</v>
@@ -4892,16 +4732,13 @@
         <v>-11153.35516706003</v>
       </c>
       <c r="Y10" t="n">
-        <v>415.9383678094663</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>429213198.5914063</v>
+        <v>193.0516511912931</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.985999351391694e-07</v>
+        <v>3.395602022712704e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9504716295071537</v>
+        <v>0.9698427700168631</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4749,7 @@
         <v>87.048</v>
       </c>
       <c r="C11" t="n">
-        <v>902.4436078541372</v>
+        <v>87.048</v>
       </c>
       <c r="D11" t="n">
         <v>2.87984e-07</v>
@@ -4944,11 +4781,10 @@
       <c r="X11" t="n">
         <v>-11838.61701463857</v>
       </c>
-      <c r="Y11" t="n">
-        <v>412.5809664772147</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>899655013.5080864</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.952566190074919e-07</v>
@@ -4965,7 +4801,7 @@
         <v>85.93200000000002</v>
       </c>
       <c r="C12" t="n">
-        <v>947.9084758738557</v>
+        <v>85.93200000000002</v>
       </c>
       <c r="D12" t="n">
         <v>2.87379e-07</v>
@@ -4997,11 +4833,10 @@
       <c r="X12" t="n">
         <v>-12099.65098283132</v>
       </c>
-      <c r="Y12" t="n">
-        <v>409.317182516985</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>334834501.7323543</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>3.909901082707743e-07</v>
@@ -5018,7 +4853,7 @@
         <v>84.14599999999996</v>
       </c>
       <c r="C13" t="n">
-        <v>936.0933854234609</v>
+        <v>242.5528426268346</v>
       </c>
       <c r="D13" t="n">
         <v>2.87175e-07</v>
@@ -5051,16 +4886,13 @@
         <v>-12075.26208024579</v>
       </c>
       <c r="Y13" t="n">
-        <v>406.1401869914395</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>222870366.8784933</v>
+        <v>200.7202387619334</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.892524334501335e-07</v>
+        <v>3.417921351066806e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9534430418002374</v>
+        <v>0.9771213984149657</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4903,7 @@
         <v>82.01800000000003</v>
       </c>
       <c r="C14" t="n">
-        <v>911.382550453404</v>
+        <v>297.5423034738733</v>
       </c>
       <c r="D14" t="n">
         <v>2.86733e-07</v>
@@ -5104,16 +4936,13 @@
         <v>-11892.42657330367</v>
       </c>
       <c r="Y14" t="n">
-        <v>403.0748855677115</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>348849294.0173115</v>
+        <v>141.7417809352117</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.858002570018155e-07</v>
+        <v>2.850034390217312e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9545566499509672</v>
+        <v>0.9628169047291291</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4953,7 @@
         <v>79.80900000000003</v>
       </c>
       <c r="C15" t="n">
-        <v>880.9208290548632</v>
+        <v>79.80900000000003</v>
       </c>
       <c r="D15" t="n">
         <v>2.86526e-07</v>
@@ -5156,11 +4985,10 @@
       <c r="X15" t="n">
         <v>-11390.89846302218</v>
       </c>
-      <c r="Y15" t="n">
-        <v>400.0886233086401</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>108984313.132315</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>3.835552427151432e-07</v>
@@ -5177,7 +5005,7 @@
         <v>80.65700000000004</v>
       </c>
       <c r="C16" t="n">
-        <v>1000.279642311502</v>
+        <v>233.8492198221027</v>
       </c>
       <c r="D16" t="n">
         <v>2.8616e-07</v>
@@ -5210,16 +5038,13 @@
         <v>-12253.84147005952</v>
       </c>
       <c r="Y16" t="n">
-        <v>397.0504871857528</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>216152544.8316074</v>
+        <v>198.5156546387944</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.812783269214345e-07</v>
+        <v>3.207749783117871e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9560525719159558</v>
+        <v>0.9843718356410278</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5055,7 @@
         <v>78.88200000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>946.0488517092964</v>
+        <v>78.88200000000001</v>
       </c>
       <c r="D17" t="n">
         <v>2.85864e-07</v>
@@ -5262,11 +5087,10 @@
       <c r="X17" t="n">
         <v>-12158.414116309</v>
       </c>
-      <c r="Y17" t="n">
-        <v>394.0754869934265</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>323781627.2760304</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>3.792557680674301e-07</v>
@@ -5283,7 +5107,7 @@
         <v>77.33299999999997</v>
       </c>
       <c r="C18" t="n">
-        <v>950.9904368370363</v>
+        <v>231.1090273050461</v>
       </c>
       <c r="D18" t="n">
         <v>2.85582e-07</v>
@@ -5316,16 +5140,13 @@
         <v>-11970.20292691997</v>
       </c>
       <c r="Y18" t="n">
-        <v>391.2051689590616</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>107339580.1232407</v>
+        <v>194.9538663590043</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.77760869651101e-07</v>
+        <v>3.107142822719211e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9571706666145723</v>
+        <v>0.9882325532148265</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5157,7 @@
         <v>75.56999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>909.3965231402768</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="D19" t="n">
         <v>2.85464e-07</v>
@@ -5368,11 +5189,10 @@
       <c r="X19" t="n">
         <v>-11512.47549531506</v>
       </c>
-      <c r="Y19" t="n">
-        <v>388.3791891831955</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>211220147.9162743</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.743627944763477e-07</v>
@@ -5389,7 +5209,7 @@
         <v>73.96099999999996</v>
       </c>
       <c r="C20" t="n">
-        <v>929.3812815715984</v>
+        <v>224.4674493150418</v>
       </c>
       <c r="D20" t="n">
         <v>2.85318e-07</v>
@@ -5422,16 +5242,13 @@
         <v>-11638.89637173298</v>
       </c>
       <c r="Y20" t="n">
-        <v>385.5153749469669</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>105835037.7178549</v>
+        <v>194.7098788015028</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.736006616054055e-07</v>
+        <v>3.010061021429438e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9587076045647994</v>
+        <v>0.9928682224195989</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5259,7 @@
         <v>73.87</v>
       </c>
       <c r="C21" t="n">
-        <v>989.5159088121409</v>
+        <v>223.3723740889823</v>
       </c>
       <c r="D21" t="n">
         <v>2.85219e-07</v>
@@ -5475,16 +5292,13 @@
         <v>-11981.09387389747</v>
       </c>
       <c r="Y21" t="n">
-        <v>382.6047261406154</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>156162063.6326108</v>
+        <v>192.678380324885</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.716763761359019e-07</v>
+        <v>3.027619675275755e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.959440793080431</v>
+        <v>0.9926762836780796</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5309,7 @@
         <v>73.55000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>1081.632682110158</v>
+        <v>221.2385319044425</v>
       </c>
       <c r="D22" t="n">
         <v>2.85043e-07</v>
@@ -5528,16 +5342,13 @@
         <v>-12706.02240559245</v>
       </c>
       <c r="Y22" t="n">
-        <v>379.749870447119</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>154933492.0837362</v>
+        <v>191.407277498355</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.70021274462572e-07</v>
+        <v>2.972150960994147e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9600280212497452</v>
+        <v>0.9945791513252689</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5505,7 @@
         <v>110.528</v>
       </c>
       <c r="C2" t="n">
-        <v>2945.058568658877</v>
+        <v>258.7721809245248</v>
       </c>
       <c r="D2" t="n">
         <v>3.33264e-07</v>
@@ -5727,16 +5538,13 @@
         <v>-4753.424589584552</v>
       </c>
       <c r="Y2" t="n">
-        <v>407.9444048816297</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>332515989.0284235</v>
+        <v>182.4202959001747</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.164514322357864e-07</v>
+        <v>2.23017765750471e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8847888335958896</v>
+        <v>0.9900257001017657</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5555,7 @@
         <v>76.30899999999997</v>
       </c>
       <c r="C3" t="n">
-        <v>1861.253355109347</v>
+        <v>76.30899999999997</v>
       </c>
       <c r="D3" t="n">
         <v>3.29263e-07</v>
@@ -5779,11 +5587,10 @@
       <c r="X3" t="n">
         <v>-6004.551330662123</v>
       </c>
-      <c r="Y3" t="n">
-        <v>386.2412426836281</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>111598513.6450507</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>5.628143140030422e-07</v>
@@ -5800,7 +5607,7 @@
         <v>68.392</v>
       </c>
       <c r="C4" t="n">
-        <v>1289.010574430256</v>
+        <v>236.8324463076088</v>
       </c>
       <c r="D4" t="n">
         <v>3.22555e-07</v>
@@ -5833,16 +5640,13 @@
         <v>-6831.823986951316</v>
       </c>
       <c r="Y4" t="n">
-        <v>379.3038843014611</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>413031317.0144475</v>
+        <v>174.1732510862643</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.088121567821781e-07</v>
+        <v>2.886987127712619e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9309032839370458</v>
+        <v>0.982695770675542</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5657,7 @@
         <v>64.28699999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>1107.398247280812</v>
+        <v>214.171211741011</v>
       </c>
       <c r="D5" t="n">
         <v>3.17461e-07</v>
@@ -5886,16 +5690,13 @@
         <v>-7452.965955708944</v>
       </c>
       <c r="Y5" t="n">
-        <v>374.5719261859737</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>152892436.3082632</v>
+        <v>191.759850306216</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.766402512075581e-07</v>
+        <v>2.977595169828971e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9382800859000076</v>
+        <v>0.9943993879610956</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5707,7 @@
         <v>63.44399999999996</v>
       </c>
       <c r="C6" t="n">
-        <v>1470.096870481593</v>
+        <v>63.44399999999996</v>
       </c>
       <c r="D6" t="n">
         <v>3.13556e-07</v>
@@ -5938,11 +5739,10 @@
       <c r="X6" t="n">
         <v>-8163.710795533659</v>
       </c>
-      <c r="Y6" t="n">
-        <v>369.9265806455115</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>301771025.1762537</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>4.561796761078541e-07</v>
@@ -5959,7 +5759,7 @@
         <v>59.33799999999997</v>
       </c>
       <c r="C7" t="n">
-        <v>1168.066462900982</v>
+        <v>134.8269978344738</v>
       </c>
       <c r="D7" t="n">
         <v>3.10572e-07</v>
@@ -5992,10 +5792,7 @@
         <v>-8138.084730669253</v>
       </c>
       <c r="Y7" t="n">
-        <v>365.090233529936</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>694411073.1949362</v>
+        <v>442.001063947961</v>
       </c>
       <c r="AA7" t="n">
         <v>4.400790055181719e-07</v>
@@ -6012,7 +5809,7 @@
         <v>58.24900000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>1392.89107352429</v>
+        <v>58.24900000000002</v>
       </c>
       <c r="D8" t="n">
         <v>3.08217e-07</v>
@@ -6044,11 +5841,10 @@
       <c r="X8" t="n">
         <v>-8556.790384070811</v>
       </c>
-      <c r="Y8" t="n">
-        <v>360.2783639012237</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>192911236.803858</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>4.28346261217713e-07</v>
@@ -6065,7 +5861,7 @@
         <v>54.84800000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1201.426277241353</v>
+        <v>54.84800000000001</v>
       </c>
       <c r="D9" t="n">
         <v>3.06404e-07</v>
@@ -6097,11 +5893,10 @@
       <c r="X9" t="n">
         <v>-8532.471943589499</v>
       </c>
-      <c r="Y9" t="n">
-        <v>355.6587425423492</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>193140130.2899781</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>4.18716131799048e-07</v>
@@ -6118,7 +5913,7 @@
         <v>52.55900000000003</v>
       </c>
       <c r="C10" t="n">
-        <v>1279.387071224094</v>
+        <v>52.55900000000003</v>
       </c>
       <c r="D10" t="n">
         <v>3.04952e-07</v>
@@ -6150,11 +5945,10 @@
       <c r="X10" t="n">
         <v>-8558.562107446602</v>
       </c>
-      <c r="Y10" t="n">
-        <v>351.3973577719283</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>285939520.9280819</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>4.115268052404907e-07</v>
@@ -6171,7 +5965,7 @@
         <v>48.81099999999998</v>
       </c>
       <c r="C11" t="n">
-        <v>1006.686458214438</v>
+        <v>249.6636074884817</v>
       </c>
       <c r="D11" t="n">
         <v>3.03864e-07</v>
@@ -6204,16 +5998,13 @@
         <v>-8073.835542757663</v>
       </c>
       <c r="Y11" t="n">
-        <v>347.5386268559336</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>282811632.505776</v>
+        <v>124.379781406035</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.051327352762345e-07</v>
+        <v>2.109349140119466e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9561260598024753</v>
+        <v>0.9946626693045172</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6161,7 @@
         <v>124.96</v>
       </c>
       <c r="C2" t="n">
-        <v>1652.773084991022</v>
+        <v>280.6835688808752</v>
       </c>
       <c r="D2" t="n">
         <v>3.15126e-07</v>
@@ -6403,16 +6194,13 @@
         <v>-7987.922226105684</v>
       </c>
       <c r="Y2" t="n">
-        <v>446.0148829950641</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>84978574.93709195</v>
+        <v>208.3634122724767</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.775022325785147e-07</v>
+        <v>3.570865159364706e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9080523895728492</v>
+        <v>0.9583794615923398</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6211,7 @@
         <v>104.848</v>
       </c>
       <c r="C3" t="n">
-        <v>980.2863676036791</v>
+        <v>300.3917292258749</v>
       </c>
       <c r="D3" t="n">
         <v>3.04695e-07</v>
@@ -6456,16 +6244,13 @@
         <v>-10453.37906471734</v>
       </c>
       <c r="Y3" t="n">
-        <v>434.2343672011721</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>177951294.6077994</v>
+        <v>176.3335081172038</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.748872196471541e-07</v>
+        <v>3.748394058196239e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9323407917249275</v>
+        <v>0.9462952187521997</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6261,7 @@
         <v>96.53099999999995</v>
       </c>
       <c r="C4" t="n">
-        <v>816.3724175747152</v>
+        <v>96.53099999999995</v>
       </c>
       <c r="D4" t="n">
         <v>3.00868e-07</v>
@@ -6508,11 +6293,10 @@
       <c r="X4" t="n">
         <v>-10342.09511917656</v>
       </c>
-      <c r="Y4" t="n">
-        <v>429.2795170630448</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>351478646.8944843</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>4.489664134397564e-07</v>
@@ -6529,7 +6313,7 @@
         <v>94.52999999999997</v>
       </c>
       <c r="C5" t="n">
-        <v>810.1952590323924</v>
+        <v>94.52999999999997</v>
       </c>
       <c r="D5" t="n">
         <v>2.98863e-07</v>
@@ -6561,11 +6345,10 @@
       <c r="X5" t="n">
         <v>-10665.8415541838</v>
       </c>
-      <c r="Y5" t="n">
-        <v>425.1959236977404</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>235351636.5837735</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>4.359411526968289e-07</v>
@@ -6582,7 +6365,7 @@
         <v>92.78500000000003</v>
       </c>
       <c r="C6" t="n">
-        <v>854.3851242670345</v>
+        <v>92.78500000000003</v>
       </c>
       <c r="D6" t="n">
         <v>2.97582e-07</v>
@@ -6614,11 +6397,10 @@
       <c r="X6" t="n">
         <v>-11109.85438935966</v>
       </c>
-      <c r="Y6" t="n">
-        <v>420.9383043666102</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>344486988.1805056</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>4.272586588934582e-07</v>
@@ -6635,7 +6417,7 @@
         <v>90.541</v>
       </c>
       <c r="C7" t="n">
-        <v>889.5644239351532</v>
+        <v>90.541</v>
       </c>
       <c r="D7" t="n">
         <v>2.96574e-07</v>
@@ -6667,11 +6449,10 @@
       <c r="X7" t="n">
         <v>-11470.74473171246</v>
       </c>
-      <c r="Y7" t="n">
-        <v>416.6609056134988</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>454622194.7657275</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>4.196190617590498e-07</v>
@@ -6688,7 +6469,7 @@
         <v>86.721</v>
       </c>
       <c r="C8" t="n">
-        <v>844.9579815557967</v>
+        <v>262.420861514187</v>
       </c>
       <c r="D8" t="n">
         <v>2.95844e-07</v>
@@ -6721,16 +6502,13 @@
         <v>-10899.96096864557</v>
       </c>
       <c r="Y8" t="n">
-        <v>412.5604978648525</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>112641204.4043455</v>
+        <v>187.5458006623315</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.14776932130355e-07</v>
+        <v>3.400083240226433e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9483399330271881</v>
+        <v>0.9658060584057936</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6519,7 @@
         <v>87.43799999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>959.0419467918387</v>
+        <v>269.485987752961</v>
       </c>
       <c r="D9" t="n">
         <v>2.9517e-07</v>
@@ -6774,16 +6552,13 @@
         <v>-12184.70842095018</v>
       </c>
       <c r="Y9" t="n">
-        <v>408.678924756534</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>111774879.4283397</v>
+        <v>177.1007652138053</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.096945883440376e-07</v>
+        <v>3.356264750867617e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9498592349681894</v>
+        <v>0.965631154648503</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6569,7 @@
         <v>83.87699999999995</v>
       </c>
       <c r="C10" t="n">
-        <v>877.1316939712378</v>
+        <v>253.9942167285361</v>
       </c>
       <c r="D10" t="n">
         <v>2.94842e-07</v>
@@ -6827,16 +6602,13 @@
         <v>-11277.14185148296</v>
       </c>
       <c r="Y10" t="n">
-        <v>405.128482187097</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>331854691.1554563</v>
+        <v>187.3540609481823</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.061919148170452e-07</v>
+        <v>3.281224984057941e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9509893207657424</v>
+        <v>0.9734914035918134</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6619,7 @@
         <v>81.40099999999995</v>
       </c>
       <c r="C11" t="n">
-        <v>870.5978815336495</v>
+        <v>247.3504645946117</v>
       </c>
       <c r="D11" t="n">
         <v>2.94245e-07</v>
@@ -6880,16 +6652,13 @@
         <v>-11202.34366021609</v>
       </c>
       <c r="Y11" t="n">
-        <v>401.7374751353441</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>437438252.4191567</v>
+        <v>190.991784482444</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.01959212551893e-07</v>
+        <v>3.323225172933509e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9522762712718709</v>
+        <v>0.9764923271513726</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6669,7 @@
         <v>80.79599999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>861.2099389687762</v>
+        <v>246.1341419458053</v>
       </c>
       <c r="D12" t="n">
         <v>2.93913e-07</v>
@@ -6933,16 +6702,13 @@
         <v>-11467.55342588361</v>
       </c>
       <c r="Y12" t="n">
-        <v>398.4736651690069</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>217053205.7063066</v>
+        <v>187.8238222386573</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.994986912557351e-07</v>
+        <v>3.211595278362294e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.95303830115764</v>
+        <v>0.9775657006486768</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6719,7 @@
         <v>80.49299999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>940.394812631066</v>
+        <v>243.6518733000956</v>
       </c>
       <c r="D13" t="n">
         <v>2.93662e-07</v>
@@ -6986,16 +6752,13 @@
         <v>-11745.34269629697</v>
       </c>
       <c r="Y13" t="n">
-        <v>395.2619056066575</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>221882014.0315479</v>
+        <v>186.7737398574768</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.96724520288062e-07</v>
+        <v>3.174577221188707e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9539697415323966</v>
+        <v>0.9801968791939476</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6769,7 @@
         <v>78.20999999999998</v>
       </c>
       <c r="C14" t="n">
-        <v>883.556337065977</v>
+        <v>78.20999999999998</v>
       </c>
       <c r="D14" t="n">
         <v>2.93307e-07</v>
@@ -7038,11 +6801,10 @@
       <c r="X14" t="n">
         <v>-11435.6013890905</v>
       </c>
-      <c r="Y14" t="n">
-        <v>392.0273051280593</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>106739280.8172119</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>3.943063813999103e-07</v>
@@ -7059,7 +6821,7 @@
         <v>76.49799999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>902.0030745582178</v>
+        <v>229.4681267327189</v>
       </c>
       <c r="D15" t="n">
         <v>2.93089e-07</v>
@@ -7092,16 +6854,13 @@
         <v>-11468.04262855224</v>
       </c>
       <c r="Y15" t="n">
-        <v>388.8272275192413</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>216422567.0752833</v>
+        <v>193.9885115996633</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.906950124330994e-07</v>
+        <v>3.174062700028061e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9559924581828777</v>
+        <v>0.9871142255886163</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6871,7 @@
         <v>76.19900000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>961.8659816921156</v>
+        <v>76.19900000000001</v>
       </c>
       <c r="D16" t="n">
         <v>2.92741e-07</v>
@@ -7144,11 +6903,10 @@
       <c r="X16" t="n">
         <v>-11676.23337937664</v>
       </c>
-      <c r="Y16" t="n">
-        <v>385.6623818984777</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>217053825.2136868</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>3.88113878768437e-07</v>
@@ -7165,7 +6923,7 @@
         <v>73.32600000000002</v>
       </c>
       <c r="C17" t="n">
-        <v>889.8595155459149</v>
+        <v>73.32600000000002</v>
       </c>
       <c r="D17" t="n">
         <v>2.92711e-07</v>
@@ -7197,11 +6955,10 @@
       <c r="X17" t="n">
         <v>-11042.48341330128</v>
       </c>
-      <c r="Y17" t="n">
-        <v>382.5544036487379</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>156182389.0318249</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>3.866932251064737e-07</v>
@@ -7218,7 +6975,7 @@
         <v>64.48699999999997</v>
       </c>
       <c r="C18" t="n">
-        <v>670.3729924183323</v>
+        <v>237.9081571010793</v>
       </c>
       <c r="D18" t="n">
         <v>2.92538e-07</v>
@@ -7251,16 +7008,13 @@
         <v>-8057.979069796295</v>
       </c>
       <c r="Y18" t="n">
-        <v>379.4769297440737</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>515933647.3736491</v>
+        <v>174.8201991126805</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.850403723704442e-07</v>
+        <v>2.91484833635785e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9579387824477997</v>
+        <v>0.9870813271271912</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +7025,7 @@
         <v>71.99799999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>934.442142010436</v>
+        <v>218.7637694602039</v>
       </c>
       <c r="D19" t="n">
         <v>2.92352e-07</v>
@@ -7304,16 +7058,13 @@
         <v>-11809.41632763514</v>
       </c>
       <c r="Y19" t="n">
-        <v>376.4565916099552</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>103033300.711237</v>
+        <v>189.4553499347431</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.824612640744002e-07</v>
+        <v>2.94568252699763e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.958858704275537</v>
+        <v>0.9950503964500338</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +7075,7 @@
         <v>70.68600000000004</v>
       </c>
       <c r="C20" t="n">
-        <v>969.192656201164</v>
+        <v>70.68600000000004</v>
       </c>
       <c r="D20" t="n">
         <v>2.92278e-07</v>
@@ -7356,11 +7107,10 @@
       <c r="X20" t="n">
         <v>-11595.30394880118</v>
       </c>
-      <c r="Y20" t="n">
-        <v>373.3676814466969</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>101526739.8696273</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>3.809198333641624e-07</v>
@@ -7377,7 +7127,7 @@
         <v>64.14300000000003</v>
       </c>
       <c r="C21" t="n">
-        <v>686.3389498796878</v>
+        <v>223.7390589225034</v>
       </c>
       <c r="D21" t="n">
         <v>2.92051e-07</v>
@@ -7410,16 +7160,13 @@
         <v>-9258.845952607056</v>
       </c>
       <c r="Y21" t="n">
-        <v>370.3318818464714</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>111811650.035345</v>
+        <v>177.812423301284</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.792846845877749e-07</v>
+        <v>2.803793833783948e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9599847294952689</v>
+        <v>0.9952667879937279</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7177,7 @@
         <v>68.22300000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>959.5968483268234</v>
+        <v>222.3887726898728</v>
       </c>
       <c r="D22" t="n">
         <v>2.92126e-07</v>
@@ -7463,16 +7210,13 @@
         <v>-11563.32149353308</v>
       </c>
       <c r="Y22" t="n">
-        <v>367.3208433238416</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>349314556.1951188</v>
+        <v>175.859700747763</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.779635824933687e-07</v>
+        <v>2.769790838218156e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9605521371591935</v>
+        <v>0.996395799365035</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7373,7 @@
         <v>119.722</v>
       </c>
       <c r="C2" t="n">
-        <v>2002.831884046453</v>
+        <v>260.0234043841783</v>
       </c>
       <c r="D2" t="n">
         <v>3.35159e-07</v>
@@ -7662,16 +7406,13 @@
         <v>-5076.239441812922</v>
       </c>
       <c r="Y2" t="n">
-        <v>407.9722052818478</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>664932994.7204992</v>
+        <v>180.6379033358458</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.207750306963229e-07</v>
+        <v>2.167010696321703e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8846357990569247</v>
+        <v>0.9908094111713995</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7423,7 @@
         <v>76.97699999999998</v>
       </c>
       <c r="C3" t="n">
-        <v>1572.201885023489</v>
+        <v>76.97699999999998</v>
       </c>
       <c r="D3" t="n">
         <v>3.28991e-07</v>
@@ -7714,11 +7455,10 @@
       <c r="X3" t="n">
         <v>-6259.776557979794</v>
       </c>
-      <c r="Y3" t="n">
-        <v>384.2056505935366</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>160366462.3266262</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>5.498404646487141e-07</v>
@@ -7735,7 +7475,7 @@
         <v>70.84300000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>1440.558812132554</v>
+        <v>212.4369395853591</v>
       </c>
       <c r="D4" t="n">
         <v>3.21697e-07</v>
@@ -7768,16 +7508,13 @@
         <v>-7592.345015751976</v>
       </c>
       <c r="Y4" t="n">
-        <v>377.1802059422451</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>205446605.1174258</v>
+        <v>197.2567514579837</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.943888532198906e-07</v>
+        <v>3.17639370631427e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9347560956255834</v>
+        <v>0.9919095726079901</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7525,7 @@
         <v>66.61000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1189.049384993106</v>
+        <v>214.5015737880682</v>
       </c>
       <c r="D5" t="n">
         <v>3.16364e-07</v>
@@ -7821,16 +7558,13 @@
         <v>-8153.215156702091</v>
       </c>
       <c r="Y5" t="n">
-        <v>372.7751086175262</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>101512622.2244934</v>
+        <v>189.6772805690467</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.637422447401791e-07</v>
+        <v>3.01162502442773e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9418317249654024</v>
+        <v>0.9937500655742596</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7575,7 @@
         <v>63.959</v>
       </c>
       <c r="C6" t="n">
-        <v>1063.578074062631</v>
+        <v>207.975910674137</v>
       </c>
       <c r="D6" t="n">
         <v>3.12615e-07</v>
@@ -7874,16 +7608,13 @@
         <v>-8592.884326206267</v>
       </c>
       <c r="Y6" t="n">
-        <v>368.6221191779746</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>302451889.9287871</v>
+        <v>191.8977119184027</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.449715321288874e-07</v>
+        <v>2.975692458448599e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9462464707352591</v>
+        <v>0.9982397475635021</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7625,7 @@
         <v>59.96599999999995</v>
       </c>
       <c r="C7" t="n">
-        <v>841.8733502328752</v>
+        <v>267.6785606494647</v>
       </c>
       <c r="D7" t="n">
         <v>3.09917e-07</v>
@@ -7927,16 +7658,13 @@
         <v>-8593.148600568107</v>
       </c>
       <c r="Y7" t="n">
-        <v>364.2640681413171</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>396827873.48667</v>
+        <v>131.3870313304807</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.308082413939267e-07</v>
+        <v>3.820887994510057e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9497996930235951</v>
+        <v>0.9457200323765764</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7675,7 @@
         <v>58.38999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1169.813453066938</v>
+        <v>58.38999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>3.07858e-07</v>
@@ -7979,11 +7707,10 @@
       <c r="X8" t="n">
         <v>-8896.116349278796</v>
       </c>
-      <c r="Y8" t="n">
-        <v>359.8727291974537</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>390775907.6157731</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>4.206757934116415e-07</v>
@@ -8000,7 +7727,7 @@
         <v>57.78399999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>1310.533998997833</v>
+        <v>258.6632438062138</v>
       </c>
       <c r="D9" t="n">
         <v>3.06218e-07</v>
@@ -8033,16 +7760,13 @@
         <v>-9358.576339660338</v>
       </c>
       <c r="Y9" t="n">
-        <v>355.6000456648105</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>385922392.4631255</v>
+        <v>124.5823931737697</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.134157118207357e-07</v>
+        <v>2.224264618925232e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9542196711932915</v>
+        <v>0.9876131771547531</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7777,7 @@
         <v>54.15499999999997</v>
       </c>
       <c r="C10" t="n">
-        <v>928.710326703539</v>
+        <v>290.797738895604</v>
       </c>
       <c r="D10" t="n">
         <v>3.05109e-07</v>
@@ -8086,16 +7810,13 @@
         <v>-8897.997046131297</v>
       </c>
       <c r="Y10" t="n">
-        <v>351.5281863840216</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>477110066.2016164</v>
+        <v>88.07387967214989</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.061003800676828e-07</v>
+        <v>2.014724352977579e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9563502490182813</v>
+        <v>0.9796621967942323</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7827,7 @@
         <v>54.13499999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1445.18318297676</v>
+        <v>271.2920793308095</v>
       </c>
       <c r="D11" t="n">
         <v>3.04068e-07</v>
@@ -8139,16 +7860,13 @@
         <v>-9576.223069857489</v>
       </c>
       <c r="Y11" t="n">
-        <v>347.6232157561738</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>422618805.0285129</v>
+        <v>103.0968507015975</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.012325572343066e-07</v>
+        <v>2.031787738120481e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9576712444619498</v>
+        <v>0.9875130401683181</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +8023,7 @@
         <v>123.476</v>
       </c>
       <c r="C2" t="n">
-        <v>1221.290708550385</v>
+        <v>284.7870706503472</v>
       </c>
       <c r="D2" t="n">
         <v>3.16062e-07</v>
@@ -8338,16 +8056,13 @@
         <v>-8041.755187989226</v>
       </c>
       <c r="Y2" t="n">
-        <v>446.0615595429655</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>49464944.57555766</v>
+        <v>204.8931155283007</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.718361790685231e-07</v>
+        <v>3.689970887188415e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9099393122285412</v>
+        <v>0.9555178336670825</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +8073,7 @@
         <v>105.87</v>
       </c>
       <c r="C3" t="n">
-        <v>880.6467379084125</v>
+        <v>105.87</v>
       </c>
       <c r="D3" t="n">
         <v>3.06331e-07</v>
@@ -8390,11 +8105,10 @@
       <c r="X3" t="n">
         <v>-9910.926835935528</v>
       </c>
-      <c r="Y3" t="n">
-        <v>434.7989703482187</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>712446686.4799011</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>4.7944172539051e-07</v>
@@ -8411,7 +8125,7 @@
         <v>100.762</v>
       </c>
       <c r="C4" t="n">
-        <v>820.5134001577698</v>
+        <v>265.1714157632723</v>
       </c>
       <c r="D4" t="n">
         <v>3.02365e-07</v>
@@ -8444,16 +8158,13 @@
         <v>-10531.45082497798</v>
       </c>
       <c r="Y4" t="n">
-        <v>429.7643533837178</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>176218480.1840758</v>
+        <v>206.3019866644949</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.528820728558591e-07</v>
+        <v>4.01572643234939e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9383162380497957</v>
+        <v>0.9566481300112695</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8175,7 @@
         <v>97.35000000000002</v>
       </c>
       <c r="C5" t="n">
-        <v>826.9341288155427</v>
+        <v>269.3187909689832</v>
       </c>
       <c r="D5" t="n">
         <v>3.00137e-07</v>
@@ -8497,16 +8208,13 @@
         <v>-10873.96235495501</v>
       </c>
       <c r="Y5" t="n">
-        <v>425.250014563747</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>348281728.977523</v>
+        <v>197.2919482908067</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.389175667214527e-07</v>
+        <v>3.990477535434941e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.941933419288708</v>
+        <v>0.9555305550340143</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8225,7 @@
         <v>93.16399999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>788.3456379760891</v>
+        <v>254.7213969374991</v>
       </c>
       <c r="D6" t="n">
         <v>2.98912e-07</v>
@@ -8550,16 +8258,13 @@
         <v>-10421.73861125145</v>
       </c>
       <c r="Y6" t="n">
-        <v>420.4541593279544</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>344473786.5084239</v>
+        <v>205.1791209890987</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.292759090466947e-07</v>
+        <v>3.695019995627369e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9446654181731156</v>
+        <v>0.9667435526669967</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8275,7 @@
         <v>91.79200000000003</v>
       </c>
       <c r="C7" t="n">
-        <v>807.5802699151379</v>
+        <v>249.3252643342661</v>
       </c>
       <c r="D7" t="n">
         <v>2.97741e-07</v>
@@ -8603,16 +8308,13 @@
         <v>-10718.83333377476</v>
       </c>
       <c r="Y7" t="n">
-        <v>415.4928506164291</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>905917161.1646137</v>
+        <v>204.3462658281587</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.218264874034907e-07</v>
+        <v>3.589545864023521e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9467339810742762</v>
+        <v>0.9698860153875035</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8325,7 @@
         <v>88.84000000000003</v>
       </c>
       <c r="C8" t="n">
-        <v>818.9506023671506</v>
+        <v>263.4759152583686</v>
       </c>
       <c r="D8" t="n">
         <v>2.97057e-07</v>
@@ -8656,16 +8358,13 @@
         <v>-10854.50825440769</v>
       </c>
       <c r="Y8" t="n">
-        <v>410.6932870237622</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>448082915.096775</v>
+        <v>185.3483289009337</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.162164143340568e-07</v>
+        <v>3.42159669722858e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9484224799859466</v>
+        <v>0.9672983795687689</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8375,7 @@
         <v>87.959</v>
       </c>
       <c r="C9" t="n">
-        <v>887.4766272188973</v>
+        <v>263.4462017747335</v>
       </c>
       <c r="D9" t="n">
         <v>2.96572e-07</v>
@@ -8709,16 +8408,13 @@
         <v>-11833.50793657148</v>
       </c>
       <c r="Y9" t="n">
-        <v>406.1558589451604</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>332301901.3206196</v>
+        <v>179.8183991103699</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.109958591551783e-07</v>
+        <v>3.359119330104113e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.95008404773359</v>
+        <v>0.9665603706025999</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8425,7 @@
         <v>84.37299999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>846.8675302132741</v>
+        <v>263.8845853519771</v>
       </c>
       <c r="D10" t="n">
         <v>2.95921e-07</v>
@@ -8762,16 +8458,13 @@
         <v>-11191.99089146436</v>
       </c>
       <c r="Y10" t="n">
-        <v>401.9571716444201</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>227694574.6184389</v>
+        <v>174.2864962991475</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.069792562363318e-07</v>
+        <v>3.246624085884148e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.951253090629922</v>
+        <v>0.9688064383274437</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8475,7 @@
         <v>82.64500000000004</v>
       </c>
       <c r="C11" t="n">
-        <v>855.0872161340203</v>
+        <v>82.64500000000004</v>
       </c>
       <c r="D11" t="n">
         <v>2.95583e-07</v>
@@ -8814,11 +8507,10 @@
       <c r="X11" t="n">
         <v>-11088.9380627502</v>
       </c>
-      <c r="Y11" t="n">
-        <v>398.0315089045411</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>162656832.7226542</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>4.029520022061135e-07</v>
@@ -8835,7 +8527,7 @@
         <v>80.87399999999997</v>
       </c>
       <c r="C12" t="n">
-        <v>856.0864387289444</v>
+        <v>245.9562497317688</v>
       </c>
       <c r="D12" t="n">
         <v>2.95296e-07</v>
@@ -8868,16 +8560,13 @@
         <v>-11435.84828978607</v>
       </c>
       <c r="Y12" t="n">
-        <v>394.3663317785396</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>322183951.9662494</v>
+        <v>183.098755169194</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.005688885956205e-07</v>
+        <v>3.162098866300597e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9533513092475097</v>
+        <v>0.9771514009325828</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8577,7 @@
         <v>78.54899999999998</v>
       </c>
       <c r="C13" t="n">
-        <v>847.6963118999857</v>
+        <v>244.3001790508072</v>
       </c>
       <c r="D13" t="n">
         <v>2.94949e-07</v>
@@ -8921,16 +8610,13 @@
         <v>-11145.94417561867</v>
       </c>
       <c r="Y13" t="n">
-        <v>390.8797159972684</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>159626181.9120257</v>
+        <v>180.6525275621665</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.965582726027328e-07</v>
+        <v>3.084695737399144e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9546981553563281</v>
+        <v>0.9803286475407739</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8627,7 @@
         <v>78.85699999999997</v>
       </c>
       <c r="C14" t="n">
-        <v>950.2183831556212</v>
+        <v>78.85699999999997</v>
       </c>
       <c r="D14" t="n">
         <v>2.94769e-07</v>
@@ -8973,11 +8659,10 @@
       <c r="X14" t="n">
         <v>-11825.7179390845</v>
       </c>
-      <c r="Y14" t="n">
-        <v>387.5367382017457</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>211283577.515597</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>3.934330596012159e-07</v>
@@ -8994,7 +8679,7 @@
         <v>75.49099999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>812.6264557238651</v>
+        <v>235.8312487161465</v>
       </c>
       <c r="D15" t="n">
         <v>2.94521e-07</v>
@@ -9027,16 +8712,13 @@
         <v>-10963.16330667192</v>
       </c>
       <c r="Y15" t="n">
-        <v>384.2435141102533</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>157013075.8890429</v>
+        <v>182.2590726081895</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.919390020539939e-07</v>
+        <v>3.101973801391645e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9562638114744985</v>
+        <v>0.9839635944491574</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8729,7 @@
         <v>75.44800000000004</v>
       </c>
       <c r="C16" t="n">
-        <v>925.7263499796172</v>
+        <v>75.44800000000004</v>
       </c>
       <c r="D16" t="n">
         <v>2.94213e-07</v>
@@ -9079,11 +8761,10 @@
       <c r="X16" t="n">
         <v>-11663.67757229711</v>
       </c>
-      <c r="Y16" t="n">
-        <v>381.0008670321984</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>103747707.3303173</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>3.892789259204391e-07</v>
@@ -9100,7 +8781,7 @@
         <v>73.67500000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>846.5147418101699</v>
+        <v>73.67500000000001</v>
       </c>
       <c r="D17" t="n">
         <v>2.94177e-07</v>
@@ -9132,11 +8813,10 @@
       <c r="X17" t="n">
         <v>-11367.48987197617</v>
       </c>
-      <c r="Y17" t="n">
-        <v>377.7220627897996</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>514012192.685697</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>3.873320049307927e-07</v>
@@ -9153,7 +8833,7 @@
         <v>72.63799999999998</v>
       </c>
       <c r="C18" t="n">
-        <v>944.2973591433489</v>
+        <v>226.7584775273525</v>
       </c>
       <c r="D18" t="n">
         <v>2.93998e-07</v>
@@ -9186,16 +8866,13 @@
         <v>-11271.29471457049</v>
       </c>
       <c r="Y18" t="n">
-        <v>374.5527151661101</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>212232685.4184781</v>
+        <v>180.4883066770728</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.85349753708965e-07</v>
+        <v>2.951506076737327e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9585727838725465</v>
+        <v>0.9914878010548637</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8883,7 @@
         <v>71.65199999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>999.4139095460389</v>
+        <v>268.0008362297931</v>
       </c>
       <c r="D19" t="n">
         <v>2.93884e-07</v>
@@ -9239,16 +8916,13 @@
         <v>-11585.46290314838</v>
       </c>
       <c r="Y19" t="n">
-        <v>371.3988009369948</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>302960231.9717601</v>
+        <v>134.7169168511316</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.833658351484886e-07</v>
+        <v>2.596782463287957e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9593036217779071</v>
+        <v>0.9777074483175497</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8933,7 @@
         <v>69.036</v>
       </c>
       <c r="C20" t="n">
-        <v>873.3150677691416</v>
+        <v>69.036</v>
       </c>
       <c r="D20" t="n">
         <v>2.93564e-07</v>
@@ -9291,11 +8965,10 @@
       <c r="X20" t="n">
         <v>-11087.49140504981</v>
       </c>
-      <c r="Y20" t="n">
-        <v>368.2134716012623</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>400428346.9202821</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>3.806417972160746e-07</v>
@@ -9312,7 +8985,7 @@
         <v>68.30000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>887.2824936258272</v>
+        <v>227.1604942619717</v>
       </c>
       <c r="D21" t="n">
         <v>2.93534e-07</v>
@@ -9345,16 +9018,13 @@
         <v>-11127.63190125026</v>
       </c>
       <c r="Y21" t="n">
-        <v>365.0742796957069</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>198553279.7935685</v>
+        <v>168.8106566591474</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.792317453037878e-07</v>
+        <v>2.752517323209766e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9607785560241461</v>
+        <v>0.9942905203413744</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +9035,7 @@
         <v>67.17000000000002</v>
       </c>
       <c r="C22" t="n">
-        <v>915.4447633939792</v>
+        <v>226.7096702187017</v>
       </c>
       <c r="D22" t="n">
         <v>2.93414e-07</v>
@@ -9398,16 +9068,13 @@
         <v>-11332.96529429052</v>
       </c>
       <c r="Y22" t="n">
-        <v>361.9240765072328</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>99000463.198246</v>
+        <v>165.3573945600585</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.773292748369564e-07</v>
+        <v>2.680274629955195e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9614831580543918</v>
+        <v>0.9954480042504721</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9231,7 @@
         <v>119.649</v>
       </c>
       <c r="C2" t="n">
-        <v>1310.750005406399</v>
+        <v>119.649</v>
       </c>
       <c r="D2" t="n">
         <v>3.22643e-07</v>
@@ -9596,11 +9263,10 @@
       <c r="X2" t="n">
         <v>-5404.922887160995</v>
       </c>
-      <c r="Y2" t="n">
-        <v>407.7407320082067</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>337489321.5219505</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>6.504215717871749e-07</v>
@@ -9617,7 +9283,7 @@
         <v>72.42899999999997</v>
       </c>
       <c r="C3" t="n">
-        <v>1729.054801464142</v>
+        <v>72.42899999999997</v>
       </c>
       <c r="D3" t="n">
         <v>3.16105e-07</v>
@@ -9649,11 +9315,10 @@
       <c r="X3" t="n">
         <v>-7005.26348855395</v>
       </c>
-      <c r="Y3" t="n">
-        <v>380.7046700202453</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>206907814.4940717</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>4.936258015863929e-07</v>
@@ -9670,7 +9335,7 @@
         <v>64.93199999999996</v>
       </c>
       <c r="C4" t="n">
-        <v>1202.795213539822</v>
+        <v>212.4241972311438</v>
       </c>
       <c r="D4" t="n">
         <v>3.09133e-07</v>
@@ -9703,16 +9368,13 @@
         <v>-8202.642918390571</v>
       </c>
       <c r="Y4" t="n">
-        <v>373.3274848692083</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>205592457.0210522</v>
+        <v>191.9080645761296</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.481677780507303e-07</v>
+        <v>2.87360510984047e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9435191502944668</v>
+        <v>0.9979894503844331</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9385,7 @@
         <v>61.55399999999997</v>
       </c>
       <c r="C5" t="n">
-        <v>1181.719827759418</v>
+        <v>340.6277595297462</v>
       </c>
       <c r="D5" t="n">
         <v>3.04231e-07</v>
@@ -9756,16 +9418,13 @@
         <v>-8793.679850124627</v>
       </c>
       <c r="Y5" t="n">
-        <v>368.4710785370489</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>200433486.6227811</v>
+        <v>56.8379120252248</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.242455604650512e-07</v>
+        <v>1.944800812258998e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9493545127657979</v>
+        <v>0.9633455369410669</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9435,7 @@
         <v>59.298</v>
       </c>
       <c r="C6" t="n">
-        <v>1318.808614792707</v>
+        <v>262.6418339825732</v>
       </c>
       <c r="D6" t="n">
         <v>3.01126e-07</v>
@@ -9809,16 +9468,13 @@
         <v>-9406.968541564451</v>
       </c>
       <c r="Y6" t="n">
-        <v>363.6699620977606</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>641576592.0366459</v>
+        <v>129.6633289268872</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.078205554322477e-07</v>
+        <v>2.25505082308554e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9537441635662159</v>
+        <v>0.9859576527848225</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9485,7 @@
         <v>54.553</v>
       </c>
       <c r="C7" t="n">
-        <v>909.5698410792626</v>
+        <v>277.1635315317897</v>
       </c>
       <c r="D7" t="n">
         <v>2.99036e-07</v>
@@ -9862,16 +9518,13 @@
         <v>-8700.101075581944</v>
       </c>
       <c r="Y7" t="n">
-        <v>358.5567049748257</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>194574662.7637895</v>
+        <v>109.1063815327246</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.980646115841885e-07</v>
+        <v>2.054973014996458e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9563507607161409</v>
+        <v>0.9853302693990088</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9535,7 @@
         <v>52.47500000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>997.6380588089178</v>
+        <v>278.7694895087054</v>
       </c>
       <c r="D8" t="n">
         <v>2.97612e-07</v>
@@ -9915,16 +9568,13 @@
         <v>-8746.053549221731</v>
       </c>
       <c r="Y8" t="n">
-        <v>353.2594697064274</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>191884537.7166275</v>
+        <v>101.3913767918073</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.91681072647163e-07</v>
+        <v>1.94983875479594e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9580796125801069</v>
+        <v>0.9875606215530723</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9585,7 @@
         <v>50.22800000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1000.827568287667</v>
+        <v>250.2821874905183</v>
       </c>
       <c r="D9" t="n">
         <v>2.9661e-07</v>
@@ -9968,16 +9618,13 @@
         <v>-8815.579496827868</v>
       </c>
       <c r="Y9" t="n">
-        <v>348.1448526875594</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>188760106.866369</v>
+        <v>124.0587381686861</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.848303036038166e-07</v>
+        <v>2.032705174252774e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9602279590496431</v>
+        <v>0.9971797572280874</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9635,7 @@
         <v>52.488</v>
       </c>
       <c r="C10" t="n">
-        <v>1162.709569721979</v>
+        <v>52.488</v>
       </c>
       <c r="D10" t="n">
         <v>2.95805e-07</v>
@@ -10020,11 +9667,10 @@
       <c r="X10" t="n">
         <v>-10328.27698914494</v>
       </c>
-      <c r="Y10" t="n">
-        <v>343.3575751524845</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>93097461.29632474</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.806756731335172e-07</v>
@@ -10041,7 +9687,7 @@
         <v>46.024</v>
       </c>
       <c r="C11" t="n">
-        <v>1148.667753648627</v>
+        <v>46.024</v>
       </c>
       <c r="D11" t="n">
         <v>2.95183e-07</v>
@@ -10073,11 +9719,10 @@
       <c r="X11" t="n">
         <v>-8761.431537887789</v>
       </c>
-      <c r="Y11" t="n">
-        <v>338.9885421096196</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>298561497.6883295</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.764243893188474e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 26.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>3.798725309185535e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9530863457808189</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>117.903</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>925.4734489101584</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.90149e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-82.578</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1041068919463167</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7571901708706376</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.410547920021136</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.400360935988278</v>
+      </c>
+      <c r="L12" t="n">
+        <v>35.05213241100099</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.15972788560832</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>20.1561106702584</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-10528.52042150222</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-358.3394706645574</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.644509464842502e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9282272543301935</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>113.654</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9639619008846253</v>
+      </c>
+      <c r="D13" t="n">
+        <v>947.5663785469496</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.023872029676063</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.8692e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.01300000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3194170350105707</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8764589634048982</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.612967485542756</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.538647966725787</v>
+      </c>
+      <c r="L13" t="n">
+        <v>42.42233563201433</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.52229951283391</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>23.11016206508113</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-11894.28030228045</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-388.4295271024732</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.389297176198378e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9350586238604292</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107.958</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9156510012467872</v>
+      </c>
+      <c r="D14" t="n">
+        <v>933.8625978900786</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.00906471059737</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.8499e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.279</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4592797322174187</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9493987655603693</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.719065192358483</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.690566899362398</v>
+      </c>
+      <c r="L14" t="n">
+        <v>48.09697425998482</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.57404826736281</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>23.60374103942669</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-11916.57385893646</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-385.3847653737393</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.242214339888221e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9392060758119588</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>103.58</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8785187823889127</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1388.840596195541</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.500681189537145</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.83647e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.505</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4211102207886185</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.041553084626962</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.636379412524552</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.492801616599428</v>
+      </c>
+      <c r="L15" t="n">
+        <v>50.38290558648398</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.6177591529958</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>24.03735103107618</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-11929.57493990915</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-792.891373765887</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.12948038816336e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9425650833111668</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102.116</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8661017955437942</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1020.816120160575</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.103020428476573</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.82578e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.648</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7438327345209143</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.034266456818511</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.709815556179475</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.695556472436689</v>
+      </c>
+      <c r="L16" t="n">
+        <v>53.70633152784784</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.80851140963313</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>26.13193448314385</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-12825.70675385108</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-477.3781490258758</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.054320414649394e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9447859928135186</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>95.48899999999998</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8098945743534937</v>
+      </c>
+      <c r="D17" t="n">
+        <v>262.8303607246793</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2839955711686699</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.81836e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.807</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.147417332115022</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.017025421234522</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.686158249670316</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.640603862558927</v>
+      </c>
+      <c r="L17" t="n">
+        <v>57.45287459411578</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.65940662234762</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>24.46554989254422</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-11753.45510055545</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>208.2551128373564</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.489763074393932e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9699086017519417</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>94.00800000000004</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7973334011857206</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1005.023536689375</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.085956099413652</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.8107e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.911</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5572059038139808</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.005477295259697</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.703728397584137</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.726851858051247</v>
+      </c>
+      <c r="L18" t="n">
+        <v>58.25520901569743</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.82088398768474</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>26.2804506968728</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-12489.76538931573</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-478.3430195522815</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.931125257048022e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9486616057469494</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>89.97500000000002</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7631273165229044</v>
+      </c>
+      <c r="D19" t="n">
+        <v>915.5715408401276</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9893007108073264</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.80569e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.02</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4414859778278686</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8971566539454259</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.526514573407282</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.53973522403997</v>
+      </c>
+      <c r="L19" t="n">
+        <v>58.41285318654739</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.74775265988983</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>25.42627719299446</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-11877.6660878247</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-405.7133989405311</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.883145652609311e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9502519050183637</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>88.03399999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7466646310950525</v>
+      </c>
+      <c r="D20" t="n">
+        <v>948.4804994604174</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.024859762943337</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.80002e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.11499999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3162438204802794</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9993338726209192</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.594613704458701</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.742590203472785</v>
+      </c>
+      <c r="L20" t="n">
+        <v>61.36584037254693</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.83208426718163</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>26.41635621116027</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-12204.34182404864</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-440.8977863843901</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.840786656903262e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9516203682861243</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>85.86799999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7282935972791191</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1534.265494761998</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.657816868294553</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.79627e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.221</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4522738789671745</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.074834127576395</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.677939947690956</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.876477818422292</v>
+      </c>
+      <c r="L21" t="n">
+        <v>64.1620202612273</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.88271007747976</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>27.04858506982115</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-12358.87300405674</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-967.9274313354755</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.798725309185535e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9530863457808189</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>3.675113956423256e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9623619981075533</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>124.576</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>274.4342229897132</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.93127e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-83.024</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2512352603199477</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.848167391707194</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.302515343780633</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.206541293170191</v>
+      </c>
+      <c r="L23" t="n">
+        <v>46.93330012626381</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.2868729892753</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>21.10219978021449</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-10893.99816159297</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>214.2692488973634</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.339189105358211e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9674340520571305</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>102.115</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8197004238376576</v>
+      </c>
+      <c r="D24" t="n">
+        <v>897.835171955873</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.271586036809727</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.92917e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.54600000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2541025803483765</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9021691411039585</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.724181389034442</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.484280407977956</v>
+      </c>
+      <c r="L24" t="n">
+        <v>55.27823998460467</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.5769512123931</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>23.63205341832907</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-11504.33945863282</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-369.483345297918</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.243705039226735e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9433243622168664</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95.654</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7678365014127924</v>
+      </c>
+      <c r="D25" t="n">
+        <v>281.8685431328552</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.027089624836697</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.9212e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.687</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1400792209286618</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8966608118183766</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.62387800334622</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.616102878286876</v>
+      </c>
+      <c r="L25" t="n">
+        <v>58.74302614582464</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.60942894374718</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>23.95349344292101</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-11430.26001686559</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>185.9407069982283</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.493100832784949e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.957599519040699</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92.30600000000004</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7409613408682255</v>
+      </c>
+      <c r="D26" t="n">
+        <v>795.425200844599</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.898418397600558</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.91187e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.82899999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.09920623244385056</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7343813721241941</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.32303098237373</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.358916168452941</v>
+      </c>
+      <c r="L26" t="n">
+        <v>56.28968986408398</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.5998281694382</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>23.85756708838235</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-11224.70583769813</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-294.2726775496425</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.087172028732938e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9481504670151254</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91.33499999999998</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7331669021320318</v>
+      </c>
+      <c r="D27" t="n">
+        <v>880.4214234868388</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.208132768192836</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.90558e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.934</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3692688177840676</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9858160041664266</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.705643425435256</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.640998369601589</v>
+      </c>
+      <c r="L27" t="n">
+        <v>62.54354667363317</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.80859278634296</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>26.1329058253196</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-12214.07350323225</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-374.9755380095908</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.036382757990266e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9497215596288465</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>88.60599999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7112605959414335</v>
+      </c>
+      <c r="D28" t="n">
+        <v>849.9977236173038</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.09727305274592</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.90046e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.021</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2876184136939834</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9087179325677058</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.665624632193091</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.735465585034756</v>
+      </c>
+      <c r="L28" t="n">
+        <v>66.11487272003404</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.76536653264944</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>25.62689850182742</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-11820.21700253824</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-353.125221338867</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.996979035424695e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9509545690055515</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>86.69299999999998</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6959045080914462</v>
+      </c>
+      <c r="D29" t="n">
+        <v>873.0966958351132</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.181442483096724</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.89592e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.09099999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3206527290458294</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8377581427668525</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.682365673612392</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.678775078082334</v>
+      </c>
+      <c r="L29" t="n">
+        <v>66.38575140201544</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.80262087592632</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>26.06181391361173</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-11887.29217957252</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-378.457072554513</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.9640601027699e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9519725757353761</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>84.95099999999996</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6819210762907782</v>
+      </c>
+      <c r="D30" t="n">
+        <v>874.0253082604949</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.184826217148786</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.89145e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.19</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2387408756064689</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.95123768973764</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.788413332746165</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.770771819141239</v>
+      </c>
+      <c r="L30" t="n">
+        <v>69.10896448725924</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.85089048505542</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>26.64773770317868</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-12030.07192896979</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-384.2957517597699</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.922137922553009e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9533537694411272</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>84.07600000000002</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6748972514770104</v>
+      </c>
+      <c r="D31" t="n">
+        <v>931.4566704279327</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.394098083980025</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.88963e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.23</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.55146302771261</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.003076447349542</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.749768262263124</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.640376314393161</v>
+      </c>
+      <c r="L31" t="n">
+        <v>64.26475751348413</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.92629413956762</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>27.61759058771168</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-12366.10545753141</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-439.9775583044109</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.904469143793302e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9539474292666617</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>82.34000000000003</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6609619830464941</v>
+      </c>
+      <c r="D32" t="n">
+        <v>955.305779429876</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.481000908059795</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.88777e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.30500000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6038148698054053</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.099727367502073</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.83739291466896</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.785260913370318</v>
+      </c>
+      <c r="L32" t="n">
+        <v>68.30870953623896</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.97949672654772</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>28.34542643957678</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-12585.91718424231</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-465.2504899987712</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.877393003707262e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9549043810237576</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79.61699999999996</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6391038402260466</v>
+      </c>
+      <c r="D33" t="n">
+        <v>881.0847316307563</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.21054977047736</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.88503e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.361</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4339865350767734</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9060177607492955</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.74330724485701</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.696143866859491</v>
+      </c>
+      <c r="L33" t="n">
+        <v>68.71468099378681</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.91906736815051</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>27.52159482215613</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-12076.69488488927</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-402.6189173280182</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.854281908457652e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9556753487634708</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78.13599999999997</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6272155150269714</v>
+      </c>
+      <c r="D34" t="n">
+        <v>867.050468421151</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.159410874399768</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.88355e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.414</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3476471371410548</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.96148350437282</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.63699611886058</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.612588019127885</v>
+      </c>
+      <c r="L34" t="n">
+        <v>67.14256464722857</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.91606963940927</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>27.48197021391608</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-11945.45472151515</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-394.1906458897204</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.83453242085289e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9563801137233561</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>77.274</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.620296044181865</v>
+      </c>
+      <c r="D35" t="n">
+        <v>912.1027312358133</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.323575031201564</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.88254e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.48099999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2703678246490247</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.170152926426403</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.773711834298076</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.754006800679737</v>
+      </c>
+      <c r="L35" t="n">
+        <v>70.95013926165225</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.97033293113847</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>28.21734255105922</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-12168.58682462352</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-437.9233043508775</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.812314796101391e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9572038175700905</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>76.548</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6144682763935271</v>
+      </c>
+      <c r="D36" t="n">
+        <v>227.914055901343</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8304870049311817</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.88131e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.52500000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3628685771184439</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.080330694159237</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.70153546192528</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.814265173938503</v>
+      </c>
+      <c r="L36" t="n">
+        <v>71.03695818615459</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.99980391079097</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>28.63344364617319</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-12247.84783957728</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>193.4820438404058</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.05859187170992e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9899072608897677</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>74.05900000000003</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5944885050089909</v>
+      </c>
+      <c r="D37" t="n">
+        <v>901.3407663008661</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.284359933253119</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.87906e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.575</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3038978515465716</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9756630456174533</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.688363114216435</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.712043805255144</v>
+      </c>
+      <c r="L37" t="n">
+        <v>71.5557900233691</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.93312207283692</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>27.70890491712827</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11721.62250437071</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-435.2121518770384</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.776512885782103e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9584622893124256</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>66.12599999999998</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5308085024402773</v>
+      </c>
+      <c r="D38" t="n">
+        <v>820.4289702263801</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.989528642924147</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.87923e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.623</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6983392137162192</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.831133003085855</v>
+      </c>
+      <c r="L38" t="n">
+        <v>57.45719279946421</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.29025771961543</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>21.12859788937235</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-8707.14723446308</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-366.2435020529643</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.761299651783017e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9590897539619861</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>72.68599999999998</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5834671204726432</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1000.148046743616</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.64439987056973</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.87619e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.688</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4190339336780965</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.130407705845098</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.993685706434679</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.016144645850049</v>
+      </c>
+      <c r="L39" t="n">
+        <v>75.31595694543999</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.08667786806856</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>29.93457259153982</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-12491.80891613518</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-530.4753962721647</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.737574662623318e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9598955535278331</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>71.12200000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.570912535319805</v>
+      </c>
+      <c r="D40" t="n">
+        <v>941.8841856717892</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.432094493940336</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.87722e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.718</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2802140777179493</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8417064449295014</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.582656702705093</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.703839375430295</v>
+      </c>
+      <c r="L40" t="n">
+        <v>69.27967284442853</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.04864330120701</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>29.35066920045311</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-12118.93204433167</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-481.6846808845174</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.729394438623448e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9602842805704072</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>70.23500000000001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5637923837657336</v>
+      </c>
+      <c r="D41" t="n">
+        <v>952.0747393123982</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.469227448896143</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.87617e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.75700000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4864753798457531</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9924731659884757</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.615954422437696</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.733754325424914</v>
+      </c>
+      <c r="L41" t="n">
+        <v>70.98514568767096</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.10185855007521</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>30.17415636788073</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-12363.80096203343</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-494.3883362826859</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.715255539773576e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9608144794824224</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>68.12400000000002</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5468469047007453</v>
+      </c>
+      <c r="D42" t="n">
+        <v>881.7059512908731</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.21281340820209</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.87411e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.804</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.04589902996738593</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6003755291315627</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.468824838368393</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.302483264452519</v>
+      </c>
+      <c r="L42" t="n">
+        <v>66.4104827663359</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.97360636318649</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>28.26296291251735</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-11432.83107502408</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-434.5842682602408</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.698263627206813e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9614076767052351</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>67.43799999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5413402260467506</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1009.847959568096</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.679744998880655</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.87422e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.884</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4027869637479747</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.112263000123599</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.619886778613026</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.657833435524025</v>
+      </c>
+      <c r="L43" t="n">
+        <v>72.79886798513982</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.13005146655154</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>30.62941788190355</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-12330.55693840722</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-552.8427784199175</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.675113956423256e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9623619981075533</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>3.535345658232639e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9625544206255605</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>130.665</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>331.0890688369926</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.86232e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-82.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3600212400616191</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8229670923061693</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.24803472987224</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.005562186327212</v>
+      </c>
+      <c r="L23" t="n">
+        <v>37.27369957969715</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.16748780124932</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>20.21142054751816</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-10616.00920003734</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>164.3334829510567</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.915724094203368e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9540207238737671</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>107.914</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8258829832013161</v>
+      </c>
+      <c r="D24" t="n">
+        <v>943.5308217089082</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.849779441596253</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.8313e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.64400000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.22385227896093</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6812874297643916</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.718230566209016</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.644023758290732</v>
+      </c>
+      <c r="L24" t="n">
+        <v>57.76290309662167</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.6572350131018</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>24.44284646434752</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-12113.06451025192</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-400.1794501583759</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.103164652903575e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9432058677849767</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100.812</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7715302491103203</v>
+      </c>
+      <c r="D25" t="n">
+        <v>835.1399051784682</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.522402530871952</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.82244e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.857</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1607162132968337</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6409050587735816</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.438259069322984</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.416153899092635</v>
+      </c>
+      <c r="L25" t="n">
+        <v>62.10286809543291</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.63265752327231</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>24.18879896270412</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-11731.88806083015</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-314.9471153587801</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.996858848909126e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9467148891320274</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99.36799999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.760479087743466</v>
+      </c>
+      <c r="D26" t="n">
+        <v>888.9535749147212</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.684937856865295</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.81385e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.01300000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4422891215339908</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8741626181170586</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.640402312331293</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.741319449131894</v>
+      </c>
+      <c r="L26" t="n">
+        <v>69.601400226964</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.82827567892951</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>26.36998513322005</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-12691.81067537729</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-367.793378742598</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.922750191135162e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9490935729409444</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98.72300000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.75554280029082</v>
+      </c>
+      <c r="D27" t="n">
+        <v>303.4240487132113</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9164423633164348</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.80933e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.089</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6625664374199612</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.131441309717978</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.04422972330892</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.829235971654585</v>
+      </c>
+      <c r="L27" t="n">
+        <v>70.52771294337612</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.9857801852595</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>28.43392464212173</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-13581.75687219688</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>162.6004877109668</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.22255554170634e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.956846782497204</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>94.12</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.720315310144262</v>
+      </c>
+      <c r="D28" t="n">
+        <v>910.0180740350421</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.748559707004635</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.8037e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5742009206833052</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9547246285750206</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.586238565801825</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.72101020733512</v>
+      </c>
+      <c r="L28" t="n">
+        <v>71.85915493200078</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.88563877351126</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>27.08608537804733</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-12742.01062557794</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-397.0792477715287</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.837094757095452e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9519092750934792</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91.20599999999996</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6980140052806791</v>
+      </c>
+      <c r="D29" t="n">
+        <v>891.53048219238</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.69272098086486</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.79929e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.248</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2922844361609989</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9979399673117147</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.702631678213623</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.717897920283384</v>
+      </c>
+      <c r="L29" t="n">
+        <v>73.00086864351213</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.84211171119026</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>26.53922676840831</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-12321.75268154482</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-385.7550818467838</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.811227722378589e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9527127075400116</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>88.53199999999998</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6775494585390117</v>
+      </c>
+      <c r="D30" t="n">
+        <v>854.9267704891149</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.582165498523381</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.79486e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.34</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2565641828460719</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8215043642565779</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.498250731075971</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.321414077576915</v>
+      </c>
+      <c r="L30" t="n">
+        <v>68.64720800059978</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.81077802907492</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>26.15901667477477</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-11994.22531311118</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-358.3498913329102</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.773477702498862e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9539794355618256</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>88.53300000000002</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6775571116978533</v>
+      </c>
+      <c r="D31" t="n">
+        <v>940.4989526657678</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.840622180519074</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.79076e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.395</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5643059452032864</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.063140900566231</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.749846662644471</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.866094091660867</v>
+      </c>
+      <c r="L31" t="n">
+        <v>75.38015616489049</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.01800130936564</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>28.89654969394406</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-13193.13106233725</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-438.8823305615233</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.747474974519782e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9548203659574124</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>84.98000000000002</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6503654383346726</v>
+      </c>
+      <c r="D32" t="n">
+        <v>850.6756676973</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.569325742723687</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.78869e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.46299999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1837260412898271</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7240862177950693</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.493079917015439</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.381524722966315</v>
+      </c>
+      <c r="L32" t="n">
+        <v>67.83620879345189</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.85323310865101</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>26.67684388052558</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-11998.70370759429</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-363.2952867580642</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.723001494175352e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9557007984034693</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>84.505</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6467301878850494</v>
+      </c>
+      <c r="D33" t="n">
+        <v>927.3846385427815</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.801012554719429</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.78439e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.51300000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5118563139027209</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9915241334210009</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.828756220847229</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.894467564747913</v>
+      </c>
+      <c r="L33" t="n">
+        <v>76.94642905001851</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.98135449886084</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>28.37153454577687</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-12691.91203782742</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-435.2748043159257</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.69921281257965e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9564516825215468</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>81.95299999999997</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6271993265220217</v>
+      </c>
+      <c r="D34" t="n">
+        <v>836.3384260671077</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.526022465812268</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.78444e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.59099999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.229574198938836</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9591626325384028</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.440958985178526</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.711599983137088</v>
+      </c>
+      <c r="L34" t="n">
+        <v>78.67533256097008</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.88812665941559</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>27.11802302793079</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-11990.52759832771</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-357.6376152195606</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.676299454202607e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9573820159405703</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>82.452</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6310182527838364</v>
+      </c>
+      <c r="D35" t="n">
+        <v>966.7349417509673</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.919863664320874</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.78023e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.634</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.434347803510383</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.1654470645435</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.750674704226418</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.653867351619731</v>
+      </c>
+      <c r="L35" t="n">
+        <v>76.68999139548374</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.08061811441863</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>29.83999460472886</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-13156.68338917681</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-477.3590766584661</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.655139131372438e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9580468525529097</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80.90600000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6191864692151685</v>
+      </c>
+      <c r="D36" t="n">
+        <v>954.0617689352111</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.881586433181009</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.77878e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.67400000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3581469239357987</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.110958083027211</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.731239591873874</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.955912051940919</v>
+      </c>
+      <c r="L36" t="n">
+        <v>80.23092062108162</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.05976693628509</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>29.51907062672297</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-12896.85828247652</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-469.4621654694121</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.640811067707824e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9585676382009772</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80.49200000000002</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6160180614548656</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1019.450435185102</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.079082129670113</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.77814e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.73399999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.552221576868164</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.086425363667317</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.719905321973447</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.687186675053379</v>
+      </c>
+      <c r="L37" t="n">
+        <v>78.46040035667616</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.12428578359595</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>30.53520034536186</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-13256.57052013853</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-530.9670108246694</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.622292421104758e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9593012392197026</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>77.25700000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5912600926032219</v>
+      </c>
+      <c r="D38" t="n">
+        <v>866.5884960920268</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.617387819948475</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.77535e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.78400000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.05290098768978027</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9590140365690504</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.559722965709733</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.618335644462825</v>
+      </c>
+      <c r="L38" t="n">
+        <v>79.44420053515682</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.96101903435023</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>28.08833991609548</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-12033.08820502537</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-397.722143473735</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.602866626102672e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9599731408910596</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>76.15100000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5827956989247312</v>
+      </c>
+      <c r="D39" t="n">
+        <v>289.0086866513669</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8729031365081296</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.77327e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.78700000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3624428162188722</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.122833573650907</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.474612146390854</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.513094994956028</v>
+      </c>
+      <c r="L39" t="n">
+        <v>74.05327803520163</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.06409994133189</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>29.58519181281325</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-12606.35367654404</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>131.0509344060565</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.535146655948013e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9739405930192611</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>75.38399999999996</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5769257260934446</v>
+      </c>
+      <c r="D40" t="n">
+        <v>968.0236177707841</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.923755897985801</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.77195e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.83799999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4034514158358037</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.067242666212434</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.574615982544359</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.630045237407072</v>
+      </c>
+      <c r="L40" t="n">
+        <v>75.21478965581689</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.08612077263473</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>29.92585269978194</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-12652.62730287282</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-494.6648337470609</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.581488370121684e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9607099646315932</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>75.06399999999996</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5744767152642249</v>
+      </c>
+      <c r="D41" t="n">
+        <v>284.5045847158586</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8592992384654377</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.77176e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.887</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6268528781091085</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.196578914362779</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.912250809512006</v>
+      </c>
+      <c r="K41" t="n">
+        <v>32.75985454284132</v>
+      </c>
+      <c r="L41" t="n">
+        <v>84.84577709147541</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.17568511874825</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>31.39612385328766</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-13197.96299407448</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>128.4446479185418</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.429271300694061e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9760738446723771</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>72.54699999999997</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5552137144606433</v>
+      </c>
+      <c r="D42" t="n">
+        <v>929.8799978846436</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.80854937661037</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.77071e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.929</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3365109060421372</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9468225981315942</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.647341199457379</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.822053814067768</v>
+      </c>
+      <c r="L42" t="n">
+        <v>80.13303696312042</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.08851357296426</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>29.96334177061874</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-12456.51290675694</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-466.8277314267241</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.553098167449959e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9618548408621095</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>72.42900000000003</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.554310641717369</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1020.560037430549</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.082433500494116</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.76954e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.98399999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4727542272050645</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8748072041229972</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.777549632949711</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.691994887180107</v>
+      </c>
+      <c r="L43" t="n">
+        <v>78.48110321966709</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.15884904291873</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>31.10883258305458</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-12847.91731832053</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-551.2025052038612</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.535345658232639e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9625544206255605</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.741848779331559e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.6237127932622879</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>122.949</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>247.355963021763</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.18192e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-79.95399999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2486354225527059</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6714478542524092</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.109033236476308</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.959900662164001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14.59981922073361</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.98650107467778</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.39911969021538</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5628.87012266916</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>205.9114456884805</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.29324622393053e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9958642887745359</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>81.48099999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6627219416180695</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1497.379878350867</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.053542676143707</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.16511e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.804</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3106808278072673</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6647876557839623</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.242120473221649</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.079642521545655</v>
+      </c>
+      <c r="L13" t="n">
+        <v>19.79920760243862</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.26403278851514</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.31452287733149</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6739.300166576242</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-941.9492851316295</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.237797684194312e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9236904914511486</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>72.35199999999998</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5884716427136455</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1114.88083801042</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.50719208217483</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.11561e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.575</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.03977054612979009</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.544466590481647</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.374963641849194</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.143646586392438</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.23297493977025</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.74681597819193</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17.59328562237409</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7506.888128436009</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-623.2178308031694</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.798370131338431e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9344184471706958</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>65.51499999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5328632197089851</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1086.396396492014</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.392036412707909</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.0739e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.045</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1951650729250658</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.037113341151677</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.978444616411733</v>
+      </c>
+      <c r="L15" t="n">
+        <v>27.52078854418912</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.84154626007687</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>18.12207346971224</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-7557.432651308401</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-605.669349063417</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.544229231216149e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9405488265181526</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>67.685</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5505128142563179</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1309.608236240773</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.294427594314961</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.04238e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.39100000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4033259512610427</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.037183714466633</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.559090716977245</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.259709780525882</v>
+      </c>
+      <c r="L16" t="n">
+        <v>31.65165128221017</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.3257801807214</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.40967156011307</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8910.349587609531</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-812.3507240628953</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.368865707032969e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9449015694633687</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>66.01600000000002</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5369380800169179</v>
+      </c>
+      <c r="D17" t="n">
+        <v>252.3372707766327</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.020138215768146</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.0168e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.64</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4485339825041705</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9646625678734848</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.617087573732252</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.697119035395382</v>
+      </c>
+      <c r="L17" t="n">
+        <v>35.55918453146462</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.44871536883718</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22.44277477716732</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-9214.317363509028</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>152.2540599284079</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.51328068498111e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9862867238260468</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>63.15200000000004</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5136438685959225</v>
+      </c>
+      <c r="D18" t="n">
+        <v>317.804240613362</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.284805252846889</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.99736e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.855</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2243178878806035</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.003194481721564</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.447723798099823</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.502804013663294</v>
+      </c>
+      <c r="L18" t="n">
+        <v>37.49646967008415</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.53264740503607</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>23.20720504156621</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9385.325435555385</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>81.08475700378105</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.056186847512987e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9697719650461623</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>61.90700000000004</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5035177187289044</v>
+      </c>
+      <c r="D19" t="n">
+        <v>310.2370450329593</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.254212921503994</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.98304e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.03400000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4282541859250891</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9659345067671664</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.659962828108113</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.749967811520317</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40.86362303584087</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.65431667172342</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>24.41240237640588</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9752.118087275996</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>83.18873472673852</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.016575231482744e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9734534308304468</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>55.04500000000002</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4477059593815325</v>
+      </c>
+      <c r="D20" t="n">
+        <v>286.2339033282167</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.15717405730394</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.96941e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.175</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2848252879509239</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.085037964328289</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.146226330084619</v>
+      </c>
+      <c r="L20" t="n">
+        <v>39.99985498118237</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.4022985224036</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>22.04122222861748</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-8582.618510701705</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>101.9895029342706</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.028856811366482e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9827277750824734</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56.73999999999995</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4614921634173517</v>
+      </c>
+      <c r="D21" t="n">
+        <v>435.1750477082898</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.759306880626937</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.95913e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.34399999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1837973103988853</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7885759017193569</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.567270559062706</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.459102146294746</v>
+      </c>
+      <c r="L21" t="n">
+        <v>44.73208725880266</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.72653360673159</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>25.18871910416521</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9770.344659172164</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.8358991650716737</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.741848779331559e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.6237127932622879</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>3.70021274462572e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9600280212497452</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>126.205</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1287.172569638919</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.13678e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.658</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2058765328604114</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7419956969701347</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.274985805276694</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.192313757476177</v>
+      </c>
+      <c r="L23" t="n">
+        <v>19.31613270051458</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.91999548823703</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.0193231526774</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7342.52900072193</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-663.5718375399701</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.053319565383948e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.900390592137451</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110.425</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8749653341785184</v>
+      </c>
+      <c r="D24" t="n">
+        <v>948.2166515330358</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7366662978213031</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.01041e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.495</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4803181678963104</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.084835429938533</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.707806969457589</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.473478225758604</v>
+      </c>
+      <c r="L24" t="n">
+        <v>33.55445824603312</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.22616082429083</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>20.639628307175</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-10390.83339015991</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-400.7409377599171</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.806494654655304e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9287117044124438</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>103.639</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8211956737054785</v>
+      </c>
+      <c r="D25" t="n">
+        <v>885.1361628731703</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6876592803103868</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.9619e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.06100000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3843534950201712</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.97034611463559</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.601801299987585</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.583752451124887</v>
+      </c>
+      <c r="L25" t="n">
+        <v>44.05860691554125</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.45954092620003</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>22.53853554475871</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-11150.89014368775</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-353.5863600614772</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.478198723949327e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9368932080426925</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100.742</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7982409571728536</v>
+      </c>
+      <c r="D26" t="n">
+        <v>268.0855049254894</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2082747187509547</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.93403e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.325</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2083235471319146</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.73010938715222</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.390358985880212</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.295733811148132</v>
+      </c>
+      <c r="L26" t="n">
+        <v>45.8776131061818</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.53414503506045</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>23.22131730709238</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-11336.89800182589</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>210.220983607323</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.915809197053948e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9599459871339387</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99.96199999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7920605364288258</v>
+      </c>
+      <c r="D27" t="n">
+        <v>925.6163201729468</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7191081771052681</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.91834e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.526</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6785141872503018</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9906741275250708</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.574629672163514</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.393626956434637</v>
+      </c>
+      <c r="L27" t="n">
+        <v>51.65748212076815</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.74917473387549</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>25.44235809931627</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-12337.34640091743</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-399.7662106520335</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.219761535761566e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9436392171724649</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96.36699999999996</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7635751356919293</v>
+      </c>
+      <c r="D28" t="n">
+        <v>898.5886954140976</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6981105071763393</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.90634e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.682</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.409746399120797</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.036599348843349</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.725119083707579</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.562838363608081</v>
+      </c>
+      <c r="L28" t="n">
+        <v>56.80727640248147</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.71348244619193</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>25.04479354257609</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-11976.82073371826</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-381.3392583619145</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.141469311108859e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9458482919092329</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93.42700000000002</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7402797036567489</v>
+      </c>
+      <c r="D29" t="n">
+        <v>872.7792941031209</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6780592709087604</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.89732e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-83.821</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3081169508986153</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8449285489430668</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.487128083682251</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.248891661438993</v>
+      </c>
+      <c r="L29" t="n">
+        <v>55.23930481460545</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.69605277979372</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>24.85512427709604</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-11729.21161930763</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-363.6070318658349</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.074363927913332e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9478533374320448</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90.64200000000005</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7182124321540353</v>
+      </c>
+      <c r="D30" t="n">
+        <v>891.8524011530907</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6928771030315504</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.89073e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-83.89700000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3630077700262435</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.791829688667647</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.481906569778616</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.23509591683225</v>
+      </c>
+      <c r="L30" t="n">
+        <v>55.96102069211216</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.7401998997705</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>25.34120910511185</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-11836.7168398624</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-385.5786835623087</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.035195149594637e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9489803524992504</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87.065</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6898696565112314</v>
+      </c>
+      <c r="D31" t="n">
+        <v>830.0606559206653</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6448713059147276</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.88377e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.008</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.0006176672374678497</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7647858989714977</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.395732388988384</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.485641604962691</v>
+      </c>
+      <c r="L31" t="n">
+        <v>62.39770614734438</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.6356424929412</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>24.21937175877649</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-11153.35516706003</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-335.0884707174562</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.985999351391694e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9504716295071537</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87.048</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.689734955033477</v>
+      </c>
+      <c r="D32" t="n">
+        <v>875.7364825646559</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6803567005862469</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.87984e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.084</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1770090710500854</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.041563791901073</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.531039304669328</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.502818301864668</v>
+      </c>
+      <c r="L32" t="n">
+        <v>63.92175517333574</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.78529593462031</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>25.8577396104478</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-11838.61701463857</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-379.9754336457712</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.952566190074919e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9515368643922498</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>85.93200000000002</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6808921991997147</v>
+      </c>
+      <c r="D33" t="n">
+        <v>886.1298785687983</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6884312946611174</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.87379e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.184</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2567083334348363</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8530155250713644</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.513482453990546</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.345775412512312</v>
+      </c>
+      <c r="L33" t="n">
+        <v>63.25235561186452</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.84936577478415</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>26.6288278269505</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-12099.65098283132</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-393.149337991157</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.909901082707743e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9528706943422542</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>84.14599999999996</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6667406204191587</v>
+      </c>
+      <c r="D34" t="n">
+        <v>920.1621395243445</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7148708426737767</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.87175e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.221</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3974558107605298</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8745597324269975</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.668040300294117</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.724596135045102</v>
+      </c>
+      <c r="L34" t="n">
+        <v>68.17427640768834</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.86399750088029</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>26.81140751899467</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-12075.26208024579</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-427.3789600171397</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.892524334501335e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9534430418002374</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>82.01800000000003</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.649879164850838</v>
+      </c>
+      <c r="D35" t="n">
+        <v>897.2628773871375</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6970804836517298</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.86733e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.307</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.387778184348667</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8889864403677089</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.612039977034764</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.463517635105662</v>
+      </c>
+      <c r="L35" t="n">
+        <v>67.03066965731426</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.85234410351843</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>26.66579086864423</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-11892.42657330367</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-410.5784035415787</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.858002570018155e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9545566499509672</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79.80900000000003</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6323758963590983</v>
+      </c>
+      <c r="D36" t="n">
+        <v>842.8288224538289</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6547908511523529</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.86526e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.364</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.07897212754286122</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8589548346795397</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.556185908640746</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.403946534046326</v>
+      </c>
+      <c r="L36" t="n">
+        <v>68.27596158378329</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.78208836734723</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>25.82030657160209</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-11390.89846302218</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-365.3584476695822</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.835552427151432e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.955336312918865</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80.65700000000004</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6390951230141437</v>
+      </c>
+      <c r="D37" t="n">
+        <v>961.0566683054243</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.746641663265884</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.8616e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.419</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3183689671825659</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.086005479311529</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.688127574696928</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.836471696111994</v>
+      </c>
+      <c r="L37" t="n">
+        <v>72.73033515571784</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.94582166090663</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>27.88035848616979</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-12253.84147005952</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-474.2266033700555</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.812783269214345e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9560525719159558</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78.88200000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6250307040133115</v>
+      </c>
+      <c r="D38" t="n">
+        <v>927.959308185643</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7209284365389766</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.85864e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.467</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4281340566556781</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.089129174027947</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.774076923695449</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.712893618344874</v>
+      </c>
+      <c r="L38" t="n">
+        <v>71.17157753560264</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.94780186405562</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>27.90728380479156</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-12158.414116309</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-448.377002808955</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.792557680674301e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9567110298252312</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>77.33299999999997</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6127570223049795</v>
+      </c>
+      <c r="D39" t="n">
+        <v>912.1938252772866</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7086802863839599</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.85582e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.497</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2587208054347807</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8839057860450589</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.416475447077426</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.538522141991346</v>
+      </c>
+      <c r="L39" t="n">
+        <v>66.58144710793715</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.9343229594916</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>27.72502753962861</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-11970.20292691997</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-437.4611788416014</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.77760869651101e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9571706666145723</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>75.56999999999999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5987876867002098</v>
+      </c>
+      <c r="D40" t="n">
+        <v>861.8209095801922</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6695457391715179</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.85464e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.607</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2543339516804881</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9588104467048927</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.579328380638299</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.577339570749896</v>
+      </c>
+      <c r="L40" t="n">
+        <v>73.97427118423293</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.87411261549317</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>26.9390959888367</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-11512.47549531506</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-395.6464571395412</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.743627944763477e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9584632276209664</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>73.96099999999996</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5860385880115679</v>
+      </c>
+      <c r="D41" t="n">
+        <v>224.4674493150418</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1743879994102189</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.85318e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.62</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3387417122810814</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.027002561894173</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.583097014269512</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.631768941793241</v>
+      </c>
+      <c r="L41" t="n">
+        <v>71.54149278135827</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.9132204823778</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>27.44441493183694</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-11638.89637173298</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>194.7098788015028</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.010061021429438e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9928682224195989</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>73.87</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5853175389247651</v>
+      </c>
+      <c r="D42" t="n">
+        <v>949.2756486858644</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7374890291145326</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.85219e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.67700000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2420241148803841</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.06438611284862</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.541251040015085</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.468336651475247</v>
+      </c>
+      <c r="L42" t="n">
+        <v>69.14300657804365</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.98631334448017</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>28.44145923289737</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-11981.09387389747</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-480.4461686373085</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.716763761359019e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.959440793080431</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>73.55000000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5827819816964461</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1054.602181001849</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8193168545362097</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.85043e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.724</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3958316044425483</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.024542466112109</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.736165161327733</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.642293903455185</v>
+      </c>
+      <c r="L43" t="n">
+        <v>71.76188862892835</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.10965037978816</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>30.29862204706572</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-12706.02240559245</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-578.06466913063</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.70021274462572e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9600280212497452</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>2.109349140119466e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9946626693045172</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>110.528</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>258.7721809245248</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.33264e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-79.247</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1510618611807043</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4960195001574212</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.052668123603086</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.916774354053074</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.47232417061691</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.30208605106759</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.02240022290733</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-4753.424589584552</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>182.4202959001747</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.23017765750471e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9900257001017657</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>76.30899999999997</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6904042414591773</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1577.520917897635</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.096176614741075</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.29263e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.348</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2952116980141143</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8142840404507666</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.289290109483257</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.188875610587383</v>
+      </c>
+      <c r="L13" t="n">
+        <v>17.59351546207182</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.91565009022914</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.00435722688345</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6004.551330662123</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1029.424569678811</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.628143140030422e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9189301152051399</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>68.392</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6187753329473074</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1210.513409428776</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.677911687044295</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.22555e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.224</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3234001837650405</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8441974878223498</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.526859376272345</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.445352675769706</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21.8837380595373</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.50723530051565</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.38380869726791</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-6831.823986951316</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-721.0618737796283</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.088121567821781e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9309032839370458</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>64.28699999999998</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5816354226983205</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1158.817522596773</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.478137945341045</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.17461e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-82.798</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2374391016058989</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7153788739296498</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.308342559995074</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.060697280363554</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.22675319762712</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.85070831700442</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>18.17490180102939</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-7452.965955708944</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-682.0717972178495</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.766402512075581e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9382800859000076</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>63.44399999999996</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5740083960625357</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1363.680052227353</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.269809325543739</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.13556e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.173</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3140501217841745</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.025257334128248</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.533797163636335</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.367205506010469</v>
+      </c>
+      <c r="L16" t="n">
+        <v>28.60255462557942</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.15456286429219</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>20.11946334980769</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8163.710795533659</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-873.309812178927</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.561796761078541e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.943001040376605</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>59.33799999999997</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5368594383323678</v>
+      </c>
+      <c r="D17" t="n">
+        <v>285.7817048770211</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.104375686196245</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.10572e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.495</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.6312124098040313</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.34907883071467</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.120357435361043</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31.13261014997833</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.2028090156015</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>20.46705169477937</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8138.084730669253</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>108.4537672770063</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.191544550160724e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9777625940142234</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58.24900000000002</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.527006731325999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1452.03912143886</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.611264380317492</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.08217e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.73</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1537407469890794</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8262612015108791</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.551033397085794</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.436708539477634</v>
+      </c>
+      <c r="L18" t="n">
+        <v>34.78708597284398</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.3724872257356</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>21.79080140932779</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-8556.790384070811</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-966.6629009672993</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.28346261217713e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9498736696083765</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>54.84800000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4962362478286045</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1483.067897218482</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.731172075452124</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.06404e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-83.94</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7494589112114485</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.553817794678873</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.362726233215268</v>
+      </c>
+      <c r="L19" t="n">
+        <v>37.00466095958433</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.40992378631864</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>22.10620114261691</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-8532.471943589499</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1001.590649423954</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.18716131799048e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.952410867380878</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>52.55900000000003</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4755265634047482</v>
+      </c>
+      <c r="D20" t="n">
+        <v>277.0998209549045</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.070825387663001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.04952e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.096</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.03565944642924405</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5004096257670951</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.336466297339484</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.118702268697823</v>
+      </c>
+      <c r="L20" t="n">
+        <v>37.2899207525377</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.45605437544947</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>22.50760528192265</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-8558.562107446602</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>100.8621028369607</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.987717821788901e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9851584140909954</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>48.81099999999998</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4416166039374635</v>
+      </c>
+      <c r="D21" t="n">
+        <v>249.6636074884817</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9648008012163418</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.03864e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2563635439275409</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9926093050820718</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.037371737764387</v>
+      </c>
+      <c r="L21" t="n">
+        <v>38.91013512432752</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.35327508706726</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21.63240278869427</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-8073.835542757663</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>124.379781406035</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.109349140119466e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9946626693045172</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>3.779635824933687e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9605521371591935</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>124.96</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>280.6835688808752</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.15126e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.19499999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4057070833483696</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8053748792515003</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.364871863717013</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.367005416128858</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22.53178775862833</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.30431200438761</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15.48190698759758</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7987.922226105684</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>208.3634122724767</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.570865159364706e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9583794615923398</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>104.848</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8390524967989754</v>
+      </c>
+      <c r="D24" t="n">
+        <v>300.3917292258749</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.070214870159942</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.04695e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.729</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6238346451875197</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.196423588085827</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.8064563650106</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.616515408539993</v>
+      </c>
+      <c r="L24" t="n">
+        <v>36.87037076161669</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.31236314362366</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>21.30263589032044</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-10453.37906471734</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>176.3335081172038</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.748394058196239e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9462952187521997</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96.53099999999995</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.772495198463508</v>
+      </c>
+      <c r="D25" t="n">
+        <v>799.2971693374116</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.847680655210142</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.00868e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.166</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.06818604703665022</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6264028865711501</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.477912588790344</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.439502624646278</v>
+      </c>
+      <c r="L25" t="n">
+        <v>43.24011030866729</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.3468866723552</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21.58023999929786</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10342.09511917656</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-290.5330936888622</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.489664134397564e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9388980632463899</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>94.52999999999997</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7564820742637643</v>
+      </c>
+      <c r="D26" t="n">
+        <v>791.1854780474258</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.818780882692897</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.98863e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.399</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1110759864314674</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.108061162488387</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.599234767628625</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.424269832401882</v>
+      </c>
+      <c r="L26" t="n">
+        <v>47.8866889164651</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.4567537694181</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>22.51380302556043</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10665.8415541838</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-288.2814829329907</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.359411526968289e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9423403858861641</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92.78500000000003</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7425176056338031</v>
+      </c>
+      <c r="D27" t="n">
+        <v>830.2174215391125</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.957841190523927</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.97582e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.568</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.241685382853705</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6686681648948729</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.464639857970716</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.311843727782422</v>
+      </c>
+      <c r="L27" t="n">
+        <v>48.24666692001083</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.58175752045857</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>23.67907861706804</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-11109.85438935966</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-328.1657573900189</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.272586588934582e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9447329504619277</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90.541</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7245598591549297</v>
+      </c>
+      <c r="D28" t="n">
+        <v>876.6317273880135</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.123202868209448</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.96574e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.73099999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.4195948978627454</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8967976421586296</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.797878315116214</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.495056104936286</v>
+      </c>
+      <c r="L28" t="n">
+        <v>55.2761735856304</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.68095563085834</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>24.69314046551235</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-11470.74473171246</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-374.7357834472147</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.196190617590498e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9469428800148512</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>86.721</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.693990076824584</v>
+      </c>
+      <c r="D29" t="n">
+        <v>843.2479117212134</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.004265319424865</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.95844e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-83.81999999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.05522112977547446</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7604135958447696</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.42913269369061</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.229254323735572</v>
+      </c>
+      <c r="L29" t="n">
+        <v>52.8945006397507</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.59691453622732</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>23.82860697059664</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10899.96096864557</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-350.1702395769662</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.14776932130355e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9483399330271881</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>87.43799999999999</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6997279129321383</v>
+      </c>
+      <c r="D30" t="n">
+        <v>941.1868576415703</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.353195420003439</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.9517e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-83.932</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6766973606147526</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.278218023216334</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.903953662788486</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.536264868640921</v>
+      </c>
+      <c r="L30" t="n">
+        <v>57.08021652063487</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.85833213739475</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>26.74041733935464</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-12184.70842095018</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-442.0285205788441</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.096945883440376e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9498592349681894</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83.87699999999995</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6712307938540331</v>
+      </c>
+      <c r="D31" t="n">
+        <v>863.7168530711241</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.077190647514155</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.94842e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.015</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1889606284772116</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9125842806124042</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.506684273391224</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.670061786139975</v>
+      </c>
+      <c r="L31" t="n">
+        <v>60.52769741581959</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.7208202390443</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>25.1255105000614</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-11277.14185148296</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-377.7531637035357</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.061919148170452e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9509893207657424</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>81.40099999999995</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6514164532650446</v>
+      </c>
+      <c r="D32" t="n">
+        <v>858.8415840846189</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.059821376466535</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.94245e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.111</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4119672874672737</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9659509904488134</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.522225168314036</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.473802438218942</v>
+      </c>
+      <c r="L32" t="n">
+        <v>61.250894534111</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.72867139211171</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>25.212451738592</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-11202.34366021609</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-377.4213587376789</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.01959212551893e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9522762712718709</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80.79599999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6465749039692702</v>
+      </c>
+      <c r="D33" t="n">
+        <v>860.2776892602224</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.064937832628645</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.93913e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.166</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3924705789042351</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.11255262776694</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.727037248295055</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.611666210330831</v>
+      </c>
+      <c r="L33" t="n">
+        <v>63.3271735158431</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.79845730324153</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>26.01247722288106</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-11467.55342588361</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-382.2046771073084</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.994986912557351e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.95303830115764</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80.49299999999999</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6441501280409732</v>
+      </c>
+      <c r="D34" t="n">
+        <v>923.0511250297969</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.288582686582373</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.93662e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.233</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5272546335985324</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.058419838938075</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.440086817524804</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.574824980029689</v>
+      </c>
+      <c r="L34" t="n">
+        <v>60.86569088545869</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.86654852666324</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>26.8434963518308</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-11745.34269629697</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-442.3072402093528</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.96724520288062e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9539697415323966</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78.20999999999998</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6258802816901408</v>
+      </c>
+      <c r="D35" t="n">
+        <v>868.9181022059111</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.095721298081001</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.93307e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.288</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2596611031854913</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9435141653295204</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.652497718098607</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.570534311941905</v>
+      </c>
+      <c r="L35" t="n">
+        <v>63.1261481642739</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.83201676099829</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>26.41553287888622</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-11435.6013890905</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-397.3912100154226</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.943063813999103e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9547232168260446</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>76.49799999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6121798975672216</v>
+      </c>
+      <c r="D36" t="n">
+        <v>887.917346387834</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.163410490781791</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.93089e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.396</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2126113263100747</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9583014120608666</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.622330190163768</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.526882202320606</v>
+      </c>
+      <c r="L36" t="n">
+        <v>67.45594452103708</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.85722191856998</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>26.72654964426845</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-11468.04262855224</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-418.003151896441</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.906950124330994e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9559924581828777</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>76.19900000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6097871318822025</v>
+      </c>
+      <c r="D37" t="n">
+        <v>904.9451348840852</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.224075917561647</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.92741e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.45699999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3853431843905843</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.100689473371648</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.676130369838767</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.776011557096753</v>
+      </c>
+      <c r="L37" t="n">
+        <v>70.73710940714196</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.91231771813393</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>27.43253680021083</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11676.23337937664</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-436.9051662934388</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.88113878768437e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9568250039780318</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>73.32600000000002</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5867957746478876</v>
+      </c>
+      <c r="D38" t="n">
+        <v>278.8337966066845</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9934097593187732</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.92711e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.498</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3312520345965826</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7302696731388462</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.69889412080919</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.613094364127872</v>
+      </c>
+      <c r="L38" t="n">
+        <v>68.70260289887703</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.81897619692099</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>26.25744040055866</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-11042.48341330128</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>136.6933822041894</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.65736443741952e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9731729562102959</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>64.48699999999997</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5160611395646605</v>
+      </c>
+      <c r="D39" t="n">
+        <v>828.2009927069897</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.950657197388303</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.92538e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.541</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.4738586040946151</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.693017134135737</v>
+      </c>
+      <c r="L39" t="n">
+        <v>53.1934855700438</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.09435177645804</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>19.70185256947746</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-8057.979069796295</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-375.0752663916552</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.850403723704442e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9579387824477997</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>71.99799999999999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5761683738796415</v>
+      </c>
+      <c r="D40" t="n">
+        <v>977.6896346323788</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.48324498840657</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.92352e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.61499999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6011164811750711</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9191885644715528</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.726160834817446</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.856578133209753</v>
+      </c>
+      <c r="L40" t="n">
+        <v>72.8778974737164</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.98796477474913</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>28.46482252698918</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-11809.41632763514</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-512.5601959648288</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.824612640744002e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.958858704275537</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>70.68600000000004</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5656690140845074</v>
+      </c>
+      <c r="D41" t="n">
+        <v>932.096459678492</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.320808779063526</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.92278e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.658</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4060632175973847</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.042458625133424</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.692159747203979</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.45092872606736</v>
+      </c>
+      <c r="L41" t="n">
+        <v>68.76086919907341</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.97144659451202</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>28.23284666278051</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-11595.30394880118</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-475.1242312056642</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.809198333641624e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9594401554595718</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>64.14300000000003</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.513308258642766</v>
+      </c>
+      <c r="D42" t="n">
+        <v>864.346147332627</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.079432653571053</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.92051e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.7</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.2050488504487967</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.018619994531899</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.15803020546676</v>
+      </c>
+      <c r="L42" t="n">
+        <v>63.22929337681712</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.51577827187131</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>23.04942061376361</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-9258.845952607056</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-417.8739529071532</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.792846845877749e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9599847294952689</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>68.22300000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5459587067861718</v>
+      </c>
+      <c r="D43" t="n">
+        <v>959.098100348849</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.417008356324198</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.92126e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.748</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3460987541429899</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.04467895370356</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.545406007342919</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.44085235249768</v>
+      </c>
+      <c r="L43" t="n">
+        <v>67.47622063492624</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.00158543006893</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>28.65899013826956</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-11563.32149353308</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-505.9818221939215</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.779635824933687e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9605521371591935</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>2.031787738120481e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9875130401683181</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>119.722</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>260.0234043841783</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.35159e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-79.379</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3355328595150014</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6804482055511709</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.099263407657684</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.771352673606299</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.03731213504306</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.58138443730105</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.54233489030185</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5076.239441812922</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>180.6379033358458</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.167010696321703e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9908094111713995</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>76.97699999999998</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6429645345049361</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1414.328495751937</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5.439235360761222</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.28991e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.65600000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1603454460234977</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6766586862729377</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.322708837300078</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.202351370345294</v>
+      </c>
+      <c r="L13" t="n">
+        <v>19.43209824949156</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.10257211204122</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.67823969356871</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6259.776557979794</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-883.0249945161697</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.498404646487141e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9222292018676466</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>70.84300000000002</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5917291725831509</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1388.952374582128</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.34164367962041</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.21697e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.571</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6273173030063035</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.005965799737246</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.667087109934765</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.30741187980177</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.55542526042193</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.85636092540231</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18.20764812775504</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7592.345015751976</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-882.3382697290455</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.943888532198906e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9347560956255834</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>66.61000000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5563722624079116</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1152.438837866765</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.43205810875418</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.16364e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4251616491959277</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.104925905465788</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.523367977419534</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.607825413038416</v>
+      </c>
+      <c r="L15" t="n">
+        <v>30.06731447683306</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.12585401084098</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>19.91816448159312</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8153.215156702091</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-677.5261796584796</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.637422447401791e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9418317249654024</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>63.959</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5342292978734066</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1119.172656102291</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.304122772151465</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.12615e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.468</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2104298985136608</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8546211693505856</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.6447065905638</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.372616878021829</v>
+      </c>
+      <c r="L16" t="n">
+        <v>33.23591491543556</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.30968270270574</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.28138027621788</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8592.884326206267</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-652.8772251310377</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.449715321288874e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9462464707352591</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>59.96599999999995</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5008770317903136</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1198.124134275422</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.607754971568723</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.09917e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.755</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5001443720737273</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.259206905605665</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.130466575246023</v>
+      </c>
+      <c r="L17" t="n">
+        <v>35.4602143761583</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.35629203936875</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>21.65712443419743</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8593.148600568107</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-730.2282425009957</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.308082413939267e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9497996930235951</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58.38999999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4877132022518832</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1206.454817613241</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.639793177350811</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.07858e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.965</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1512018233207274</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8047038994732026</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.383524679641766</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.215004230025612</v>
+      </c>
+      <c r="L18" t="n">
+        <v>38.84563472361194</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.47807250315246</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>22.70436923196747</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-8896.116349278796</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-743.4933088953675</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.206757934116415e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9523874288927405</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57.78399999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4826514759192126</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1310.533998997832</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.040061690222121</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.06218e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.107</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.360155359749003</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9095160942308766</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.652409814546662</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.452019306743237</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40.4718942824779</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.62764350509046</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>24.13761720802264</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9358.576339660338</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-843.435774108191</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.134157118207357e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9542196711932915</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>54.15499999999997</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4523395867092093</v>
+      </c>
+      <c r="D20" t="n">
+        <v>290.797738895604</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.118352171352842</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.05109e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1289736245424689</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4504251037910206</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.247410594748134</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.159750425796299</v>
+      </c>
+      <c r="L20" t="n">
+        <v>42.37005219511519</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.55097369441968</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>23.38108078055718</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-8897.997046131297</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>88.07387967214989</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.014724352977579e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9796621967942323</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>54.13499999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4521725330348639</v>
+      </c>
+      <c r="D21" t="n">
+        <v>271.2920793308095</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.043337156412205</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.04068e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.393</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2649344826764415</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9451558878577174</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.485217419381681</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.509662586807515</v>
+      </c>
+      <c r="L21" t="n">
+        <v>46.38228518431572</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.7410947813129</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>25.35125862392669</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9576.223069857489</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>103.0968507015975</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.031787738120481e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9875130401683181</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>3.773292748369564e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9614831580543918</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>123.476</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1242.008456904876</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.16062e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.358</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1533710651901444</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7245642791048292</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.221589433776774</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.175556123042548</v>
+      </c>
+      <c r="L23" t="n">
+        <v>24.19059123434943</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.34408499697118</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15.65080144821873</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8041.755187989226</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-631.9968486493535</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.718361790685231e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9099393122285412</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>105.87</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.857413586445949</v>
+      </c>
+      <c r="D24" t="n">
+        <v>837.9793466263948</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6746969732514265</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.06331e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.718</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.167238872282497</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7050714748481942</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.409574464902523</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.172448982978186</v>
+      </c>
+      <c r="L24" t="n">
+        <v>36.0521371975066</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.17115866982472</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>20.23769081315276</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9910.926835935528</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-313.2206116927107</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.7944172539051e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9316954105400852</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100.762</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8160452233632447</v>
+      </c>
+      <c r="D25" t="n">
+        <v>800.3305512296578</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6443841398826756</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.02365e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.161</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.118683459369862</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8824416069147959</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.501044363112665</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.226485937308932</v>
+      </c>
+      <c r="L25" t="n">
+        <v>41.99482348921419</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.38250855412426</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21.87434653623128</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10531.45082497798</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-288.2663053439209</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.528820728558591e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9383162380497957</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97.35000000000002</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7884123230425347</v>
+      </c>
+      <c r="D26" t="n">
+        <v>809.4347524556584</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6517143647095569</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.00137e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.40600000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4456917023317447</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6350826278786909</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.372139171861937</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.26986075329446</v>
+      </c>
+      <c r="L26" t="n">
+        <v>46.42372623510469</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.49667151033833</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>22.87327340244075</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10873.96235495501</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-301.8856040593159</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.389175667214527e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.941933419288708</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93.16399999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7545109980886973</v>
+      </c>
+      <c r="D27" t="n">
+        <v>773.3132246924616</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6226312070527944</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.98912e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.601</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1273861864446729</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6328501924732713</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.362341768281472</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.473878970157005</v>
+      </c>
+      <c r="L27" t="n">
+        <v>54.04369071210695</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.43192785567331</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>22.29587139013903</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10421.73861125145</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-275.7802034931219</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.292759090466947e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9446654181731156</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91.79200000000003</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7433995270335938</v>
+      </c>
+      <c r="D28" t="n">
+        <v>249.3252643342661</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2007436124513939</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.97741e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.742</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.05249041822420263</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8032345853238527</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.349927941641192</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.288935125191448</v>
+      </c>
+      <c r="L28" t="n">
+        <v>52.96937609159355</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.53207240313291</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>23.20179130868673</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10718.83333377476</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>204.3462658281587</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.589545864023521e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9698860153875035</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>88.84000000000003</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7194920470374813</v>
+      </c>
+      <c r="D29" t="n">
+        <v>797.2352084168997</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6418919323654484</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.97057e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-83.855</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1700647641337131</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7124500758115256</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.406216605477173</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.201836601116868</v>
+      </c>
+      <c r="L29" t="n">
+        <v>54.72558091695743</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.59404176537804</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>23.80012163804978</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10854.50825440769</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-308.5977769091123</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.162164143340568e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9484224799859466</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>87.959</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7123570572418932</v>
+      </c>
+      <c r="D30" t="n">
+        <v>887.595309841316</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7146451418319898</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.96572e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-83.97499999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5752312257961332</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.152255718735553</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.611151521995237</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.764956126595941</v>
+      </c>
+      <c r="L30" t="n">
+        <v>63.33998589125022</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.80924670836981</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>26.14071389635892</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-11833.50793657148</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-394.7412267762481</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.109958591551783e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.95008404773359</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>84.37299999999999</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6833149761897048</v>
+      </c>
+      <c r="D31" t="n">
+        <v>874.4170741171235</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7040347183272796</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.95921e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.054</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2813013731631299</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.047920397374887</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.54900727540491</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.597043891723491</v>
+      </c>
+      <c r="L31" t="n">
+        <v>62.12484118042187</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.71843829331985</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>25.09925181224669</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-11191.99089146436</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-388.2711037633563</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.069792562363318e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.951253090629922</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>82.64500000000004</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6693203537529564</v>
+      </c>
+      <c r="D32" t="n">
+        <v>807.6178161160427</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6502514629639895</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.95583e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.151</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.09319130765298622</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7137455480773889</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.485974028876222</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.443909492176366</v>
+      </c>
+      <c r="L32" t="n">
+        <v>60.31831370401734</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.72565101633602</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>25.17893402795078</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-11088.9380627502</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-333.4180099214634</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.029520022061135e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9525873861399603</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80.87399999999997</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6549774855032554</v>
+      </c>
+      <c r="D33" t="n">
+        <v>843.9191915736076</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6794794245416659</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.95296e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.20099999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3599413389630866</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9145946503021367</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.802260968801326</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.616039436042207</v>
+      </c>
+      <c r="L33" t="n">
+        <v>64.05266926438564</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.81329754196575</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>26.18918636428014</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-11435.84828978607</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-370.4749441579589</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.005688885956205e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9533513092475097</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78.54899999999998</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.636147915384366</v>
+      </c>
+      <c r="D34" t="n">
+        <v>823.219794798537</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6628133570443042</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.94949e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.303</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1708077574308895</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7762551210474734</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.512155374442657</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.34444198768511</v>
+      </c>
+      <c r="L34" t="n">
+        <v>61.12813746493553</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.78284089096459</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>25.82907897366553</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-11145.94417561867</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-356.2138789156168</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.965582726027328e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9546981553563281</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78.85699999999997</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.638642327253879</v>
+      </c>
+      <c r="D35" t="n">
+        <v>914.9663873057029</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7366828963353662</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.94769e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.392</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5627007889638423</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.068253994196024</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.672813135867305</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.481622282947821</v>
+      </c>
+      <c r="L35" t="n">
+        <v>65.54995613195798</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.92232514794816</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>27.56478643485267</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-11825.7179390845</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-441.9653624789083</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.934330596012159e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9558029224871718</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>75.49099999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6113819689656288</v>
+      </c>
+      <c r="D36" t="n">
+        <v>824.7546394509691</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6640491333740862</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.94521e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.419</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2204768402855436</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6561107785640229</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.602392556592513</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.588404823648371</v>
+      </c>
+      <c r="L36" t="n">
+        <v>66.29716072186261</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.79026631901429</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>25.9159596897849</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-10963.16330667192</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-365.0599691287987</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.919390020539939e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9562638114744985</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>75.44800000000004</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6110337231526778</v>
+      </c>
+      <c r="D37" t="n">
+        <v>894.4030663916237</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7201263899768477</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.94213e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.486</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4084886904978213</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.067863444094029</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.727325641167364</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.699398319383147</v>
+      </c>
+      <c r="L37" t="n">
+        <v>70.00739688004435</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.93441783095179</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>27.72630204445711</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11663.67757229711</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-431.1710404716848</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.892789259204391e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9571435246807782</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>73.67500000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5966746574233051</v>
+      </c>
+      <c r="D38" t="n">
+        <v>831.6394740232223</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6695924406953668</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.94177e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.547</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3421720146806932</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.152414468641993</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.589321176364626</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.423485846321491</v>
+      </c>
+      <c r="L38" t="n">
+        <v>64.90500295091788</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.90393481292853</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>27.32272703207274</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-11367.48987197617</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-378.6284835931449</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.873320049307927e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.957885023769002</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>72.63799999999998</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5882762642132883</v>
+      </c>
+      <c r="D39" t="n">
+        <v>875.330430074435</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7047701045899364</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.93998e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.598</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3530225523922933</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.011735491274543</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.686434274838671</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.722171198697846</v>
+      </c>
+      <c r="L39" t="n">
+        <v>71.41813176231717</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.9064504720627</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>27.35558796752993</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-11271.29471457049</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-421.3114284644072</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.85349753708965e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9585727838725465</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>71.65199999999999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5802909067349119</v>
+      </c>
+      <c r="D40" t="n">
+        <v>920.0541756620033</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7407793163943562</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.93884e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.655</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.50489475641645</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.139473550624453</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.5714424977189</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.652950907873838</v>
+      </c>
+      <c r="L40" t="n">
+        <v>68.62224383112247</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.97865480775026</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>28.33361037370389</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-11585.46290314838</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-464.8902497046043</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.833658351484886e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9593036217779071</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>69.036</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5591046033237228</v>
+      </c>
+      <c r="D41" t="n">
+        <v>857.7855096272497</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6906438558114797</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.93564e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.729</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2225979619249348</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9607236614117955</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.56991567667043</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.501764017444762</v>
+      </c>
+      <c r="L41" t="n">
+        <v>70.63260643865866</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.91287197858743</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>27.43982827175756</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-11087.49140504981</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-412.7835645924011</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.806417972160746e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9602221084007631</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>68.30000000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.553143930804367</v>
+      </c>
+      <c r="D42" t="n">
+        <v>227.1604942619717</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.1828977033119909</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.93534e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.773</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.08864719402297366</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8722136673376452</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.511189771764061</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.499596440390314</v>
+      </c>
+      <c r="L42" t="n">
+        <v>70.72505513174754</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.93871331944476</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>27.78413056553261</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-11127.63190125026</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>168.8106566591474</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.752517323209766e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9942905203413744</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>67.17000000000002</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5439923547895948</v>
+      </c>
+      <c r="D43" t="n">
+        <v>896.8330555604782</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7220828896732429</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.93414e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.828</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2331695885852351</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9122493617328646</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.649961773729861</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.574527433048503</v>
+      </c>
+      <c r="L43" t="n">
+        <v>74.0091934585966</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.99303877125151</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>28.53684637346715</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-11332.96529429052</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-454.5880246731366</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.773292748369564e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9614831580543918</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.9969559098377738</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>119.649</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>218.8217784862454</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.22643e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-80.02800000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3090341367424562</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5308465054758211</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.027644683138892</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.743696397116366</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14.57643281036454</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.89641936567848</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.19687740708324</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5404.922887160995</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>218.859017686955</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.49209951005785e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9953731469205851</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>72.42899999999997</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6053456359852567</v>
+      </c>
+      <c r="D13" t="n">
+        <v>208.2323038121337</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9516068521727264</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.16105e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-82.399</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2408363026047992</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7227355020843027</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.246241661801309</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.123317880375487</v>
+      </c>
+      <c r="L13" t="n">
+        <v>22.68401499367438</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.56053363199396</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16.63831917910231</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7005.26348855395</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>203.7326792746686</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.915511483878306e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9987834351979642</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>64.93199999999996</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5426873605295486</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1168.160154169192</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.338409011434936</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.09133e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.236</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3624615440235107</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9136509366498469</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.462481742756875</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.243777689528735</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29.23334580861584</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.14506056677826</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>20.05238789549495</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8202.642918390571</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-691.417298341971</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.481677780507303e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9435191502944668</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>61.55399999999997</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5144547802321789</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1290.123872599936</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.895774550068515</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.04231e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.06844359911676329</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6873639578265295</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.609985596460753</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.34321390745836</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35.10020962830896</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.38244622427608</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21.87382493336156</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8793.679850124627</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-808.1290012333595</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.242455604650512e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9493545127657979</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>59.298</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.4955996289145752</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1318.808614792709</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6.026861786408551</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.01126e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-84.06100000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1555675523765995</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8204768247986844</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.547259575064588</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.520914854308544</v>
+      </c>
+      <c r="L16" t="n">
+        <v>41.16124270910477</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.58863587287293</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>23.74670272912869</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9406.968541564451</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-841.3384847983297</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.078205554322477e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9537441635662159</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>54.553</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4559419635767955</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1501.658304605001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6.862471893762582</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.99036e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-84.277</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2138370355941804</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.109952624219674</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.164037848852737</v>
+      </c>
+      <c r="L17" t="n">
+        <v>42.05634372696766</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.45309475640305</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22.48141600116517</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8700.101075581944</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-1012.710134517282</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.980646115841885e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9563507607161409</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>52.47500000000002</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4385744970705984</v>
+      </c>
+      <c r="D18" t="n">
+        <v>278.7694895087054</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.273956785458757</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.97612e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.42100000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0005794371424074043</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2331873151208127</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.08227993573927</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.076285827223712</v>
+      </c>
+      <c r="L18" t="n">
+        <v>43.1564362449834</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.50780406106331</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>22.97557735749044</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-8746.053549221731</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>101.3913767918073</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.94983875479594e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9875606215530723</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>50.22800000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4197945657715485</v>
+      </c>
+      <c r="D19" t="n">
+        <v>250.2821874905183</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.143771836706145</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.9661e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.605</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.03656112523676364</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3001650276894069</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.212283279106117</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.235377642781037</v>
+      </c>
+      <c r="L19" t="n">
+        <v>48.3938397270645</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.56832152919188</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>23.54808634414038</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-8815.579496827868</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>124.0587381686861</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.032705174252774e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9971797572280874</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>52.488</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4386831482085099</v>
+      </c>
+      <c r="D20" t="n">
+        <v>267.7897913784959</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.223780344127531</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.95805e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.70999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8745145247774707</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.096867263827675</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.606574075872174</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.880229214074707</v>
+      </c>
+      <c r="L20" t="n">
+        <v>52.76862864027265</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.93266750370438</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>27.70280693916595</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-10328.27698914494</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>101.4530164305408</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.899976238827829e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9931607619717784</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>46.024</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.3846584593268644</v>
+      </c>
+      <c r="D21" t="n">
+        <v>180.0649729290919</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8228841488024478</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.95183e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.83199999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0576374564442183</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1707707730924771</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.133223056637642</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.11558045342054</v>
+      </c>
+      <c r="L21" t="n">
+        <v>48.62871498862907</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.62702090976043</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>24.1312770089516</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-8761.431537887789</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>189.0153037404162</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.602840738619943e-09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9969559098377738</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
